--- a/stella/test_fixtures/pantry_loaded/iri_data.xlsx
+++ b/stella/test_fixtures/pantry_loaded/iri_data.xlsx
@@ -499,22 +499,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15028.5</v>
+        <v>15328.75</v>
       </c>
       <c r="E2" t="n">
-        <v>400.8</v>
+        <v>408.8</v>
       </c>
       <c r="F2" t="n">
         <v>6.25</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2532</v>
+        <v>0.2522</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2525</v>
+        <v>0.2515</v>
       </c>
       <c r="I2" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14522.01</v>
+        <v>14926.65</v>
       </c>
       <c r="E3" t="n">
-        <v>387.3</v>
+        <v>398</v>
       </c>
       <c r="F3" t="n">
         <v>6.25</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2447</v>
+        <v>0.2456</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2439</v>
+        <v>0.2449</v>
       </c>
       <c r="I3" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -571,22 +571,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16632.16</v>
+        <v>16664.74</v>
       </c>
       <c r="E4" t="n">
-        <v>462</v>
+        <v>462.9</v>
       </c>
       <c r="F4" t="n">
         <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2803</v>
+        <v>0.2742</v>
       </c>
       <c r="H4" t="n">
-        <v>0.291</v>
+        <v>0.2848</v>
       </c>
       <c r="I4" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -607,22 +607,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13160.74</v>
+        <v>13865.53</v>
       </c>
       <c r="E5" t="n">
-        <v>337.5</v>
+        <v>355.5</v>
       </c>
       <c r="F5" t="n">
         <v>6.5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2218</v>
+        <v>0.2281</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2126</v>
+        <v>0.2188</v>
       </c>
       <c r="I5" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -643,19 +643,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15575.48</v>
+        <v>14553.74</v>
       </c>
       <c r="E6" t="n">
-        <v>415.3</v>
+        <v>388.1</v>
       </c>
       <c r="F6" t="n">
         <v>6.25</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2541</v>
+        <v>0.244</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2534</v>
+        <v>0.2435</v>
       </c>
       <c r="I6" t="n">
         <v>91</v>
@@ -679,22 +679,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15362.43</v>
+        <v>14940.46</v>
       </c>
       <c r="E7" t="n">
-        <v>409.7</v>
+        <v>398.4</v>
       </c>
       <c r="F7" t="n">
         <v>6.25</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2506</v>
+        <v>0.2505</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2499</v>
+        <v>0.25</v>
       </c>
       <c r="I7" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -715,19 +715,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16562.2</v>
+        <v>16032.55</v>
       </c>
       <c r="E8" t="n">
-        <v>460.1</v>
+        <v>445.3</v>
       </c>
       <c r="F8" t="n">
         <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2702</v>
+        <v>0.2688</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2807</v>
+        <v>0.2794</v>
       </c>
       <c r="I8" t="n">
         <v>90</v>
@@ -751,22 +751,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13805.59</v>
+        <v>14116.03</v>
       </c>
       <c r="E9" t="n">
-        <v>354</v>
+        <v>361.9</v>
       </c>
       <c r="F9" t="n">
         <v>6.5</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2252</v>
+        <v>0.2367</v>
       </c>
       <c r="H9" t="n">
-        <v>0.216</v>
+        <v>0.2271</v>
       </c>
       <c r="I9" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -787,22 +787,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15429.09</v>
+        <v>15065.5</v>
       </c>
       <c r="E10" t="n">
-        <v>411.4</v>
+        <v>401.7</v>
       </c>
       <c r="F10" t="n">
         <v>6.25</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2561</v>
+        <v>0.2513</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2556</v>
+        <v>0.2506</v>
       </c>
       <c r="I10" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14955.36</v>
+        <v>14476.58</v>
       </c>
       <c r="E11" t="n">
-        <v>398.8</v>
+        <v>386</v>
       </c>
       <c r="F11" t="n">
         <v>6.25</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2483</v>
+        <v>0.2414</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2477</v>
+        <v>0.2408</v>
       </c>
       <c r="I11" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16051.08</v>
+        <v>16624.61</v>
       </c>
       <c r="E12" t="n">
-        <v>445.9</v>
+        <v>461.8</v>
       </c>
       <c r="F12" t="n">
         <v>6</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2665</v>
+        <v>0.2773</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2769</v>
+        <v>0.288</v>
       </c>
       <c r="I12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -895,22 +895,22 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13802.4</v>
+        <v>13793.78</v>
       </c>
       <c r="E13" t="n">
-        <v>353.9</v>
+        <v>353.7</v>
       </c>
       <c r="F13" t="n">
         <v>6.5</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2291</v>
+        <v>0.23</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2198</v>
+        <v>0.2206</v>
       </c>
       <c r="I13" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -931,22 +931,22 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14679.08</v>
+        <v>15334.06</v>
       </c>
       <c r="E14" t="n">
-        <v>391.4</v>
+        <v>408.9</v>
       </c>
       <c r="F14" t="n">
         <v>6.25</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2488</v>
+        <v>0.2587</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2481</v>
+        <v>0.258</v>
       </c>
       <c r="I14" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -967,19 +967,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14841.01</v>
+        <v>14633.57</v>
       </c>
       <c r="E15" t="n">
-        <v>395.8</v>
+        <v>390.2</v>
       </c>
       <c r="F15" t="n">
         <v>6.25</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2515</v>
+        <v>0.2469</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2509</v>
+        <v>0.2462</v>
       </c>
       <c r="I15" t="n">
         <v>91</v>
@@ -1003,22 +1003,22 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16026.84</v>
+        <v>16156.87</v>
       </c>
       <c r="E16" t="n">
-        <v>445.2</v>
+        <v>448.8</v>
       </c>
       <c r="F16" t="n">
         <v>6</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2716</v>
+        <v>0.2726</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2822</v>
+        <v>0.2831</v>
       </c>
       <c r="I16" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1039,19 +1039,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13461.63</v>
+        <v>13151.83</v>
       </c>
       <c r="E17" t="n">
-        <v>345.2</v>
+        <v>337.2</v>
       </c>
       <c r="F17" t="n">
         <v>6.5</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2281</v>
+        <v>0.2219</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2188</v>
+        <v>0.2127</v>
       </c>
       <c r="I17" t="n">
         <v>92</v>
@@ -1075,22 +1075,22 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>27279.33</v>
+        <v>26032.14</v>
       </c>
       <c r="E18" t="n">
-        <v>909.3</v>
+        <v>867.7</v>
       </c>
       <c r="F18" t="n">
         <v>5</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3298</v>
+        <v>0.3212</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3542</v>
+        <v>0.3453</v>
       </c>
       <c r="I18" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>26359.68</v>
+        <v>26126.41</v>
       </c>
       <c r="E19" t="n">
-        <v>878.7</v>
+        <v>870.9</v>
       </c>
       <c r="F19" t="n">
         <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3187</v>
+        <v>0.3224</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3423</v>
+        <v>0.3465</v>
       </c>
       <c r="I19" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -1147,22 +1147,22 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15658</v>
+        <v>15837.33</v>
       </c>
       <c r="E20" t="n">
-        <v>434.9</v>
+        <v>439.9</v>
       </c>
       <c r="F20" t="n">
         <v>6</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1893</v>
+        <v>0.1954</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1694</v>
+        <v>0.1751</v>
       </c>
       <c r="I20" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1183,22 +1183,22 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13414.92</v>
+        <v>13044.68</v>
       </c>
       <c r="E21" t="n">
-        <v>344</v>
+        <v>334.5</v>
       </c>
       <c r="F21" t="n">
         <v>6.5</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1622</v>
+        <v>0.161</v>
       </c>
       <c r="H21" t="n">
-        <v>0.134</v>
+        <v>0.1331</v>
       </c>
       <c r="I21" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1219,22 +1219,22 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>26680.72</v>
+        <v>26267.26</v>
       </c>
       <c r="E22" t="n">
-        <v>889.4</v>
+        <v>875.6</v>
       </c>
       <c r="F22" t="n">
         <v>5</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3259</v>
+        <v>0.3177</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3503</v>
+        <v>0.3414</v>
       </c>
       <c r="I22" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -1255,19 +1255,19 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>25952.58</v>
+        <v>27102.62</v>
       </c>
       <c r="E23" t="n">
-        <v>865.1</v>
+        <v>903.4</v>
       </c>
       <c r="F23" t="n">
         <v>5</v>
       </c>
       <c r="G23" t="n">
-        <v>0.317</v>
+        <v>0.3278</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3408</v>
+        <v>0.3522</v>
       </c>
       <c r="I23" t="n">
         <v>92</v>
@@ -1291,22 +1291,22 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16174.33</v>
+        <v>16130.35</v>
       </c>
       <c r="E24" t="n">
-        <v>449.3</v>
+        <v>448.1</v>
       </c>
       <c r="F24" t="n">
         <v>6</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1976</v>
+        <v>0.1951</v>
       </c>
       <c r="H24" t="n">
-        <v>0.177</v>
+        <v>0.1747</v>
       </c>
       <c r="I24" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13058.53</v>
+        <v>13176.2</v>
       </c>
       <c r="E25" t="n">
-        <v>334.8</v>
+        <v>337.9</v>
       </c>
       <c r="F25" t="n">
         <v>6.5</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1595</v>
+        <v>0.1594</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1319</v>
+        <v>0.1317</v>
       </c>
       <c r="I25" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1363,22 +1363,22 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>25544.84</v>
+        <v>26785.43</v>
       </c>
       <c r="E26" t="n">
-        <v>851.5</v>
+        <v>892.8</v>
       </c>
       <c r="F26" t="n">
         <v>5</v>
       </c>
       <c r="G26" t="n">
-        <v>0.313</v>
+        <v>0.3316</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3367</v>
+        <v>0.3561</v>
       </c>
       <c r="I26" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -1399,22 +1399,22 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>26876.71</v>
+        <v>25639.16</v>
       </c>
       <c r="E27" t="n">
-        <v>895.9</v>
+        <v>854.6</v>
       </c>
       <c r="F27" t="n">
         <v>5</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3293</v>
+        <v>0.3174</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3543</v>
+        <v>0.3408</v>
       </c>
       <c r="I27" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -1435,19 +1435,19 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15348.27</v>
+        <v>15494.86</v>
       </c>
       <c r="E28" t="n">
-        <v>426.3</v>
+        <v>430.4</v>
       </c>
       <c r="F28" t="n">
         <v>6</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1881</v>
+        <v>0.1918</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1686</v>
+        <v>0.1717</v>
       </c>
       <c r="I28" t="n">
         <v>91</v>
@@ -1471,22 +1471,22 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13843.53</v>
+        <v>12849.8</v>
       </c>
       <c r="E29" t="n">
-        <v>355</v>
+        <v>329.5</v>
       </c>
       <c r="F29" t="n">
         <v>6.5</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1696</v>
+        <v>0.1591</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1404</v>
+        <v>0.1314</v>
       </c>
       <c r="I29" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1507,19 +1507,19 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>26996.9</v>
+        <v>26313.23</v>
       </c>
       <c r="E30" t="n">
-        <v>899.9</v>
+        <v>877.1</v>
       </c>
       <c r="F30" t="n">
         <v>5</v>
       </c>
       <c r="G30" t="n">
-        <v>0.323</v>
+        <v>0.3239</v>
       </c>
       <c r="H30" t="n">
-        <v>0.347</v>
+        <v>0.3477</v>
       </c>
       <c r="I30" t="n">
         <v>91</v>
@@ -1543,22 +1543,22 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>27023.28</v>
+        <v>26545.18</v>
       </c>
       <c r="E31" t="n">
-        <v>900.8</v>
+        <v>884.8</v>
       </c>
       <c r="F31" t="n">
         <v>5</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3233</v>
+        <v>0.3267</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3473</v>
+        <v>0.3508</v>
       </c>
       <c r="I31" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
@@ -1579,22 +1579,22 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>16442.49</v>
+        <v>15418.51</v>
       </c>
       <c r="E32" t="n">
-        <v>456.7</v>
+        <v>428.3</v>
       </c>
       <c r="F32" t="n">
         <v>6</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1967</v>
+        <v>0.1898</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1761</v>
+        <v>0.1698</v>
       </c>
       <c r="I32" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1615,22 +1615,22 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13113.08</v>
+        <v>12964.49</v>
       </c>
       <c r="E33" t="n">
-        <v>336.2</v>
+        <v>332.4</v>
       </c>
       <c r="F33" t="n">
         <v>6.5</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1569</v>
+        <v>0.1596</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1296</v>
+        <v>0.1318</v>
       </c>
       <c r="I33" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1651,22 +1651,22 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10253</v>
+        <v>10309.93</v>
       </c>
       <c r="E34" t="n">
-        <v>273.4</v>
+        <v>274.9</v>
       </c>
       <c r="F34" t="n">
         <v>6.25</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2037</v>
+        <v>0.2051</v>
       </c>
       <c r="H34" t="n">
-        <v>0.2031</v>
+        <v>0.2044</v>
       </c>
       <c r="I34" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10259.1</v>
+        <v>10243.72</v>
       </c>
       <c r="E35" t="n">
-        <v>273.6</v>
+        <v>273.2</v>
       </c>
       <c r="F35" t="n">
         <v>6.25</v>
@@ -1699,10 +1699,10 @@
         <v>0.2038</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2032</v>
+        <v>0.2031</v>
       </c>
       <c r="I35" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -1723,22 +1723,22 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>16155.92</v>
+        <v>16276.73</v>
       </c>
       <c r="E36" t="n">
-        <v>448.8</v>
+        <v>452.1</v>
       </c>
       <c r="F36" t="n">
         <v>6</v>
       </c>
       <c r="G36" t="n">
-        <v>0.3209</v>
+        <v>0.3238</v>
       </c>
       <c r="H36" t="n">
-        <v>0.3333</v>
+        <v>0.3362</v>
       </c>
       <c r="I36" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -1759,19 +1759,19 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13674.71</v>
+        <v>13435.91</v>
       </c>
       <c r="E37" t="n">
-        <v>350.6</v>
+        <v>344.5</v>
       </c>
       <c r="F37" t="n">
         <v>6.5</v>
       </c>
       <c r="G37" t="n">
-        <v>0.2716</v>
+        <v>0.2673</v>
       </c>
       <c r="H37" t="n">
-        <v>0.2604</v>
+        <v>0.2562</v>
       </c>
       <c r="I37" t="n">
         <v>90</v>
@@ -1795,22 +1795,22 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>10551.89</v>
+        <v>10488.38</v>
       </c>
       <c r="E38" t="n">
-        <v>281.4</v>
+        <v>279.7</v>
       </c>
       <c r="F38" t="n">
         <v>6.25</v>
       </c>
       <c r="G38" t="n">
-        <v>0.2138</v>
+        <v>0.2118</v>
       </c>
       <c r="H38" t="n">
-        <v>0.2132</v>
+        <v>0.2113</v>
       </c>
       <c r="I38" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -1831,22 +1831,22 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>9889.700000000001</v>
+        <v>9982.889999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>263.7</v>
+        <v>266.2</v>
       </c>
       <c r="F39" t="n">
         <v>6.25</v>
       </c>
       <c r="G39" t="n">
-        <v>0.2004</v>
+        <v>0.2016</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1998</v>
+        <v>0.2011</v>
       </c>
       <c r="I39" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -1867,22 +1867,22 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>15703.77</v>
+        <v>15627.56</v>
       </c>
       <c r="E40" t="n">
-        <v>436.2</v>
+        <v>434.1</v>
       </c>
       <c r="F40" t="n">
         <v>6</v>
       </c>
       <c r="G40" t="n">
-        <v>0.3182</v>
+        <v>0.3156</v>
       </c>
       <c r="H40" t="n">
-        <v>0.3305</v>
+        <v>0.3279</v>
       </c>
       <c r="I40" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -1903,19 +1903,19 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13199.78</v>
+        <v>13411.27</v>
       </c>
       <c r="E41" t="n">
-        <v>338.5</v>
+        <v>343.9</v>
       </c>
       <c r="F41" t="n">
         <v>6.5</v>
       </c>
       <c r="G41" t="n">
-        <v>0.2675</v>
+        <v>0.2709</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2564</v>
+        <v>0.2598</v>
       </c>
       <c r="I41" t="n">
         <v>91</v>
@@ -1939,22 +1939,22 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>10064.25</v>
+        <v>10334.08</v>
       </c>
       <c r="E42" t="n">
-        <v>268.4</v>
+        <v>275.6</v>
       </c>
       <c r="F42" t="n">
         <v>6.25</v>
       </c>
       <c r="G42" t="n">
-        <v>0.1992</v>
+        <v>0.2052</v>
       </c>
       <c r="H42" t="n">
-        <v>0.1985</v>
+        <v>0.2045</v>
       </c>
       <c r="I42" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -1975,22 +1975,22 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>10525.07</v>
+        <v>10123.61</v>
       </c>
       <c r="E43" t="n">
-        <v>280.7</v>
+        <v>270</v>
       </c>
       <c r="F43" t="n">
         <v>6.25</v>
       </c>
       <c r="G43" t="n">
-        <v>0.2083</v>
+        <v>0.2011</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2076</v>
+        <v>0.2003</v>
       </c>
       <c r="I43" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2011,22 +2011,22 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>16540.24</v>
+        <v>16606.97</v>
       </c>
       <c r="E44" t="n">
-        <v>459.5</v>
+        <v>461.3</v>
       </c>
       <c r="F44" t="n">
         <v>6</v>
       </c>
       <c r="G44" t="n">
-        <v>0.3273</v>
+        <v>0.3298</v>
       </c>
       <c r="H44" t="n">
-        <v>0.3398</v>
+        <v>0.3423</v>
       </c>
       <c r="I44" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2047,22 +2047,22 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13399.42</v>
+        <v>13286.33</v>
       </c>
       <c r="E45" t="n">
-        <v>343.6</v>
+        <v>340.7</v>
       </c>
       <c r="F45" t="n">
         <v>6.5</v>
       </c>
       <c r="G45" t="n">
-        <v>0.2652</v>
+        <v>0.2639</v>
       </c>
       <c r="H45" t="n">
-        <v>0.2541</v>
+        <v>0.2528</v>
       </c>
       <c r="I45" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2083,19 +2083,19 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10555.88</v>
+        <v>9923.6</v>
       </c>
       <c r="E46" t="n">
-        <v>281.5</v>
+        <v>264.6</v>
       </c>
       <c r="F46" t="n">
         <v>6.25</v>
       </c>
       <c r="G46" t="n">
-        <v>0.2084</v>
+        <v>0.1995</v>
       </c>
       <c r="H46" t="n">
-        <v>0.2078</v>
+        <v>0.199</v>
       </c>
       <c r="I46" t="n">
         <v>90</v>
@@ -2119,22 +2119,22 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10149.33</v>
+        <v>10200.85</v>
       </c>
       <c r="E47" t="n">
-        <v>270.6</v>
+        <v>272</v>
       </c>
       <c r="F47" t="n">
         <v>6.25</v>
       </c>
       <c r="G47" t="n">
-        <v>0.2004</v>
+        <v>0.2051</v>
       </c>
       <c r="H47" t="n">
-        <v>0.1998</v>
+        <v>0.2046</v>
       </c>
       <c r="I47" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2155,22 +2155,22 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>16048.78</v>
+        <v>15749.4</v>
       </c>
       <c r="E48" t="n">
-        <v>445.8</v>
+        <v>437.5</v>
       </c>
       <c r="F48" t="n">
         <v>6</v>
       </c>
       <c r="G48" t="n">
-        <v>0.3168</v>
+        <v>0.3166</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3292</v>
+        <v>0.329</v>
       </c>
       <c r="I48" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -2191,22 +2191,22 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13900.82</v>
+        <v>13864.38</v>
       </c>
       <c r="E49" t="n">
-        <v>356.4</v>
+        <v>355.5</v>
       </c>
       <c r="F49" t="n">
         <v>6.5</v>
       </c>
       <c r="G49" t="n">
-        <v>0.2744</v>
+        <v>0.2787</v>
       </c>
       <c r="H49" t="n">
-        <v>0.2632</v>
+        <v>0.2674</v>
       </c>
       <c r="I49" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2227,22 +2227,22 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11881.31</v>
+        <v>11867.34</v>
       </c>
       <c r="E50" t="n">
-        <v>316.8</v>
+        <v>316.5</v>
       </c>
       <c r="F50" t="n">
         <v>6.25</v>
       </c>
       <c r="G50" t="n">
-        <v>0.2161</v>
+        <v>0.2225</v>
       </c>
       <c r="H50" t="n">
-        <v>0.2156</v>
+        <v>0.2221</v>
       </c>
       <c r="I50" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12467.17</v>
+        <v>11604.14</v>
       </c>
       <c r="E51" t="n">
-        <v>332.5</v>
+        <v>309.4</v>
       </c>
       <c r="F51" t="n">
         <v>6.25</v>
       </c>
       <c r="G51" t="n">
-        <v>0.2268</v>
+        <v>0.2176</v>
       </c>
       <c r="H51" t="n">
-        <v>0.2262</v>
+        <v>0.2171</v>
       </c>
       <c r="I51" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2299,22 +2299,22 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>16482.22</v>
+        <v>15704.94</v>
       </c>
       <c r="E52" t="n">
-        <v>457.8</v>
+        <v>436.2</v>
       </c>
       <c r="F52" t="n">
         <v>6</v>
       </c>
       <c r="G52" t="n">
-        <v>0.2998</v>
+        <v>0.2945</v>
       </c>
       <c r="H52" t="n">
-        <v>0.3115</v>
+        <v>0.3061</v>
       </c>
       <c r="I52" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -2335,22 +2335,22 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>14142.7</v>
+        <v>14154.39</v>
       </c>
       <c r="E53" t="n">
-        <v>362.6</v>
+        <v>362.9</v>
       </c>
       <c r="F53" t="n">
         <v>6.5</v>
       </c>
       <c r="G53" t="n">
-        <v>0.2573</v>
+        <v>0.2654</v>
       </c>
       <c r="H53" t="n">
-        <v>0.2467</v>
+        <v>0.2547</v>
       </c>
       <c r="I53" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2371,22 +2371,22 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12084.73</v>
+        <v>12267.6</v>
       </c>
       <c r="E54" t="n">
-        <v>322.3</v>
+        <v>327.1</v>
       </c>
       <c r="F54" t="n">
         <v>6.25</v>
       </c>
       <c r="G54" t="n">
-        <v>0.2262</v>
+        <v>0.2271</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2256</v>
+        <v>0.2265</v>
       </c>
       <c r="I54" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2407,22 +2407,22 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12178.65</v>
+        <v>12208.21</v>
       </c>
       <c r="E55" t="n">
-        <v>324.8</v>
+        <v>325.6</v>
       </c>
       <c r="F55" t="n">
         <v>6.25</v>
       </c>
       <c r="G55" t="n">
-        <v>0.2279</v>
+        <v>0.226</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2274</v>
+        <v>0.2254</v>
       </c>
       <c r="I55" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -2443,19 +2443,19 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>15567.94</v>
+        <v>16134.37</v>
       </c>
       <c r="E56" t="n">
-        <v>432.4</v>
+        <v>448.2</v>
       </c>
       <c r="F56" t="n">
         <v>6</v>
       </c>
       <c r="G56" t="n">
-        <v>0.2914</v>
+        <v>0.2987</v>
       </c>
       <c r="H56" t="n">
-        <v>0.3028</v>
+        <v>0.3103</v>
       </c>
       <c r="I56" t="n">
         <v>90</v>
@@ -2479,22 +2479,22 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13600.12</v>
+        <v>13401.29</v>
       </c>
       <c r="E57" t="n">
-        <v>348.7</v>
+        <v>343.6</v>
       </c>
       <c r="F57" t="n">
         <v>6.5</v>
       </c>
       <c r="G57" t="n">
-        <v>0.2545</v>
+        <v>0.2481</v>
       </c>
       <c r="H57" t="n">
-        <v>0.2442</v>
+        <v>0.2379</v>
       </c>
       <c r="I57" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -2515,22 +2515,22 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13286.08</v>
+        <v>13290.43</v>
       </c>
       <c r="E58" t="n">
-        <v>354.3</v>
+        <v>354.4</v>
       </c>
       <c r="F58" t="n">
         <v>6.25</v>
       </c>
       <c r="G58" t="n">
-        <v>0.233</v>
+        <v>0.2344</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2322</v>
+        <v>0.2339</v>
       </c>
       <c r="I58" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -2551,22 +2551,22 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>13951.92</v>
+        <v>13585.56</v>
       </c>
       <c r="E59" t="n">
-        <v>372.1</v>
+        <v>362.3</v>
       </c>
       <c r="F59" t="n">
         <v>6.25</v>
       </c>
       <c r="G59" t="n">
-        <v>0.2447</v>
+        <v>0.2396</v>
       </c>
       <c r="H59" t="n">
-        <v>0.2439</v>
+        <v>0.2391</v>
       </c>
       <c r="I59" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -2587,22 +2587,22 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>16564.56</v>
+        <v>15781.1</v>
       </c>
       <c r="E60" t="n">
-        <v>460.1</v>
+        <v>438.4</v>
       </c>
       <c r="F60" t="n">
         <v>6</v>
       </c>
       <c r="G60" t="n">
-        <v>0.2905</v>
+        <v>0.2783</v>
       </c>
       <c r="H60" t="n">
-        <v>0.3016</v>
+        <v>0.2893</v>
       </c>
       <c r="I60" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -2623,22 +2623,22 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13224.76</v>
+        <v>14039.42</v>
       </c>
       <c r="E61" t="n">
-        <v>339.1</v>
+        <v>360</v>
       </c>
       <c r="F61" t="n">
         <v>6.5</v>
       </c>
       <c r="G61" t="n">
-        <v>0.2319</v>
+        <v>0.2476</v>
       </c>
       <c r="H61" t="n">
-        <v>0.2223</v>
+        <v>0.2376</v>
       </c>
       <c r="I61" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -2659,19 +2659,19 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13074.93</v>
+        <v>13590.83</v>
       </c>
       <c r="E62" t="n">
-        <v>348.7</v>
+        <v>362.4</v>
       </c>
       <c r="F62" t="n">
         <v>6.25</v>
       </c>
       <c r="G62" t="n">
-        <v>0.228</v>
+        <v>0.2407</v>
       </c>
       <c r="H62" t="n">
-        <v>0.2274</v>
+        <v>0.2401</v>
       </c>
       <c r="I62" t="n">
         <v>88</v>
@@ -2695,22 +2695,22 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>14039.03</v>
+        <v>13661.83</v>
       </c>
       <c r="E63" t="n">
-        <v>374.4</v>
+        <v>364.3</v>
       </c>
       <c r="F63" t="n">
         <v>6.25</v>
       </c>
       <c r="G63" t="n">
-        <v>0.2448</v>
+        <v>0.2419</v>
       </c>
       <c r="H63" t="n">
-        <v>0.2442</v>
+        <v>0.2414</v>
       </c>
       <c r="I63" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>16414.73</v>
+        <v>15661.44</v>
       </c>
       <c r="E64" t="n">
-        <v>456</v>
+        <v>435</v>
       </c>
       <c r="F64" t="n">
         <v>6</v>
       </c>
       <c r="G64" t="n">
-        <v>0.2863</v>
+        <v>0.2773</v>
       </c>
       <c r="H64" t="n">
-        <v>0.2974</v>
+        <v>0.2882</v>
       </c>
       <c r="I64" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -2767,22 +2767,22 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13813.94</v>
+        <v>13558.06</v>
       </c>
       <c r="E65" t="n">
-        <v>354.2</v>
+        <v>347.6</v>
       </c>
       <c r="F65" t="n">
         <v>6.5</v>
       </c>
       <c r="G65" t="n">
-        <v>0.2409</v>
+        <v>0.2401</v>
       </c>
       <c r="H65" t="n">
-        <v>0.231</v>
+        <v>0.2303</v>
       </c>
       <c r="I65" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>

--- a/stella/test_fixtures/pantry_loaded/iri_data.xlsx
+++ b/stella/test_fixtures/pantry_loaded/iri_data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,26 +495,26 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15328.75</v>
+        <v>16750.37</v>
       </c>
       <c r="E2" t="n">
-        <v>408.8</v>
+        <v>2663</v>
       </c>
       <c r="F2" t="n">
-        <v>6.25</v>
+        <v>6.29</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2522</v>
+        <v>0.0725</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2515</v>
+        <v>0.0519</v>
       </c>
       <c r="I2" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -531,26 +531,26 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14926.65</v>
+        <v>17856.52</v>
       </c>
       <c r="E3" t="n">
-        <v>398</v>
+        <v>2838.9</v>
       </c>
       <c r="F3" t="n">
-        <v>6.25</v>
+        <v>6.29</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2456</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2449</v>
+        <v>0.0553</v>
       </c>
       <c r="I3" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -562,31 +562,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>Summit Foods</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16664.74</v>
+        <v>17803.38</v>
       </c>
       <c r="E4" t="n">
-        <v>462.9</v>
+        <v>2830.4</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>6.29</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2742</v>
+        <v>0.0771</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2848</v>
+        <v>0.0552</v>
       </c>
       <c r="I4" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -598,31 +598,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>PC-Deep Clean 6oz</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13865.53</v>
+        <v>16445.81</v>
       </c>
       <c r="E5" t="n">
-        <v>355.5</v>
+        <v>2534</v>
       </c>
       <c r="F5" t="n">
-        <v>6.5</v>
+        <v>6.49</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2281</v>
+        <v>0.0712</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2188</v>
+        <v>0.0494</v>
       </c>
       <c r="I5" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -630,35 +630,35 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45668</v>
+        <v>45661</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>PC-Gentle 4oz</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14553.74</v>
+        <v>15548.57</v>
       </c>
       <c r="E6" t="n">
-        <v>388.1</v>
+        <v>2395.8</v>
       </c>
       <c r="F6" t="n">
-        <v>6.25</v>
+        <v>6.49</v>
       </c>
       <c r="G6" t="n">
-        <v>0.244</v>
+        <v>0.0673</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2435</v>
+        <v>0.0467</v>
       </c>
       <c r="I6" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -666,35 +666,35 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45668</v>
+        <v>45661</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>PC-Total 6oz</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14940.46</v>
+        <v>15682.89</v>
       </c>
       <c r="E7" t="n">
-        <v>398.4</v>
+        <v>2416.5</v>
       </c>
       <c r="F7" t="n">
-        <v>6.25</v>
+        <v>6.49</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2505</v>
+        <v>0.0679</v>
       </c>
       <c r="H7" t="n">
-        <v>0.25</v>
+        <v>0.0471</v>
       </c>
       <c r="I7" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -702,35 +702,35 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45668</v>
+        <v>45661</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>CP-Fresh 6oz</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16032.55</v>
+        <v>16838.37</v>
       </c>
       <c r="E8" t="n">
-        <v>445.3</v>
+        <v>3925</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>4.29</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2688</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2794</v>
+        <v>0.0765</v>
       </c>
       <c r="I8" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -738,32 +738,32 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45668</v>
+        <v>45661</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>CP-Cavity Shield 4oz</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14116.03</v>
+        <v>15886.42</v>
       </c>
       <c r="E9" t="n">
-        <v>361.9</v>
+        <v>3703.1</v>
       </c>
       <c r="F9" t="n">
-        <v>6.5</v>
+        <v>4.29</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2367</v>
+        <v>0.0688</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2271</v>
+        <v>0.0722</v>
       </c>
       <c r="I9" t="n">
         <v>89</v>
@@ -774,35 +774,35 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45675</v>
+        <v>45661</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>CP-Mint Blast 6oz</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15065.5</v>
+        <v>17149.71</v>
       </c>
       <c r="E10" t="n">
-        <v>401.7</v>
+        <v>3997.6</v>
       </c>
       <c r="F10" t="n">
-        <v>6.25</v>
+        <v>4.29</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2513</v>
+        <v>0.0742</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2506</v>
+        <v>0.0779</v>
       </c>
       <c r="I10" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -810,35 +810,35 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45675</v>
+        <v>45661</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>DS-Original 6oz</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14476.58</v>
+        <v>14478.04</v>
       </c>
       <c r="E11" t="n">
-        <v>386</v>
+        <v>3539.9</v>
       </c>
       <c r="F11" t="n">
-        <v>6.25</v>
+        <v>4.09</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2414</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2408</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -846,35 +846,35 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45675</v>
+        <v>45661</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>DS-Whitening 4oz</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16624.61</v>
+        <v>14878.29</v>
       </c>
       <c r="E12" t="n">
-        <v>461.8</v>
+        <v>3637.7</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>4.09</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2773</v>
+        <v>0.0644</v>
       </c>
       <c r="H12" t="n">
-        <v>0.288</v>
+        <v>0.0709</v>
       </c>
       <c r="I12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -882,35 +882,35 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45675</v>
+        <v>45661</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>DS-Cool Mint 6oz</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13793.78</v>
+        <v>15075.11</v>
       </c>
       <c r="E13" t="n">
-        <v>353.7</v>
+        <v>3685.8</v>
       </c>
       <c r="F13" t="n">
-        <v>6.5</v>
+        <v>4.09</v>
       </c>
       <c r="G13" t="n">
-        <v>0.23</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2206</v>
+        <v>0.0718</v>
       </c>
       <c r="I13" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -918,35 +918,35 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45682</v>
+        <v>45661</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SC-Basic Clean 6oz</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15334.06</v>
+        <v>12172.52</v>
       </c>
       <c r="E14" t="n">
-        <v>408.9</v>
+        <v>4362.9</v>
       </c>
       <c r="F14" t="n">
-        <v>6.25</v>
+        <v>2.79</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2587</v>
+        <v>0.0527</v>
       </c>
       <c r="H14" t="n">
-        <v>0.258</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -954,35 +954,35 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45682</v>
+        <v>45661</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SC-Whitening 4oz</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14633.57</v>
+        <v>12098.37</v>
       </c>
       <c r="E15" t="n">
-        <v>390.2</v>
+        <v>4336.3</v>
       </c>
       <c r="F15" t="n">
-        <v>6.25</v>
+        <v>2.79</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2469</v>
+        <v>0.0524</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2462</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -990,35 +990,35 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45682</v>
+        <v>45661</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>SC-Fresh 6oz</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16156.87</v>
+        <v>12382.79</v>
       </c>
       <c r="E16" t="n">
-        <v>448.8</v>
+        <v>4438.3</v>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>2.79</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2726</v>
+        <v>0.0536</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2831</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1026,35 +1026,35 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45682</v>
+        <v>45668</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>Summit Foods</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13151.83</v>
+        <v>17648.3</v>
       </c>
       <c r="E17" t="n">
-        <v>337.2</v>
+        <v>2805.8</v>
       </c>
       <c r="F17" t="n">
-        <v>6.5</v>
+        <v>6.29</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2219</v>
+        <v>0.077</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2127</v>
+        <v>0.0552</v>
       </c>
       <c r="I17" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1062,7 +1062,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45689</v>
+        <v>45668</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1071,34 +1071,34 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>26032.14</v>
+        <v>17824.78</v>
       </c>
       <c r="E18" t="n">
-        <v>867.7</v>
+        <v>2833.8</v>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>6.29</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3212</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3453</v>
+        <v>0.0557</v>
       </c>
       <c r="I18" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45689</v>
+        <v>45668</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1107,62 +1107,62 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>26126.41</v>
+        <v>16990.45</v>
       </c>
       <c r="E19" t="n">
-        <v>870.9</v>
+        <v>2701.2</v>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>6.29</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3224</v>
+        <v>0.0741</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3465</v>
+        <v>0.0531</v>
       </c>
       <c r="I19" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45689</v>
+        <v>45668</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>PC-Deep Clean 6oz</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15837.33</v>
+        <v>15679.93</v>
       </c>
       <c r="E20" t="n">
-        <v>439.9</v>
+        <v>2416</v>
       </c>
       <c r="F20" t="n">
-        <v>6</v>
+        <v>6.49</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1954</v>
+        <v>0.0684</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1751</v>
+        <v>0.0475</v>
       </c>
       <c r="I20" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1170,35 +1170,35 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45689</v>
+        <v>45668</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>PC-Gentle 4oz</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13044.68</v>
+        <v>15658.95</v>
       </c>
       <c r="E21" t="n">
-        <v>334.5</v>
+        <v>2412.8</v>
       </c>
       <c r="F21" t="n">
-        <v>6.5</v>
+        <v>6.49</v>
       </c>
       <c r="G21" t="n">
-        <v>0.161</v>
+        <v>0.0683</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1331</v>
+        <v>0.0475</v>
       </c>
       <c r="I21" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1206,107 +1206,107 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45696</v>
+        <v>45668</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>PC-Total 6oz</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>26267.26</v>
+        <v>16091.04</v>
       </c>
       <c r="E22" t="n">
-        <v>875.6</v>
+        <v>2479.4</v>
       </c>
       <c r="F22" t="n">
-        <v>5</v>
+        <v>6.49</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3177</v>
+        <v>0.0702</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3414</v>
+        <v>0.0488</v>
       </c>
       <c r="I22" t="n">
         <v>92</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45696</v>
+        <v>45668</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>CP-Fresh 6oz</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>27102.62</v>
+        <v>16474.77</v>
       </c>
       <c r="E23" t="n">
-        <v>903.4</v>
+        <v>3840.3</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>4.29</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3278</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3522</v>
+        <v>0.0755</v>
       </c>
       <c r="I23" t="n">
         <v>92</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45696</v>
+        <v>45668</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>CP-Cavity Shield 4oz</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16130.35</v>
+        <v>16198.64</v>
       </c>
       <c r="E24" t="n">
-        <v>448.1</v>
+        <v>3775.9</v>
       </c>
       <c r="F24" t="n">
-        <v>6</v>
+        <v>4.29</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1951</v>
+        <v>0.0707</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1747</v>
+        <v>0.0743</v>
       </c>
       <c r="I24" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1314,35 +1314,35 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45696</v>
+        <v>45668</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>CP-Mint Blast 6oz</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13176.2</v>
+        <v>15915.53</v>
       </c>
       <c r="E25" t="n">
-        <v>337.9</v>
+        <v>3709.9</v>
       </c>
       <c r="F25" t="n">
-        <v>6.5</v>
+        <v>4.29</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1594</v>
+        <v>0.0694</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1317</v>
+        <v>0.073</v>
       </c>
       <c r="I25" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1350,107 +1350,107 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45703</v>
+        <v>45668</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>DS-Original 6oz</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>26785.43</v>
+        <v>14600.1</v>
       </c>
       <c r="E26" t="n">
-        <v>892.8</v>
+        <v>3569.7</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>4.09</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3316</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3561</v>
+        <v>0.0702</v>
       </c>
       <c r="I26" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45703</v>
+        <v>45668</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>DS-Whitening 4oz</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>25639.16</v>
+        <v>15159.05</v>
       </c>
       <c r="E27" t="n">
-        <v>854.6</v>
+        <v>3706.4</v>
       </c>
       <c r="F27" t="n">
-        <v>5</v>
+        <v>4.09</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3174</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3408</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45703</v>
+        <v>45668</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>DS-Cool Mint 6oz</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15494.86</v>
+        <v>14800.16</v>
       </c>
       <c r="E28" t="n">
-        <v>430.4</v>
+        <v>3618.6</v>
       </c>
       <c r="F28" t="n">
-        <v>6</v>
+        <v>4.09</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1918</v>
+        <v>0.0646</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1717</v>
+        <v>0.0712</v>
       </c>
       <c r="I28" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1458,35 +1458,35 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45703</v>
+        <v>45668</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>SC-Basic Clean 6oz</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12849.8</v>
+        <v>12271.59</v>
       </c>
       <c r="E29" t="n">
-        <v>329.5</v>
+        <v>4398.4</v>
       </c>
       <c r="F29" t="n">
-        <v>6.5</v>
+        <v>2.79</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1591</v>
+        <v>0.0535</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1314</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1494,107 +1494,107 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45710</v>
+        <v>45668</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SC-Whitening 4oz</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>26313.23</v>
+        <v>11893.67</v>
       </c>
       <c r="E30" t="n">
-        <v>877.1</v>
+        <v>4263</v>
       </c>
       <c r="F30" t="n">
-        <v>5</v>
+        <v>2.79</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3239</v>
+        <v>0.0519</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3477</v>
+        <v>0.0838</v>
       </c>
       <c r="I30" t="n">
         <v>91</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45710</v>
+        <v>45668</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SC-Fresh 6oz</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>26545.18</v>
+        <v>12032.87</v>
       </c>
       <c r="E31" t="n">
-        <v>884.8</v>
+        <v>4312.9</v>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>2.79</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3267</v>
+        <v>0.0525</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3508</v>
+        <v>0.0848</v>
       </c>
       <c r="I31" t="n">
         <v>90</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45710</v>
+        <v>45675</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>Summit Foods</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>15418.51</v>
+        <v>16834.36</v>
       </c>
       <c r="E32" t="n">
-        <v>428.3</v>
+        <v>2676.4</v>
       </c>
       <c r="F32" t="n">
-        <v>6</v>
+        <v>6.29</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1898</v>
+        <v>0.0732</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1698</v>
+        <v>0.0523</v>
       </c>
       <c r="I32" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1602,35 +1602,35 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45710</v>
+        <v>45675</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>Summit Foods</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12964.49</v>
+        <v>16956.05</v>
       </c>
       <c r="E33" t="n">
-        <v>332.4</v>
+        <v>2695.7</v>
       </c>
       <c r="F33" t="n">
-        <v>6.5</v>
+        <v>6.29</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1596</v>
+        <v>0.0737</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1318</v>
+        <v>0.0527</v>
       </c>
       <c r="I33" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1638,7 +1638,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45717</v>
+        <v>45675</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1647,26 +1647,26 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10309.93</v>
+        <v>16827.44</v>
       </c>
       <c r="E34" t="n">
-        <v>274.9</v>
+        <v>2675.3</v>
       </c>
       <c r="F34" t="n">
-        <v>6.25</v>
+        <v>6.29</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2051</v>
+        <v>0.0731</v>
       </c>
       <c r="H34" t="n">
-        <v>0.2044</v>
+        <v>0.0523</v>
       </c>
       <c r="I34" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -1674,35 +1674,35 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45717</v>
+        <v>45675</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>PC-Deep Clean 6oz</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10243.72</v>
+        <v>16514.99</v>
       </c>
       <c r="E35" t="n">
-        <v>273.2</v>
+        <v>2544.7</v>
       </c>
       <c r="F35" t="n">
-        <v>6.25</v>
+        <v>6.49</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2038</v>
+        <v>0.0718</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2031</v>
+        <v>0.0497</v>
       </c>
       <c r="I35" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -1710,35 +1710,35 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45717</v>
+        <v>45675</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>PC-Gentle 4oz</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>16276.73</v>
+        <v>16170.98</v>
       </c>
       <c r="E36" t="n">
-        <v>452.1</v>
+        <v>2491.7</v>
       </c>
       <c r="F36" t="n">
-        <v>6</v>
+        <v>6.49</v>
       </c>
       <c r="G36" t="n">
-        <v>0.3238</v>
+        <v>0.0703</v>
       </c>
       <c r="H36" t="n">
-        <v>0.3362</v>
+        <v>0.0487</v>
       </c>
       <c r="I36" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -1746,32 +1746,32 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45717</v>
+        <v>45675</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>PC-Total 6oz</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13435.91</v>
+        <v>16364.9</v>
       </c>
       <c r="E37" t="n">
-        <v>344.5</v>
+        <v>2521.6</v>
       </c>
       <c r="F37" t="n">
-        <v>6.5</v>
+        <v>6.49</v>
       </c>
       <c r="G37" t="n">
-        <v>0.2673</v>
+        <v>0.0711</v>
       </c>
       <c r="H37" t="n">
-        <v>0.2562</v>
+        <v>0.0493</v>
       </c>
       <c r="I37" t="n">
         <v>90</v>
@@ -1782,32 +1782,32 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45724</v>
+        <v>45675</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>CP-Fresh 6oz</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>10488.38</v>
+        <v>16246.99</v>
       </c>
       <c r="E38" t="n">
-        <v>279.7</v>
+        <v>3787.2</v>
       </c>
       <c r="F38" t="n">
-        <v>6.25</v>
+        <v>4.29</v>
       </c>
       <c r="G38" t="n">
-        <v>0.2118</v>
+        <v>0.0706</v>
       </c>
       <c r="H38" t="n">
-        <v>0.2113</v>
+        <v>0.074</v>
       </c>
       <c r="I38" t="n">
         <v>89</v>
@@ -1818,32 +1818,32 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45724</v>
+        <v>45675</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>CP-Cavity Shield 4oz</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>9982.889999999999</v>
+        <v>16346.38</v>
       </c>
       <c r="E39" t="n">
-        <v>266.2</v>
+        <v>3810.3</v>
       </c>
       <c r="F39" t="n">
-        <v>6.25</v>
+        <v>4.29</v>
       </c>
       <c r="G39" t="n">
-        <v>0.2016</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="H39" t="n">
-        <v>0.2011</v>
+        <v>0.0745</v>
       </c>
       <c r="I39" t="n">
         <v>91</v>
@@ -1854,35 +1854,35 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45724</v>
+        <v>45675</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>CP-Mint Blast 6oz</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>15627.56</v>
+        <v>16390.78</v>
       </c>
       <c r="E40" t="n">
-        <v>434.1</v>
+        <v>3820.7</v>
       </c>
       <c r="F40" t="n">
-        <v>6</v>
+        <v>4.29</v>
       </c>
       <c r="G40" t="n">
-        <v>0.3156</v>
+        <v>0.0712</v>
       </c>
       <c r="H40" t="n">
-        <v>0.3279</v>
+        <v>0.0747</v>
       </c>
       <c r="I40" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -1890,35 +1890,35 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45724</v>
+        <v>45675</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>DS-Original 6oz</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13411.27</v>
+        <v>14925.9</v>
       </c>
       <c r="E41" t="n">
-        <v>343.9</v>
+        <v>3649.4</v>
       </c>
       <c r="F41" t="n">
-        <v>6.5</v>
+        <v>4.09</v>
       </c>
       <c r="G41" t="n">
-        <v>0.2709</v>
+        <v>0.0649</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2598</v>
+        <v>0.0713</v>
       </c>
       <c r="I41" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -1926,35 +1926,35 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45731</v>
+        <v>45675</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>DS-Whitening 4oz</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>10334.08</v>
+        <v>14940.33</v>
       </c>
       <c r="E42" t="n">
-        <v>275.6</v>
+        <v>3652.9</v>
       </c>
       <c r="F42" t="n">
-        <v>6.25</v>
+        <v>4.09</v>
       </c>
       <c r="G42" t="n">
-        <v>0.2052</v>
+        <v>0.0649</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2045</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -1962,35 +1962,35 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45731</v>
+        <v>45675</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>DS-Cool Mint 6oz</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>10123.61</v>
+        <v>14278.8</v>
       </c>
       <c r="E43" t="n">
-        <v>270</v>
+        <v>3491.1</v>
       </c>
       <c r="F43" t="n">
-        <v>6.25</v>
+        <v>4.09</v>
       </c>
       <c r="G43" t="n">
-        <v>0.2011</v>
+        <v>0.0621</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2003</v>
+        <v>0.0682</v>
       </c>
       <c r="I43" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -1998,35 +1998,35 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45731</v>
+        <v>45675</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>SC-Basic Clean 6oz</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>16606.97</v>
+        <v>12709.63</v>
       </c>
       <c r="E44" t="n">
-        <v>461.3</v>
+        <v>4555.4</v>
       </c>
       <c r="F44" t="n">
-        <v>6</v>
+        <v>2.79</v>
       </c>
       <c r="G44" t="n">
-        <v>0.3298</v>
+        <v>0.0552</v>
       </c>
       <c r="H44" t="n">
-        <v>0.3423</v>
+        <v>0.089</v>
       </c>
       <c r="I44" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2034,35 +2034,35 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45731</v>
+        <v>45675</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>SC-Whitening 4oz</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13286.33</v>
+        <v>11903.45</v>
       </c>
       <c r="E45" t="n">
-        <v>340.7</v>
+        <v>4266.5</v>
       </c>
       <c r="F45" t="n">
-        <v>6.5</v>
+        <v>2.79</v>
       </c>
       <c r="G45" t="n">
-        <v>0.2639</v>
+        <v>0.0517</v>
       </c>
       <c r="H45" t="n">
-        <v>0.2528</v>
+        <v>0.0834</v>
       </c>
       <c r="I45" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2070,35 +2070,35 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45738</v>
+        <v>45675</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SC-Fresh 6oz</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>9923.6</v>
+        <v>12665.02</v>
       </c>
       <c r="E46" t="n">
-        <v>264.6</v>
+        <v>4539.4</v>
       </c>
       <c r="F46" t="n">
-        <v>6.25</v>
+        <v>2.79</v>
       </c>
       <c r="G46" t="n">
-        <v>0.1995</v>
+        <v>0.055</v>
       </c>
       <c r="H46" t="n">
-        <v>0.199</v>
+        <v>0.0887</v>
       </c>
       <c r="I46" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2106,7 +2106,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45738</v>
+        <v>45682</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2115,23 +2115,23 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10200.85</v>
+        <v>17906.4</v>
       </c>
       <c r="E47" t="n">
-        <v>272</v>
+        <v>2846.8</v>
       </c>
       <c r="F47" t="n">
-        <v>6.25</v>
+        <v>6.29</v>
       </c>
       <c r="G47" t="n">
-        <v>0.2051</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2046</v>
+        <v>0.0554</v>
       </c>
       <c r="I47" t="n">
         <v>89</v>
@@ -2142,32 +2142,32 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45738</v>
+        <v>45682</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>Summit Foods</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>15749.4</v>
+        <v>17834.4</v>
       </c>
       <c r="E48" t="n">
-        <v>437.5</v>
+        <v>2835.4</v>
       </c>
       <c r="F48" t="n">
-        <v>6</v>
+        <v>6.29</v>
       </c>
       <c r="G48" t="n">
-        <v>0.3166</v>
+        <v>0.077</v>
       </c>
       <c r="H48" t="n">
-        <v>0.329</v>
+        <v>0.0552</v>
       </c>
       <c r="I48" t="n">
         <v>89</v>
@@ -2178,35 +2178,35 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45738</v>
+        <v>45682</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>Summit Foods</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13864.38</v>
+        <v>17681.31</v>
       </c>
       <c r="E49" t="n">
-        <v>355.5</v>
+        <v>2811</v>
       </c>
       <c r="F49" t="n">
-        <v>6.5</v>
+        <v>6.29</v>
       </c>
       <c r="G49" t="n">
-        <v>0.2787</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="H49" t="n">
-        <v>0.2674</v>
+        <v>0.0547</v>
       </c>
       <c r="I49" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2214,35 +2214,35 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45745</v>
+        <v>45682</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>PC-Deep Clean 6oz</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11867.34</v>
+        <v>16085.45</v>
       </c>
       <c r="E50" t="n">
-        <v>316.5</v>
+        <v>2478.5</v>
       </c>
       <c r="F50" t="n">
-        <v>6.25</v>
+        <v>6.49</v>
       </c>
       <c r="G50" t="n">
-        <v>0.2225</v>
+        <v>0.0694</v>
       </c>
       <c r="H50" t="n">
-        <v>0.2221</v>
+        <v>0.0483</v>
       </c>
       <c r="I50" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2250,35 +2250,35 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45745</v>
+        <v>45682</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>PC-Gentle 4oz</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11604.14</v>
+        <v>16050.68</v>
       </c>
       <c r="E51" t="n">
-        <v>309.4</v>
+        <v>2473.1</v>
       </c>
       <c r="F51" t="n">
-        <v>6.25</v>
+        <v>6.49</v>
       </c>
       <c r="G51" t="n">
-        <v>0.2176</v>
+        <v>0.0693</v>
       </c>
       <c r="H51" t="n">
-        <v>0.2171</v>
+        <v>0.0482</v>
       </c>
       <c r="I51" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2286,32 +2286,32 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45745</v>
+        <v>45682</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>PC-Total 6oz</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>15704.94</v>
+        <v>16100.97</v>
       </c>
       <c r="E52" t="n">
-        <v>436.2</v>
+        <v>2480.9</v>
       </c>
       <c r="F52" t="n">
-        <v>6</v>
+        <v>6.49</v>
       </c>
       <c r="G52" t="n">
-        <v>0.2945</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="H52" t="n">
-        <v>0.3061</v>
+        <v>0.0483</v>
       </c>
       <c r="I52" t="n">
         <v>89</v>
@@ -2322,35 +2322,35 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45745</v>
+        <v>45682</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>CP-Fresh 6oz</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>14154.39</v>
+        <v>16564.82</v>
       </c>
       <c r="E53" t="n">
-        <v>362.9</v>
+        <v>3861.3</v>
       </c>
       <c r="F53" t="n">
-        <v>6.5</v>
+        <v>4.29</v>
       </c>
       <c r="G53" t="n">
-        <v>0.2654</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="H53" t="n">
-        <v>0.2547</v>
+        <v>0.0752</v>
       </c>
       <c r="I53" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2358,35 +2358,35 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45752</v>
+        <v>45682</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>CP-Cavity Shield 4oz</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12267.6</v>
+        <v>16430.04</v>
       </c>
       <c r="E54" t="n">
-        <v>327.1</v>
+        <v>3829.8</v>
       </c>
       <c r="F54" t="n">
-        <v>6.25</v>
+        <v>4.29</v>
       </c>
       <c r="G54" t="n">
-        <v>0.2271</v>
+        <v>0.0709</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2265</v>
+        <v>0.0746</v>
       </c>
       <c r="I54" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2394,35 +2394,35 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45752</v>
+        <v>45682</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>CP-Mint Blast 6oz</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12208.21</v>
+        <v>16029.93</v>
       </c>
       <c r="E55" t="n">
-        <v>325.6</v>
+        <v>3736.6</v>
       </c>
       <c r="F55" t="n">
-        <v>6.25</v>
+        <v>4.29</v>
       </c>
       <c r="G55" t="n">
-        <v>0.226</v>
+        <v>0.0692</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2254</v>
+        <v>0.0728</v>
       </c>
       <c r="I55" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -2430,32 +2430,32 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45752</v>
+        <v>45682</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>DS-Original 6oz</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>16134.37</v>
+        <v>14183.87</v>
       </c>
       <c r="E56" t="n">
-        <v>448.2</v>
+        <v>3467.9</v>
       </c>
       <c r="F56" t="n">
-        <v>6</v>
+        <v>4.09</v>
       </c>
       <c r="G56" t="n">
-        <v>0.2987</v>
+        <v>0.0612</v>
       </c>
       <c r="H56" t="n">
-        <v>0.3103</v>
+        <v>0.0675</v>
       </c>
       <c r="I56" t="n">
         <v>90</v>
@@ -2466,35 +2466,35 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45752</v>
+        <v>45682</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>DS-Whitening 4oz</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13401.29</v>
+        <v>15150.76</v>
       </c>
       <c r="E57" t="n">
-        <v>343.6</v>
+        <v>3704.3</v>
       </c>
       <c r="F57" t="n">
-        <v>6.5</v>
+        <v>4.09</v>
       </c>
       <c r="G57" t="n">
-        <v>0.2481</v>
+        <v>0.0654</v>
       </c>
       <c r="H57" t="n">
-        <v>0.2379</v>
+        <v>0.0721</v>
       </c>
       <c r="I57" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -2502,35 +2502,35 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>45759</v>
+        <v>45682</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>DS-Cool Mint 6oz</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13290.43</v>
+        <v>14600.73</v>
       </c>
       <c r="E58" t="n">
-        <v>354.4</v>
+        <v>3569.9</v>
       </c>
       <c r="F58" t="n">
-        <v>6.25</v>
+        <v>4.09</v>
       </c>
       <c r="G58" t="n">
-        <v>0.2344</v>
+        <v>0.063</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2339</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -2538,35 +2538,35 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>45759</v>
+        <v>45682</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SC-Basic Clean 6oz</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>13585.56</v>
+        <v>12721.08</v>
       </c>
       <c r="E59" t="n">
-        <v>362.3</v>
+        <v>4559.5</v>
       </c>
       <c r="F59" t="n">
-        <v>6.25</v>
+        <v>2.79</v>
       </c>
       <c r="G59" t="n">
-        <v>0.2396</v>
+        <v>0.0549</v>
       </c>
       <c r="H59" t="n">
-        <v>0.2391</v>
+        <v>0.0888</v>
       </c>
       <c r="I59" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -2574,35 +2574,35 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>45759</v>
+        <v>45682</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>SC-Whitening 4oz</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>15781.1</v>
+        <v>11945.61</v>
       </c>
       <c r="E60" t="n">
-        <v>438.4</v>
+        <v>4281.6</v>
       </c>
       <c r="F60" t="n">
-        <v>6</v>
+        <v>2.79</v>
       </c>
       <c r="G60" t="n">
-        <v>0.2783</v>
+        <v>0.0516</v>
       </c>
       <c r="H60" t="n">
-        <v>0.2893</v>
+        <v>0.0834</v>
       </c>
       <c r="I60" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -2610,35 +2610,35 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>45759</v>
+        <v>45682</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>SC-Fresh 6oz</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>14039.42</v>
+        <v>12329.44</v>
       </c>
       <c r="E61" t="n">
-        <v>360</v>
+        <v>4419.2</v>
       </c>
       <c r="F61" t="n">
-        <v>6.5</v>
+        <v>2.79</v>
       </c>
       <c r="G61" t="n">
-        <v>0.2476</v>
+        <v>0.0532</v>
       </c>
       <c r="H61" t="n">
-        <v>0.2376</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>45766</v>
+        <v>45689</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -2655,34 +2655,34 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13590.83</v>
+        <v>29645.24</v>
       </c>
       <c r="E62" t="n">
-        <v>362.4</v>
+        <v>5882</v>
       </c>
       <c r="F62" t="n">
-        <v>6.25</v>
+        <v>5.04</v>
       </c>
       <c r="G62" t="n">
-        <v>0.2407</v>
+        <v>0.1114</v>
       </c>
       <c r="H62" t="n">
-        <v>0.2401</v>
+        <v>0.0974</v>
       </c>
       <c r="I62" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>45766</v>
+        <v>45689</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -2691,100 +2691,6436 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13661.83</v>
+        <v>31518.16</v>
       </c>
       <c r="E63" t="n">
-        <v>364.3</v>
+        <v>6253.6</v>
       </c>
       <c r="F63" t="n">
-        <v>6.25</v>
+        <v>5.04</v>
       </c>
       <c r="G63" t="n">
-        <v>0.2419</v>
+        <v>0.1184</v>
       </c>
       <c r="H63" t="n">
-        <v>0.2414</v>
+        <v>0.1035</v>
       </c>
       <c r="I63" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>45766</v>
+        <v>45689</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>Summit Foods</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>15661.44</v>
+        <v>30105.09</v>
       </c>
       <c r="E64" t="n">
-        <v>435</v>
+        <v>5973.2</v>
       </c>
       <c r="F64" t="n">
-        <v>6</v>
+        <v>5.04</v>
       </c>
       <c r="G64" t="n">
-        <v>0.2773</v>
+        <v>0.1131</v>
       </c>
       <c r="H64" t="n">
-        <v>0.2882</v>
+        <v>0.0989</v>
       </c>
       <c r="I64" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>45766</v>
+        <v>45689</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>PC-Deep Clean 6oz</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13558.06</v>
+        <v>14710.4</v>
       </c>
       <c r="E65" t="n">
-        <v>347.6</v>
+        <v>2266.6</v>
       </c>
       <c r="F65" t="n">
-        <v>6.5</v>
+        <v>6.49</v>
       </c>
       <c r="G65" t="n">
-        <v>0.2401</v>
+        <v>0.0553</v>
       </c>
       <c r="H65" t="n">
-        <v>0.2303</v>
+        <v>0.0375</v>
       </c>
       <c r="I65" t="n">
         <v>88</v>
       </c>
       <c r="J65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>15067.22</v>
+      </c>
+      <c r="E66" t="n">
+        <v>2321.6</v>
+      </c>
+      <c r="F66" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.0566</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.0384</v>
+      </c>
+      <c r="I66" t="n">
+        <v>88</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>15619.08</v>
+      </c>
+      <c r="E67" t="n">
+        <v>2406.6</v>
+      </c>
+      <c r="F67" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.0587</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.0398</v>
+      </c>
+      <c r="I67" t="n">
+        <v>91</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>16345.06</v>
+      </c>
+      <c r="E68" t="n">
+        <v>3810</v>
+      </c>
+      <c r="F68" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.0614</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.0631</v>
+      </c>
+      <c r="I68" t="n">
+        <v>89</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>16510.98</v>
+      </c>
+      <c r="E69" t="n">
+        <v>3848.7</v>
+      </c>
+      <c r="F69" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.06370000000000001</v>
+      </c>
+      <c r="I69" t="n">
+        <v>92</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>16566.4</v>
+      </c>
+      <c r="E70" t="n">
+        <v>3861.6</v>
+      </c>
+      <c r="F70" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.0623</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.0639</v>
+      </c>
+      <c r="I70" t="n">
+        <v>89</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>13999.12</v>
+      </c>
+      <c r="E71" t="n">
+        <v>3422.8</v>
+      </c>
+      <c r="F71" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.0526</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.0567</v>
+      </c>
+      <c r="I71" t="n">
+        <v>91</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>14815.12</v>
+      </c>
+      <c r="E72" t="n">
+        <v>3622.3</v>
+      </c>
+      <c r="F72" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.0557</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I72" t="n">
+        <v>90</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>14258.23</v>
+      </c>
+      <c r="E73" t="n">
+        <v>3486.1</v>
+      </c>
+      <c r="F73" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.0536</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.0577</v>
+      </c>
+      <c r="I73" t="n">
+        <v>91</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>12412.52</v>
+      </c>
+      <c r="E74" t="n">
+        <v>4448.9</v>
+      </c>
+      <c r="F74" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.0466</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.0737</v>
+      </c>
+      <c r="I74" t="n">
+        <v>90</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>11787.23</v>
+      </c>
+      <c r="E75" t="n">
+        <v>4224.8</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.0443</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.0699</v>
+      </c>
+      <c r="I75" t="n">
+        <v>90</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>12760.53</v>
+      </c>
+      <c r="E76" t="n">
+        <v>4573.7</v>
+      </c>
+      <c r="F76" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.0757</v>
+      </c>
+      <c r="I76" t="n">
+        <v>92</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>30108.32</v>
+      </c>
+      <c r="E77" t="n">
+        <v>5973.9</v>
+      </c>
+      <c r="F77" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.1129</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.09859999999999999</v>
+      </c>
+      <c r="I77" t="n">
+        <v>89</v>
+      </c>
+      <c r="J77" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>29704.66</v>
+      </c>
+      <c r="E78" t="n">
+        <v>5893.8</v>
+      </c>
+      <c r="F78" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.1114</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.0973</v>
+      </c>
+      <c r="I78" t="n">
+        <v>90</v>
+      </c>
+      <c r="J78" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>30926.44</v>
+      </c>
+      <c r="E79" t="n">
+        <v>6136.2</v>
+      </c>
+      <c r="F79" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.1013</v>
+      </c>
+      <c r="I79" t="n">
+        <v>91</v>
+      </c>
+      <c r="J79" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>15682.01</v>
+      </c>
+      <c r="E80" t="n">
+        <v>2416.3</v>
+      </c>
+      <c r="F80" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.0399</v>
+      </c>
+      <c r="I80" t="n">
+        <v>90</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>14698.37</v>
+      </c>
+      <c r="E81" t="n">
+        <v>2264.8</v>
+      </c>
+      <c r="F81" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.0551</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.0374</v>
+      </c>
+      <c r="I81" t="n">
+        <v>92</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>15198.13</v>
+      </c>
+      <c r="E82" t="n">
+        <v>2341.8</v>
+      </c>
+      <c r="F82" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.0386</v>
+      </c>
+      <c r="I82" t="n">
+        <v>90</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>16694.4</v>
+      </c>
+      <c r="E83" t="n">
+        <v>3891.5</v>
+      </c>
+      <c r="F83" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.0626</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.06419999999999999</v>
+      </c>
+      <c r="I83" t="n">
+        <v>91</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>16509.4</v>
+      </c>
+      <c r="E84" t="n">
+        <v>3848.3</v>
+      </c>
+      <c r="F84" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.0619</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.0635</v>
+      </c>
+      <c r="I84" t="n">
+        <v>89</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>16823.01</v>
+      </c>
+      <c r="E85" t="n">
+        <v>3921.4</v>
+      </c>
+      <c r="F85" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.0631</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0.06469999999999999</v>
+      </c>
+      <c r="I85" t="n">
+        <v>90</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>14365.33</v>
+      </c>
+      <c r="E86" t="n">
+        <v>3512.3</v>
+      </c>
+      <c r="F86" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.0539</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="I86" t="n">
+        <v>90</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>14512.73</v>
+      </c>
+      <c r="E87" t="n">
+        <v>3548.3</v>
+      </c>
+      <c r="F87" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.0544</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0.0586</v>
+      </c>
+      <c r="I87" t="n">
+        <v>88</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>14102.89</v>
+      </c>
+      <c r="E88" t="n">
+        <v>3448.1</v>
+      </c>
+      <c r="F88" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.0529</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0.0569</v>
+      </c>
+      <c r="I88" t="n">
+        <v>88</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>12715.52</v>
+      </c>
+      <c r="E89" t="n">
+        <v>4557.5</v>
+      </c>
+      <c r="F89" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.0477</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0.0752</v>
+      </c>
+      <c r="I89" t="n">
+        <v>91</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>12144.73</v>
+      </c>
+      <c r="E90" t="n">
+        <v>4353</v>
+      </c>
+      <c r="F90" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.0455</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0.0718</v>
+      </c>
+      <c r="I90" t="n">
+        <v>91</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>12510.24</v>
+      </c>
+      <c r="E91" t="n">
+        <v>4484</v>
+      </c>
+      <c r="F91" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0.0469</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="I91" t="n">
+        <v>91</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>29320.54</v>
+      </c>
+      <c r="E92" t="n">
+        <v>5817.6</v>
+      </c>
+      <c r="F92" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0.1115</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0.0975</v>
+      </c>
+      <c r="I92" t="n">
+        <v>91</v>
+      </c>
+      <c r="J92" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>30068.89</v>
+      </c>
+      <c r="E93" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F93" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0.1144</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I93" t="n">
+        <v>93</v>
+      </c>
+      <c r="J93" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>29754.85</v>
+      </c>
+      <c r="E94" t="n">
+        <v>5903.7</v>
+      </c>
+      <c r="F94" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.1132</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="I94" t="n">
+        <v>91</v>
+      </c>
+      <c r="J94" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>15599.17</v>
+      </c>
+      <c r="E95" t="n">
+        <v>2403.6</v>
+      </c>
+      <c r="F95" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0.0593</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0.0403</v>
+      </c>
+      <c r="I95" t="n">
+        <v>89</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>15699.86</v>
+      </c>
+      <c r="E96" t="n">
+        <v>2419.1</v>
+      </c>
+      <c r="F96" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0.0597</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0.0406</v>
+      </c>
+      <c r="I96" t="n">
+        <v>91</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>14950.37</v>
+      </c>
+      <c r="E97" t="n">
+        <v>2303.6</v>
+      </c>
+      <c r="F97" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0.0569</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0.0386</v>
+      </c>
+      <c r="I97" t="n">
+        <v>89</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>16403.52</v>
+      </c>
+      <c r="E98" t="n">
+        <v>3823.7</v>
+      </c>
+      <c r="F98" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0.0624</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0.0641</v>
+      </c>
+      <c r="I98" t="n">
+        <v>92</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>15706.23</v>
+      </c>
+      <c r="E99" t="n">
+        <v>3661.1</v>
+      </c>
+      <c r="F99" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0.0597</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0.0614</v>
+      </c>
+      <c r="I99" t="n">
+        <v>90</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>15895.02</v>
+      </c>
+      <c r="E100" t="n">
+        <v>3705.1</v>
+      </c>
+      <c r="F100" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0.0605</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0.0621</v>
+      </c>
+      <c r="I100" t="n">
+        <v>91</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>13915.09</v>
+      </c>
+      <c r="E101" t="n">
+        <v>3402.2</v>
+      </c>
+      <c r="F101" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0.0529</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="I101" t="n">
+        <v>88</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>14081.16</v>
+      </c>
+      <c r="E102" t="n">
+        <v>3442.8</v>
+      </c>
+      <c r="F102" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0.0536</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0.0577</v>
+      </c>
+      <c r="I102" t="n">
+        <v>90</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>14529.62</v>
+      </c>
+      <c r="E103" t="n">
+        <v>3552.5</v>
+      </c>
+      <c r="F103" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0.0553</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0.0595</v>
+      </c>
+      <c r="I103" t="n">
+        <v>92</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>12678.97</v>
+      </c>
+      <c r="E104" t="n">
+        <v>4544.4</v>
+      </c>
+      <c r="F104" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0.0482</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0.0762</v>
+      </c>
+      <c r="I104" t="n">
+        <v>91</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>11983.85</v>
+      </c>
+      <c r="E105" t="n">
+        <v>4295.3</v>
+      </c>
+      <c r="F105" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0.0456</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="I105" t="n">
+        <v>90</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>12317.32</v>
+      </c>
+      <c r="E106" t="n">
+        <v>4414.8</v>
+      </c>
+      <c r="F106" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0.0469</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="I106" t="n">
+        <v>92</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>31355.5</v>
+      </c>
+      <c r="E107" t="n">
+        <v>6221.3</v>
+      </c>
+      <c r="F107" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0.1167</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="I107" t="n">
+        <v>90</v>
+      </c>
+      <c r="J107" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>30058.32</v>
+      </c>
+      <c r="E108" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F108" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0.1119</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0.0978</v>
+      </c>
+      <c r="I108" t="n">
+        <v>88</v>
+      </c>
+      <c r="J108" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>30600.67</v>
+      </c>
+      <c r="E109" t="n">
+        <v>6071.6</v>
+      </c>
+      <c r="F109" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0.1139</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0.09959999999999999</v>
+      </c>
+      <c r="I109" t="n">
+        <v>91</v>
+      </c>
+      <c r="J109" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>15247.19</v>
+      </c>
+      <c r="E110" t="n">
+        <v>2349.3</v>
+      </c>
+      <c r="F110" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0.0568</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0.0385</v>
+      </c>
+      <c r="I110" t="n">
+        <v>89</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>15421</v>
+      </c>
+      <c r="E111" t="n">
+        <v>2376.1</v>
+      </c>
+      <c r="F111" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0.0574</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="I111" t="n">
+        <v>89</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>15057.1</v>
+      </c>
+      <c r="E112" t="n">
+        <v>2320</v>
+      </c>
+      <c r="F112" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0.0561</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="I112" t="n">
+        <v>90</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>15854.94</v>
+      </c>
+      <c r="E113" t="n">
+        <v>3695.8</v>
+      </c>
+      <c r="F113" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0.0606</v>
+      </c>
+      <c r="I113" t="n">
+        <v>90</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>16720.54</v>
+      </c>
+      <c r="E114" t="n">
+        <v>3897.6</v>
+      </c>
+      <c r="F114" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0.0623</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0.0639</v>
+      </c>
+      <c r="I114" t="n">
+        <v>89</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>16735.04</v>
+      </c>
+      <c r="E115" t="n">
+        <v>3900.9</v>
+      </c>
+      <c r="F115" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0.0623</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="I115" t="n">
+        <v>92</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>14722.88</v>
+      </c>
+      <c r="E116" t="n">
+        <v>3599.7</v>
+      </c>
+      <c r="F116" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0.0548</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="I116" t="n">
+        <v>92</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>14877.5</v>
+      </c>
+      <c r="E117" t="n">
+        <v>3637.5</v>
+      </c>
+      <c r="F117" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.0554</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.0596</v>
+      </c>
+      <c r="I117" t="n">
+        <v>88</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>14610.16</v>
+      </c>
+      <c r="E118" t="n">
+        <v>3572.2</v>
+      </c>
+      <c r="F118" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.0544</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.0586</v>
+      </c>
+      <c r="I118" t="n">
+        <v>88</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>12535.92</v>
+      </c>
+      <c r="E119" t="n">
+        <v>4493.2</v>
+      </c>
+      <c r="F119" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.0467</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.0737</v>
+      </c>
+      <c r="I119" t="n">
+        <v>89</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>12533.88</v>
+      </c>
+      <c r="E120" t="n">
+        <v>4492.4</v>
+      </c>
+      <c r="F120" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.0467</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.0737</v>
+      </c>
+      <c r="I120" t="n">
+        <v>91</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>12256.96</v>
+      </c>
+      <c r="E121" t="n">
+        <v>4393.2</v>
+      </c>
+      <c r="F121" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.0456</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="I121" t="n">
+        <v>92</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>12933.71</v>
+      </c>
+      <c r="E122" t="n">
+        <v>2056.2</v>
+      </c>
+      <c r="F122" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.0594</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.0419</v>
+      </c>
+      <c r="I122" t="n">
+        <v>92</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>13611.39</v>
+      </c>
+      <c r="E123" t="n">
+        <v>2164</v>
+      </c>
+      <c r="F123" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="I123" t="n">
+        <v>91</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>12909.6</v>
+      </c>
+      <c r="E124" t="n">
+        <v>2052.4</v>
+      </c>
+      <c r="F124" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.0593</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.0418</v>
+      </c>
+      <c r="I124" t="n">
+        <v>88</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>15921.48</v>
+      </c>
+      <c r="E125" t="n">
+        <v>2453.2</v>
+      </c>
+      <c r="F125" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.0731</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.0499</v>
+      </c>
+      <c r="I125" t="n">
+        <v>92</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>16703.47</v>
+      </c>
+      <c r="E126" t="n">
+        <v>2573.7</v>
+      </c>
+      <c r="F126" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.0767</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.0524</v>
+      </c>
+      <c r="I126" t="n">
+        <v>88</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>15667.72</v>
+      </c>
+      <c r="E127" t="n">
+        <v>2414.1</v>
+      </c>
+      <c r="F127" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.07190000000000001</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.0491</v>
+      </c>
+      <c r="I127" t="n">
+        <v>90</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>16059.28</v>
+      </c>
+      <c r="E128" t="n">
+        <v>3743.4</v>
+      </c>
+      <c r="F128" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.0737</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.0762</v>
+      </c>
+      <c r="I128" t="n">
+        <v>90</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>16414.49</v>
+      </c>
+      <c r="E129" t="n">
+        <v>3826.2</v>
+      </c>
+      <c r="F129" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.07530000000000001</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.0779</v>
+      </c>
+      <c r="I129" t="n">
+        <v>90</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>16674.62</v>
+      </c>
+      <c r="E130" t="n">
+        <v>3886.9</v>
+      </c>
+      <c r="F130" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.0765</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.0791</v>
+      </c>
+      <c r="I130" t="n">
+        <v>91</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>15128.13</v>
+      </c>
+      <c r="E131" t="n">
+        <v>3698.8</v>
+      </c>
+      <c r="F131" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.0694</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.07530000000000001</v>
+      </c>
+      <c r="I131" t="n">
+        <v>91</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>15184.19</v>
+      </c>
+      <c r="E132" t="n">
+        <v>3712.5</v>
+      </c>
+      <c r="F132" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.0697</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.0756</v>
+      </c>
+      <c r="I132" t="n">
+        <v>92</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>14118.34</v>
+      </c>
+      <c r="E133" t="n">
+        <v>3451.9</v>
+      </c>
+      <c r="F133" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.0648</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.0703</v>
+      </c>
+      <c r="I133" t="n">
+        <v>92</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>11920.48</v>
+      </c>
+      <c r="E134" t="n">
+        <v>4272.6</v>
+      </c>
+      <c r="F134" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.0547</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="I134" t="n">
+        <v>90</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>12561.53</v>
+      </c>
+      <c r="E135" t="n">
+        <v>4502.3</v>
+      </c>
+      <c r="F135" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.0577</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.0916</v>
+      </c>
+      <c r="I135" t="n">
+        <v>88</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>12050.74</v>
+      </c>
+      <c r="E136" t="n">
+        <v>4319.3</v>
+      </c>
+      <c r="F136" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.0553</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.08790000000000001</v>
+      </c>
+      <c r="I136" t="n">
+        <v>91</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>14365.69</v>
+      </c>
+      <c r="E137" t="n">
+        <v>2283.9</v>
+      </c>
+      <c r="F137" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.0458</v>
+      </c>
+      <c r="I137" t="n">
+        <v>92</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>13636.88</v>
+      </c>
+      <c r="E138" t="n">
+        <v>2168</v>
+      </c>
+      <c r="F138" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.0617</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.0435</v>
+      </c>
+      <c r="I138" t="n">
+        <v>88</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>13795.06</v>
+      </c>
+      <c r="E139" t="n">
+        <v>2193.2</v>
+      </c>
+      <c r="F139" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.0624</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="I139" t="n">
+        <v>92</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>15966.09</v>
+      </c>
+      <c r="E140" t="n">
+        <v>2460.1</v>
+      </c>
+      <c r="F140" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.0722</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.0494</v>
+      </c>
+      <c r="I140" t="n">
+        <v>88</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>15486.31</v>
+      </c>
+      <c r="E141" t="n">
+        <v>2386.2</v>
+      </c>
+      <c r="F141" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.0701</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.0479</v>
+      </c>
+      <c r="I141" t="n">
+        <v>88</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>16284.11</v>
+      </c>
+      <c r="E142" t="n">
+        <v>2509.1</v>
+      </c>
+      <c r="F142" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.0737</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.0504</v>
+      </c>
+      <c r="I142" t="n">
+        <v>90</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>16322.71</v>
+      </c>
+      <c r="E143" t="n">
+        <v>3804.8</v>
+      </c>
+      <c r="F143" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.07389999999999999</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.0764</v>
+      </c>
+      <c r="I143" t="n">
+        <v>88</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>16896.33</v>
+      </c>
+      <c r="E144" t="n">
+        <v>3938.5</v>
+      </c>
+      <c r="F144" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0.0765</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="I144" t="n">
+        <v>88</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>16955.34</v>
+      </c>
+      <c r="E145" t="n">
+        <v>3952.3</v>
+      </c>
+      <c r="F145" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0.0767</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0.0793</v>
+      </c>
+      <c r="I145" t="n">
+        <v>88</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>14997.51</v>
+      </c>
+      <c r="E146" t="n">
+        <v>3666.9</v>
+      </c>
+      <c r="F146" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0.0679</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0.0736</v>
+      </c>
+      <c r="I146" t="n">
+        <v>90</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>14524.27</v>
+      </c>
+      <c r="E147" t="n">
+        <v>3551.2</v>
+      </c>
+      <c r="F147" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0.06569999999999999</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0.0713</v>
+      </c>
+      <c r="I147" t="n">
+        <v>91</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>14413</v>
+      </c>
+      <c r="E148" t="n">
+        <v>3524</v>
+      </c>
+      <c r="F148" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0.06519999999999999</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0.0707</v>
+      </c>
+      <c r="I148" t="n">
+        <v>88</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>12520.36</v>
+      </c>
+      <c r="E149" t="n">
+        <v>4487.6</v>
+      </c>
+      <c r="F149" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0.0567</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0.0901</v>
+      </c>
+      <c r="I149" t="n">
+        <v>91</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>12571.99</v>
+      </c>
+      <c r="E150" t="n">
+        <v>4506.1</v>
+      </c>
+      <c r="F150" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0.0569</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0.09039999999999999</v>
+      </c>
+      <c r="I150" t="n">
+        <v>92</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>12267.41</v>
+      </c>
+      <c r="E151" t="n">
+        <v>4396.9</v>
+      </c>
+      <c r="F151" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0.0555</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0.0882</v>
+      </c>
+      <c r="I151" t="n">
+        <v>88</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>14119.42</v>
+      </c>
+      <c r="E152" t="n">
+        <v>2244.7</v>
+      </c>
+      <c r="F152" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0.0635</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="I152" t="n">
+        <v>89</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>14949.29</v>
+      </c>
+      <c r="E153" t="n">
+        <v>2376.7</v>
+      </c>
+      <c r="F153" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0.0672</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0.0477</v>
+      </c>
+      <c r="I153" t="n">
+        <v>91</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>14905.5</v>
+      </c>
+      <c r="E154" t="n">
+        <v>2369.7</v>
+      </c>
+      <c r="F154" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0.0476</v>
+      </c>
+      <c r="I154" t="n">
+        <v>88</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>16112.79</v>
+      </c>
+      <c r="E155" t="n">
+        <v>2482.7</v>
+      </c>
+      <c r="F155" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0.0498</v>
+      </c>
+      <c r="I155" t="n">
+        <v>88</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>16472.93</v>
+      </c>
+      <c r="E156" t="n">
+        <v>2538.2</v>
+      </c>
+      <c r="F156" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0.0741</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0.0509</v>
+      </c>
+      <c r="I156" t="n">
+        <v>88</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>15539.43</v>
+      </c>
+      <c r="E157" t="n">
+        <v>2394.4</v>
+      </c>
+      <c r="F157" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0.0699</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="I157" t="n">
+        <v>88</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>16377.08</v>
+      </c>
+      <c r="E158" t="n">
+        <v>3817.5</v>
+      </c>
+      <c r="F158" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0.0737</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0.0766</v>
+      </c>
+      <c r="I158" t="n">
+        <v>92</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>16830.71</v>
+      </c>
+      <c r="E159" t="n">
+        <v>3923.2</v>
+      </c>
+      <c r="F159" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0.0757</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0.07870000000000001</v>
+      </c>
+      <c r="I159" t="n">
+        <v>90</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>16196.02</v>
+      </c>
+      <c r="E160" t="n">
+        <v>3775.3</v>
+      </c>
+      <c r="F160" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0.0728</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0.07580000000000001</v>
+      </c>
+      <c r="I160" t="n">
+        <v>92</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>14916.91</v>
+      </c>
+      <c r="E161" t="n">
+        <v>3647.2</v>
+      </c>
+      <c r="F161" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0.06710000000000001</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0.0732</v>
+      </c>
+      <c r="I161" t="n">
+        <v>88</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>14626.64</v>
+      </c>
+      <c r="E162" t="n">
+        <v>3576.2</v>
+      </c>
+      <c r="F162" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0.0658</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0.0718</v>
+      </c>
+      <c r="I162" t="n">
+        <v>91</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>14914.5</v>
+      </c>
+      <c r="E163" t="n">
+        <v>3646.6</v>
+      </c>
+      <c r="F163" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G163" t="n">
+        <v>0.06710000000000001</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0.0732</v>
+      </c>
+      <c r="I163" t="n">
+        <v>90</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>12241.31</v>
+      </c>
+      <c r="E164" t="n">
+        <v>4387.6</v>
+      </c>
+      <c r="F164" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0.0551</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="I164" t="n">
+        <v>89</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>12146.27</v>
+      </c>
+      <c r="E165" t="n">
+        <v>4353.5</v>
+      </c>
+      <c r="F165" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0.0546</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0.08740000000000001</v>
+      </c>
+      <c r="I165" t="n">
+        <v>92</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>12000.22</v>
+      </c>
+      <c r="E166" t="n">
+        <v>4301.2</v>
+      </c>
+      <c r="F166" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G166" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0.0863</v>
+      </c>
+      <c r="I166" t="n">
+        <v>92</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>15497.71</v>
+      </c>
+      <c r="E167" t="n">
+        <v>2463.9</v>
+      </c>
+      <c r="F167" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G167" t="n">
+        <v>0.0694</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0.0493</v>
+      </c>
+      <c r="I167" t="n">
+        <v>90</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>14678.38</v>
+      </c>
+      <c r="E168" t="n">
+        <v>2333.6</v>
+      </c>
+      <c r="F168" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G168" t="n">
+        <v>0.0658</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0.0467</v>
+      </c>
+      <c r="I168" t="n">
+        <v>91</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>14712.69</v>
+      </c>
+      <c r="E169" t="n">
+        <v>2339.1</v>
+      </c>
+      <c r="F169" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0.0659</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0.0468</v>
+      </c>
+      <c r="I169" t="n">
+        <v>92</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>16263.31</v>
+      </c>
+      <c r="E170" t="n">
+        <v>2505.9</v>
+      </c>
+      <c r="F170" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0.07290000000000001</v>
+      </c>
+      <c r="H170" t="n">
+        <v>0.0502</v>
+      </c>
+      <c r="I170" t="n">
+        <v>90</v>
+      </c>
+      <c r="J170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>15791.72</v>
+      </c>
+      <c r="E171" t="n">
+        <v>2433.2</v>
+      </c>
+      <c r="F171" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0.0708</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0.0487</v>
+      </c>
+      <c r="I171" t="n">
+        <v>89</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>16364.38</v>
+      </c>
+      <c r="E172" t="n">
+        <v>2521.5</v>
+      </c>
+      <c r="F172" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0.0733</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0.0505</v>
+      </c>
+      <c r="I172" t="n">
+        <v>89</v>
+      </c>
+      <c r="J172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>16604.26</v>
+      </c>
+      <c r="E173" t="n">
+        <v>3870.5</v>
+      </c>
+      <c r="F173" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0.07439999999999999</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0.0775</v>
+      </c>
+      <c r="I173" t="n">
+        <v>90</v>
+      </c>
+      <c r="J173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>16583.77</v>
+      </c>
+      <c r="E174" t="n">
+        <v>3865.7</v>
+      </c>
+      <c r="F174" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0.0743</v>
+      </c>
+      <c r="H174" t="n">
+        <v>0.0774</v>
+      </c>
+      <c r="I174" t="n">
+        <v>89</v>
+      </c>
+      <c r="J174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>16950.62</v>
+      </c>
+      <c r="E175" t="n">
+        <v>3951.2</v>
+      </c>
+      <c r="F175" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="H175" t="n">
+        <v>0.0791</v>
+      </c>
+      <c r="I175" t="n">
+        <v>90</v>
+      </c>
+      <c r="J175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>14868.02</v>
+      </c>
+      <c r="E176" t="n">
+        <v>3635.2</v>
+      </c>
+      <c r="F176" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G176" t="n">
+        <v>0.06660000000000001</v>
+      </c>
+      <c r="H176" t="n">
+        <v>0.0728</v>
+      </c>
+      <c r="I176" t="n">
+        <v>91</v>
+      </c>
+      <c r="J176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>14067.97</v>
+      </c>
+      <c r="E177" t="n">
+        <v>3439.6</v>
+      </c>
+      <c r="F177" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="H177" t="n">
+        <v>0.0689</v>
+      </c>
+      <c r="I177" t="n">
+        <v>88</v>
+      </c>
+      <c r="J177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>14094.73</v>
+      </c>
+      <c r="E178" t="n">
+        <v>3446.1</v>
+      </c>
+      <c r="F178" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G178" t="n">
+        <v>0.06320000000000001</v>
+      </c>
+      <c r="H178" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="I178" t="n">
+        <v>88</v>
+      </c>
+      <c r="J178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>12375.74</v>
+      </c>
+      <c r="E179" t="n">
+        <v>4435.7</v>
+      </c>
+      <c r="F179" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0.0555</v>
+      </c>
+      <c r="H179" t="n">
+        <v>0.0888</v>
+      </c>
+      <c r="I179" t="n">
+        <v>89</v>
+      </c>
+      <c r="J179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>12262.44</v>
+      </c>
+      <c r="E180" t="n">
+        <v>4395.1</v>
+      </c>
+      <c r="F180" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G180" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="H180" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="I180" t="n">
+        <v>92</v>
+      </c>
+      <c r="J180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>12040.48</v>
+      </c>
+      <c r="E181" t="n">
+        <v>4315.6</v>
+      </c>
+      <c r="F181" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G181" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="H181" t="n">
+        <v>0.0864</v>
+      </c>
+      <c r="I181" t="n">
+        <v>91</v>
+      </c>
+      <c r="J181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>15159.2</v>
+      </c>
+      <c r="E182" t="n">
+        <v>2410</v>
+      </c>
+      <c r="F182" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0.0679</v>
+      </c>
+      <c r="H182" t="n">
+        <v>0.0484</v>
+      </c>
+      <c r="I182" t="n">
+        <v>88</v>
+      </c>
+      <c r="J182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>16053.79</v>
+      </c>
+      <c r="E183" t="n">
+        <v>2552.3</v>
+      </c>
+      <c r="F183" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G183" t="n">
+        <v>0.07190000000000001</v>
+      </c>
+      <c r="H183" t="n">
+        <v>0.0513</v>
+      </c>
+      <c r="I183" t="n">
+        <v>92</v>
+      </c>
+      <c r="J183" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>15530.33</v>
+      </c>
+      <c r="E184" t="n">
+        <v>2469.1</v>
+      </c>
+      <c r="F184" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G184" t="n">
+        <v>0.0696</v>
+      </c>
+      <c r="H184" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="I184" t="n">
+        <v>89</v>
+      </c>
+      <c r="J184" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>16032.03</v>
+      </c>
+      <c r="E185" t="n">
+        <v>2470.3</v>
+      </c>
+      <c r="F185" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0.0718</v>
+      </c>
+      <c r="H185" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="I185" t="n">
+        <v>89</v>
+      </c>
+      <c r="J185" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>16622.43</v>
+      </c>
+      <c r="E186" t="n">
+        <v>2561.2</v>
+      </c>
+      <c r="F186" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G186" t="n">
+        <v>0.0745</v>
+      </c>
+      <c r="H186" t="n">
+        <v>0.0514</v>
+      </c>
+      <c r="I186" t="n">
+        <v>88</v>
+      </c>
+      <c r="J186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>15496.68</v>
+      </c>
+      <c r="E187" t="n">
+        <v>2387.8</v>
+      </c>
+      <c r="F187" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0.0694</v>
+      </c>
+      <c r="H187" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="I187" t="n">
+        <v>89</v>
+      </c>
+      <c r="J187" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>16140.16</v>
+      </c>
+      <c r="E188" t="n">
+        <v>3762.3</v>
+      </c>
+      <c r="F188" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0.0723</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0.0756</v>
+      </c>
+      <c r="I188" t="n">
+        <v>89</v>
+      </c>
+      <c r="J188" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>16629.83</v>
+      </c>
+      <c r="E189" t="n">
+        <v>3876.4</v>
+      </c>
+      <c r="F189" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G189" t="n">
+        <v>0.0745</v>
+      </c>
+      <c r="H189" t="n">
+        <v>0.0779</v>
+      </c>
+      <c r="I189" t="n">
+        <v>91</v>
+      </c>
+      <c r="J189" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>16114.14</v>
+      </c>
+      <c r="E190" t="n">
+        <v>3756.2</v>
+      </c>
+      <c r="F190" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0.0722</v>
+      </c>
+      <c r="H190" t="n">
+        <v>0.0755</v>
+      </c>
+      <c r="I190" t="n">
+        <v>89</v>
+      </c>
+      <c r="J190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>14831.75</v>
+      </c>
+      <c r="E191" t="n">
+        <v>3626.3</v>
+      </c>
+      <c r="F191" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G191" t="n">
+        <v>0.0665</v>
+      </c>
+      <c r="H191" t="n">
+        <v>0.0728</v>
+      </c>
+      <c r="I191" t="n">
+        <v>92</v>
+      </c>
+      <c r="J191" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>14287.31</v>
+      </c>
+      <c r="E192" t="n">
+        <v>3493.2</v>
+      </c>
+      <c r="F192" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G192" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="H192" t="n">
+        <v>0.0702</v>
+      </c>
+      <c r="I192" t="n">
+        <v>92</v>
+      </c>
+      <c r="J192" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>14152.87</v>
+      </c>
+      <c r="E193" t="n">
+        <v>3460.4</v>
+      </c>
+      <c r="F193" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G193" t="n">
+        <v>0.0634</v>
+      </c>
+      <c r="H193" t="n">
+        <v>0.06950000000000001</v>
+      </c>
+      <c r="I193" t="n">
+        <v>88</v>
+      </c>
+      <c r="J193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>11988.24</v>
+      </c>
+      <c r="E194" t="n">
+        <v>4296.9</v>
+      </c>
+      <c r="F194" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G194" t="n">
+        <v>0.0537</v>
+      </c>
+      <c r="H194" t="n">
+        <v>0.0863</v>
+      </c>
+      <c r="I194" t="n">
+        <v>88</v>
+      </c>
+      <c r="J194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>12200.12</v>
+      </c>
+      <c r="E195" t="n">
+        <v>4372.8</v>
+      </c>
+      <c r="F195" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G195" t="n">
+        <v>0.0547</v>
+      </c>
+      <c r="H195" t="n">
+        <v>0.0878</v>
+      </c>
+      <c r="I195" t="n">
+        <v>88</v>
+      </c>
+      <c r="J195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>11957.94</v>
+      </c>
+      <c r="E196" t="n">
+        <v>4286</v>
+      </c>
+      <c r="F196" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0.0536</v>
+      </c>
+      <c r="H196" t="n">
+        <v>0.0861</v>
+      </c>
+      <c r="I196" t="n">
+        <v>91</v>
+      </c>
+      <c r="J196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>15600.17</v>
+      </c>
+      <c r="E197" t="n">
+        <v>2480.2</v>
+      </c>
+      <c r="F197" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G197" t="n">
+        <v>0.0684</v>
+      </c>
+      <c r="H197" t="n">
+        <v>0.0488</v>
+      </c>
+      <c r="I197" t="n">
+        <v>90</v>
+      </c>
+      <c r="J197" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>16540.17</v>
+      </c>
+      <c r="E198" t="n">
+        <v>2629.6</v>
+      </c>
+      <c r="F198" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="H198" t="n">
+        <v>0.0517</v>
+      </c>
+      <c r="I198" t="n">
+        <v>92</v>
+      </c>
+      <c r="J198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>16413.91</v>
+      </c>
+      <c r="E199" t="n">
+        <v>2609.5</v>
+      </c>
+      <c r="F199" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0.07190000000000001</v>
+      </c>
+      <c r="H199" t="n">
+        <v>0.0513</v>
+      </c>
+      <c r="I199" t="n">
+        <v>89</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>16473.71</v>
+      </c>
+      <c r="E200" t="n">
+        <v>2538.3</v>
+      </c>
+      <c r="F200" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G200" t="n">
+        <v>0.0722</v>
+      </c>
+      <c r="H200" t="n">
+        <v>0.0499</v>
+      </c>
+      <c r="I200" t="n">
+        <v>90</v>
+      </c>
+      <c r="J200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>16096.24</v>
+      </c>
+      <c r="E201" t="n">
+        <v>2480.2</v>
+      </c>
+      <c r="F201" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G201" t="n">
+        <v>0.07049999999999999</v>
+      </c>
+      <c r="H201" t="n">
+        <v>0.0488</v>
+      </c>
+      <c r="I201" t="n">
+        <v>90</v>
+      </c>
+      <c r="J201" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>16700.99</v>
+      </c>
+      <c r="E202" t="n">
+        <v>2573.3</v>
+      </c>
+      <c r="F202" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G202" t="n">
+        <v>0.0732</v>
+      </c>
+      <c r="H202" t="n">
+        <v>0.0506</v>
+      </c>
+      <c r="I202" t="n">
+        <v>88</v>
+      </c>
+      <c r="J202" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>15914.21</v>
+      </c>
+      <c r="E203" t="n">
+        <v>3709.6</v>
+      </c>
+      <c r="F203" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G203" t="n">
+        <v>0.0697</v>
+      </c>
+      <c r="H203" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="I203" t="n">
+        <v>89</v>
+      </c>
+      <c r="J203" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>16386.04</v>
+      </c>
+      <c r="E204" t="n">
+        <v>3819.6</v>
+      </c>
+      <c r="F204" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G204" t="n">
+        <v>0.0718</v>
+      </c>
+      <c r="H204" t="n">
+        <v>0.0751</v>
+      </c>
+      <c r="I204" t="n">
+        <v>89</v>
+      </c>
+      <c r="J204" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>16283.86</v>
+      </c>
+      <c r="E205" t="n">
+        <v>3795.8</v>
+      </c>
+      <c r="F205" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G205" t="n">
+        <v>0.07140000000000001</v>
+      </c>
+      <c r="H205" t="n">
+        <v>0.0746</v>
+      </c>
+      <c r="I205" t="n">
+        <v>88</v>
+      </c>
+      <c r="J205" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>15146.55</v>
+      </c>
+      <c r="E206" t="n">
+        <v>3703.3</v>
+      </c>
+      <c r="F206" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G206" t="n">
+        <v>0.0664</v>
+      </c>
+      <c r="H206" t="n">
+        <v>0.0728</v>
+      </c>
+      <c r="I206" t="n">
+        <v>92</v>
+      </c>
+      <c r="J206" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>14711.66</v>
+      </c>
+      <c r="E207" t="n">
+        <v>3597</v>
+      </c>
+      <c r="F207" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G207" t="n">
+        <v>0.0645</v>
+      </c>
+      <c r="H207" t="n">
+        <v>0.0707</v>
+      </c>
+      <c r="I207" t="n">
+        <v>90</v>
+      </c>
+      <c r="J207" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>14979.91</v>
+      </c>
+      <c r="E208" t="n">
+        <v>3662.6</v>
+      </c>
+      <c r="F208" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0.06560000000000001</v>
+      </c>
+      <c r="H208" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="I208" t="n">
+        <v>89</v>
+      </c>
+      <c r="J208" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>11952.25</v>
+      </c>
+      <c r="E209" t="n">
+        <v>4284</v>
+      </c>
+      <c r="F209" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0.0524</v>
+      </c>
+      <c r="H209" t="n">
+        <v>0.0842</v>
+      </c>
+      <c r="I209" t="n">
+        <v>90</v>
+      </c>
+      <c r="J209" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>12746.06</v>
+      </c>
+      <c r="E210" t="n">
+        <v>4568.5</v>
+      </c>
+      <c r="F210" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G210" t="n">
+        <v>0.0558</v>
+      </c>
+      <c r="H210" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="I210" t="n">
+        <v>90</v>
+      </c>
+      <c r="J210" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>12274.66</v>
+      </c>
+      <c r="E211" t="n">
+        <v>4399.5</v>
+      </c>
+      <c r="F211" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G211" t="n">
+        <v>0.0538</v>
+      </c>
+      <c r="H211" t="n">
+        <v>0.08649999999999999</v>
+      </c>
+      <c r="I211" t="n">
+        <v>91</v>
+      </c>
+      <c r="J211" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>17172.54</v>
+      </c>
+      <c r="E212" t="n">
+        <v>2730.1</v>
+      </c>
+      <c r="F212" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G212" t="n">
+        <v>0.0752</v>
+      </c>
+      <c r="H212" t="n">
+        <v>0.0539</v>
+      </c>
+      <c r="I212" t="n">
+        <v>89</v>
+      </c>
+      <c r="J212" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>17180.53</v>
+      </c>
+      <c r="E213" t="n">
+        <v>2731.4</v>
+      </c>
+      <c r="F213" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G213" t="n">
+        <v>0.07530000000000001</v>
+      </c>
+      <c r="H213" t="n">
+        <v>0.0539</v>
+      </c>
+      <c r="I213" t="n">
+        <v>89</v>
+      </c>
+      <c r="J213" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>16461.45</v>
+      </c>
+      <c r="E214" t="n">
+        <v>2617.1</v>
+      </c>
+      <c r="F214" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G214" t="n">
+        <v>0.0721</v>
+      </c>
+      <c r="H214" t="n">
+        <v>0.0516</v>
+      </c>
+      <c r="I214" t="n">
+        <v>90</v>
+      </c>
+      <c r="J214" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>15843.35</v>
+      </c>
+      <c r="E215" t="n">
+        <v>2441.2</v>
+      </c>
+      <c r="F215" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0.0694</v>
+      </c>
+      <c r="H215" t="n">
+        <v>0.0482</v>
+      </c>
+      <c r="I215" t="n">
+        <v>91</v>
+      </c>
+      <c r="J215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>15999.84</v>
+      </c>
+      <c r="E216" t="n">
+        <v>2465.3</v>
+      </c>
+      <c r="F216" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G216" t="n">
+        <v>0.0701</v>
+      </c>
+      <c r="H216" t="n">
+        <v>0.0486</v>
+      </c>
+      <c r="I216" t="n">
+        <v>89</v>
+      </c>
+      <c r="J216" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>16150.05</v>
+      </c>
+      <c r="E217" t="n">
+        <v>2488.5</v>
+      </c>
+      <c r="F217" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G217" t="n">
+        <v>0.0708</v>
+      </c>
+      <c r="H217" t="n">
+        <v>0.0491</v>
+      </c>
+      <c r="I217" t="n">
+        <v>92</v>
+      </c>
+      <c r="J217" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>16466.05</v>
+      </c>
+      <c r="E218" t="n">
+        <v>3838.2</v>
+      </c>
+      <c r="F218" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0.0721</v>
+      </c>
+      <c r="H218" t="n">
+        <v>0.0757</v>
+      </c>
+      <c r="I218" t="n">
+        <v>92</v>
+      </c>
+      <c r="J218" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>16726.26</v>
+      </c>
+      <c r="E219" t="n">
+        <v>3898.9</v>
+      </c>
+      <c r="F219" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0.0733</v>
+      </c>
+      <c r="H219" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="I219" t="n">
+        <v>90</v>
+      </c>
+      <c r="J219" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>16588.38</v>
+      </c>
+      <c r="E220" t="n">
+        <v>3866.8</v>
+      </c>
+      <c r="F220" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0.0727</v>
+      </c>
+      <c r="H220" t="n">
+        <v>0.07630000000000001</v>
+      </c>
+      <c r="I220" t="n">
+        <v>91</v>
+      </c>
+      <c r="J220" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>14412.03</v>
+      </c>
+      <c r="E221" t="n">
+        <v>3523.7</v>
+      </c>
+      <c r="F221" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G221" t="n">
+        <v>0.0631</v>
+      </c>
+      <c r="H221" t="n">
+        <v>0.06950000000000001</v>
+      </c>
+      <c r="I221" t="n">
+        <v>88</v>
+      </c>
+      <c r="J221" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>14441.3</v>
+      </c>
+      <c r="E222" t="n">
+        <v>3530.9</v>
+      </c>
+      <c r="F222" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G222" t="n">
+        <v>0.0633</v>
+      </c>
+      <c r="H222" t="n">
+        <v>0.0697</v>
+      </c>
+      <c r="I222" t="n">
+        <v>92</v>
+      </c>
+      <c r="J222" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>14479.74</v>
+      </c>
+      <c r="E223" t="n">
+        <v>3540.3</v>
+      </c>
+      <c r="F223" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G223" t="n">
+        <v>0.0634</v>
+      </c>
+      <c r="H223" t="n">
+        <v>0.0698</v>
+      </c>
+      <c r="I223" t="n">
+        <v>89</v>
+      </c>
+      <c r="J223" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>11877.9</v>
+      </c>
+      <c r="E224" t="n">
+        <v>4257.3</v>
+      </c>
+      <c r="F224" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G224" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="H224" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="I224" t="n">
+        <v>92</v>
+      </c>
+      <c r="J224" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>11948.05</v>
+      </c>
+      <c r="E225" t="n">
+        <v>4282.5</v>
+      </c>
+      <c r="F225" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G225" t="n">
+        <v>0.0523</v>
+      </c>
+      <c r="H225" t="n">
+        <v>0.08450000000000001</v>
+      </c>
+      <c r="I225" t="n">
+        <v>90</v>
+      </c>
+      <c r="J225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>12495.12</v>
+      </c>
+      <c r="E226" t="n">
+        <v>4478.5</v>
+      </c>
+      <c r="F226" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G226" t="n">
+        <v>0.0547</v>
+      </c>
+      <c r="H226" t="n">
+        <v>0.08840000000000001</v>
+      </c>
+      <c r="I226" t="n">
+        <v>88</v>
+      </c>
+      <c r="J226" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>16658.93</v>
+      </c>
+      <c r="E227" t="n">
+        <v>2648.5</v>
+      </c>
+      <c r="F227" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G227" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="H227" t="n">
+        <v>0.0519</v>
+      </c>
+      <c r="I227" t="n">
+        <v>88</v>
+      </c>
+      <c r="J227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>17547.16</v>
+      </c>
+      <c r="E228" t="n">
+        <v>2789.7</v>
+      </c>
+      <c r="F228" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G228" t="n">
+        <v>0.0764</v>
+      </c>
+      <c r="H228" t="n">
+        <v>0.0547</v>
+      </c>
+      <c r="I228" t="n">
+        <v>91</v>
+      </c>
+      <c r="J228" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>17384.22</v>
+      </c>
+      <c r="E229" t="n">
+        <v>2763.8</v>
+      </c>
+      <c r="F229" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G229" t="n">
+        <v>0.0757</v>
+      </c>
+      <c r="H229" t="n">
+        <v>0.0542</v>
+      </c>
+      <c r="I229" t="n">
+        <v>90</v>
+      </c>
+      <c r="J229" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>15454.33</v>
+      </c>
+      <c r="E230" t="n">
+        <v>2381.3</v>
+      </c>
+      <c r="F230" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G230" t="n">
+        <v>0.0673</v>
+      </c>
+      <c r="H230" t="n">
+        <v>0.0467</v>
+      </c>
+      <c r="I230" t="n">
+        <v>90</v>
+      </c>
+      <c r="J230" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>16375.6</v>
+      </c>
+      <c r="E231" t="n">
+        <v>2523.2</v>
+      </c>
+      <c r="F231" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G231" t="n">
+        <v>0.0713</v>
+      </c>
+      <c r="H231" t="n">
+        <v>0.0495</v>
+      </c>
+      <c r="I231" t="n">
+        <v>92</v>
+      </c>
+      <c r="J231" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>16515.26</v>
+      </c>
+      <c r="E232" t="n">
+        <v>2544.7</v>
+      </c>
+      <c r="F232" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G232" t="n">
+        <v>0.07190000000000001</v>
+      </c>
+      <c r="H232" t="n">
+        <v>0.0499</v>
+      </c>
+      <c r="I232" t="n">
+        <v>92</v>
+      </c>
+      <c r="J232" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>16511.77</v>
+      </c>
+      <c r="E233" t="n">
+        <v>3848.9</v>
+      </c>
+      <c r="F233" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G233" t="n">
+        <v>0.07190000000000001</v>
+      </c>
+      <c r="H233" t="n">
+        <v>0.0755</v>
+      </c>
+      <c r="I233" t="n">
+        <v>92</v>
+      </c>
+      <c r="J233" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>16471.25</v>
+      </c>
+      <c r="E234" t="n">
+        <v>3839.5</v>
+      </c>
+      <c r="F234" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G234" t="n">
+        <v>0.0717</v>
+      </c>
+      <c r="H234" t="n">
+        <v>0.07530000000000001</v>
+      </c>
+      <c r="I234" t="n">
+        <v>89</v>
+      </c>
+      <c r="J234" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>15863.07</v>
+      </c>
+      <c r="E235" t="n">
+        <v>3697.7</v>
+      </c>
+      <c r="F235" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G235" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="H235" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="I235" t="n">
+        <v>90</v>
+      </c>
+      <c r="J235" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>14957.06</v>
+      </c>
+      <c r="E236" t="n">
+        <v>3657</v>
+      </c>
+      <c r="F236" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G236" t="n">
+        <v>0.06510000000000001</v>
+      </c>
+      <c r="H236" t="n">
+        <v>0.0717</v>
+      </c>
+      <c r="I236" t="n">
+        <v>92</v>
+      </c>
+      <c r="J236" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>14423.73</v>
+      </c>
+      <c r="E237" t="n">
+        <v>3526.6</v>
+      </c>
+      <c r="F237" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G237" t="n">
+        <v>0.06279999999999999</v>
+      </c>
+      <c r="H237" t="n">
+        <v>0.06909999999999999</v>
+      </c>
+      <c r="I237" t="n">
+        <v>89</v>
+      </c>
+      <c r="J237" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>15064.8</v>
+      </c>
+      <c r="E238" t="n">
+        <v>3683.3</v>
+      </c>
+      <c r="F238" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G238" t="n">
+        <v>0.06560000000000001</v>
+      </c>
+      <c r="H238" t="n">
+        <v>0.0722</v>
+      </c>
+      <c r="I238" t="n">
+        <v>88</v>
+      </c>
+      <c r="J238" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>12151.34</v>
+      </c>
+      <c r="E239" t="n">
+        <v>4355.3</v>
+      </c>
+      <c r="F239" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G239" t="n">
+        <v>0.0529</v>
+      </c>
+      <c r="H239" t="n">
+        <v>0.0854</v>
+      </c>
+      <c r="I239" t="n">
+        <v>91</v>
+      </c>
+      <c r="J239" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>12339.91</v>
+      </c>
+      <c r="E240" t="n">
+        <v>4422.9</v>
+      </c>
+      <c r="F240" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G240" t="n">
+        <v>0.0537</v>
+      </c>
+      <c r="H240" t="n">
+        <v>0.0867</v>
+      </c>
+      <c r="I240" t="n">
+        <v>90</v>
+      </c>
+      <c r="J240" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>12050.46</v>
+      </c>
+      <c r="E241" t="n">
+        <v>4319.2</v>
+      </c>
+      <c r="F241" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G241" t="n">
+        <v>0.0524</v>
+      </c>
+      <c r="H241" t="n">
+        <v>0.0847</v>
+      </c>
+      <c r="I241" t="n">
+        <v>90</v>
+      </c>
+      <c r="J241" t="n">
         <v>0</v>
       </c>
     </row>

--- a/stella/test_fixtures/pantry_loaded/iri_data.xlsx
+++ b/stella/test_fixtures/pantry_loaded/iri_data.xlsx
@@ -499,10 +499,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16750.37</v>
+        <v>3045.52</v>
       </c>
       <c r="E2" t="n">
-        <v>2663</v>
+        <v>484.2</v>
       </c>
       <c r="F2" t="n">
         <v>6.29</v>
@@ -535,10 +535,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17856.52</v>
+        <v>3246.64</v>
       </c>
       <c r="E3" t="n">
-        <v>2838.9</v>
+        <v>516.2</v>
       </c>
       <c r="F3" t="n">
         <v>6.29</v>
@@ -571,10 +571,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17803.38</v>
+        <v>3236.98</v>
       </c>
       <c r="E4" t="n">
-        <v>2830.4</v>
+        <v>514.6</v>
       </c>
       <c r="F4" t="n">
         <v>6.29</v>
@@ -607,10 +607,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16445.81</v>
+        <v>2990.15</v>
       </c>
       <c r="E5" t="n">
-        <v>2534</v>
+        <v>460.7</v>
       </c>
       <c r="F5" t="n">
         <v>6.49</v>
@@ -643,10 +643,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15548.57</v>
+        <v>2827.01</v>
       </c>
       <c r="E6" t="n">
-        <v>2395.8</v>
+        <v>435.6</v>
       </c>
       <c r="F6" t="n">
         <v>6.49</v>
@@ -679,10 +679,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15682.89</v>
+        <v>2851.44</v>
       </c>
       <c r="E7" t="n">
-        <v>2416.5</v>
+        <v>439.4</v>
       </c>
       <c r="F7" t="n">
         <v>6.49</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16838.37</v>
+        <v>3061.52</v>
       </c>
       <c r="E8" t="n">
-        <v>3925</v>
+        <v>713.6</v>
       </c>
       <c r="F8" t="n">
         <v>4.29</v>
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15886.42</v>
+        <v>2888.44</v>
       </c>
       <c r="E9" t="n">
-        <v>3703.1</v>
+        <v>673.3</v>
       </c>
       <c r="F9" t="n">
         <v>4.29</v>
@@ -787,10 +787,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17149.71</v>
+        <v>3118.13</v>
       </c>
       <c r="E10" t="n">
-        <v>3997.6</v>
+        <v>726.8</v>
       </c>
       <c r="F10" t="n">
         <v>4.29</v>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14478.04</v>
+        <v>2632.37</v>
       </c>
       <c r="E11" t="n">
-        <v>3539.9</v>
+        <v>643.6</v>
       </c>
       <c r="F11" t="n">
         <v>4.09</v>
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14878.29</v>
+        <v>2705.14</v>
       </c>
       <c r="E12" t="n">
-        <v>3637.7</v>
+        <v>661.4</v>
       </c>
       <c r="F12" t="n">
         <v>4.09</v>
@@ -895,10 +895,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15075.11</v>
+        <v>2740.93</v>
       </c>
       <c r="E13" t="n">
-        <v>3685.8</v>
+        <v>670.2</v>
       </c>
       <c r="F13" t="n">
         <v>4.09</v>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12172.52</v>
+        <v>2213.19</v>
       </c>
       <c r="E14" t="n">
-        <v>4362.9</v>
+        <v>793.3</v>
       </c>
       <c r="F14" t="n">
         <v>2.79</v>
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12098.37</v>
+        <v>2199.7</v>
       </c>
       <c r="E15" t="n">
-        <v>4336.3</v>
+        <v>788.4</v>
       </c>
       <c r="F15" t="n">
         <v>2.79</v>
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12382.79</v>
+        <v>2251.42</v>
       </c>
       <c r="E16" t="n">
-        <v>4438.3</v>
+        <v>807</v>
       </c>
       <c r="F16" t="n">
         <v>2.79</v>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>17648.3</v>
+        <v>3208.78</v>
       </c>
       <c r="E17" t="n">
-        <v>2805.8</v>
+        <v>510.1</v>
       </c>
       <c r="F17" t="n">
         <v>6.29</v>
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>17824.78</v>
+        <v>3240.87</v>
       </c>
       <c r="E18" t="n">
-        <v>2833.8</v>
+        <v>515.2</v>
       </c>
       <c r="F18" t="n">
         <v>6.29</v>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16990.45</v>
+        <v>3089.17</v>
       </c>
       <c r="E19" t="n">
-        <v>2701.2</v>
+        <v>491.1</v>
       </c>
       <c r="F19" t="n">
         <v>6.29</v>
@@ -1147,10 +1147,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15679.93</v>
+        <v>2850.9</v>
       </c>
       <c r="E20" t="n">
-        <v>2416</v>
+        <v>439.3</v>
       </c>
       <c r="F20" t="n">
         <v>6.49</v>
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15658.95</v>
+        <v>2847.08</v>
       </c>
       <c r="E21" t="n">
-        <v>2412.8</v>
+        <v>438.7</v>
       </c>
       <c r="F21" t="n">
         <v>6.49</v>
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16091.04</v>
+        <v>2925.64</v>
       </c>
       <c r="E22" t="n">
-        <v>2479.4</v>
+        <v>450.8</v>
       </c>
       <c r="F22" t="n">
         <v>6.49</v>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16474.77</v>
+        <v>2995.41</v>
       </c>
       <c r="E23" t="n">
-        <v>3840.3</v>
+        <v>698.2</v>
       </c>
       <c r="F23" t="n">
         <v>4.29</v>
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16198.64</v>
+        <v>2945.21</v>
       </c>
       <c r="E24" t="n">
-        <v>3775.9</v>
+        <v>686.5</v>
       </c>
       <c r="F24" t="n">
         <v>4.29</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15915.53</v>
+        <v>2893.73</v>
       </c>
       <c r="E25" t="n">
-        <v>3709.9</v>
+        <v>674.5</v>
       </c>
       <c r="F25" t="n">
         <v>4.29</v>
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14600.1</v>
+        <v>2654.56</v>
       </c>
       <c r="E26" t="n">
-        <v>3569.7</v>
+        <v>649</v>
       </c>
       <c r="F26" t="n">
         <v>4.09</v>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15159.05</v>
+        <v>2756.19</v>
       </c>
       <c r="E27" t="n">
-        <v>3706.4</v>
+        <v>673.9</v>
       </c>
       <c r="F27" t="n">
         <v>4.09</v>
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14800.16</v>
+        <v>2690.94</v>
       </c>
       <c r="E28" t="n">
-        <v>3618.6</v>
+        <v>657.9</v>
       </c>
       <c r="F28" t="n">
         <v>4.09</v>
@@ -1471,10 +1471,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12271.59</v>
+        <v>2231.2</v>
       </c>
       <c r="E29" t="n">
-        <v>4398.4</v>
+        <v>799.7</v>
       </c>
       <c r="F29" t="n">
         <v>2.79</v>
@@ -1507,10 +1507,10 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11893.67</v>
+        <v>2162.49</v>
       </c>
       <c r="E30" t="n">
-        <v>4263</v>
+        <v>775.1</v>
       </c>
       <c r="F30" t="n">
         <v>2.79</v>
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12032.87</v>
+        <v>2187.8</v>
       </c>
       <c r="E31" t="n">
-        <v>4312.9</v>
+        <v>784.2</v>
       </c>
       <c r="F31" t="n">
         <v>2.79</v>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>16834.36</v>
+        <v>3060.79</v>
       </c>
       <c r="E32" t="n">
-        <v>2676.4</v>
+        <v>486.6</v>
       </c>
       <c r="F32" t="n">
         <v>6.29</v>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>16956.05</v>
+        <v>3082.92</v>
       </c>
       <c r="E33" t="n">
-        <v>2695.7</v>
+        <v>490.1</v>
       </c>
       <c r="F33" t="n">
         <v>6.29</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>16827.44</v>
+        <v>3059.53</v>
       </c>
       <c r="E34" t="n">
-        <v>2675.3</v>
+        <v>486.4</v>
       </c>
       <c r="F34" t="n">
         <v>6.29</v>
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>16514.99</v>
+        <v>3002.73</v>
       </c>
       <c r="E35" t="n">
-        <v>2544.7</v>
+        <v>462.7</v>
       </c>
       <c r="F35" t="n">
         <v>6.49</v>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>16170.98</v>
+        <v>2940.18</v>
       </c>
       <c r="E36" t="n">
-        <v>2491.7</v>
+        <v>453</v>
       </c>
       <c r="F36" t="n">
         <v>6.49</v>
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>16364.9</v>
+        <v>2975.44</v>
       </c>
       <c r="E37" t="n">
-        <v>2521.6</v>
+        <v>458.5</v>
       </c>
       <c r="F37" t="n">
         <v>6.49</v>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>16246.99</v>
+        <v>2954</v>
       </c>
       <c r="E38" t="n">
-        <v>3787.2</v>
+        <v>688.6</v>
       </c>
       <c r="F38" t="n">
         <v>4.29</v>
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>16346.38</v>
+        <v>2972.07</v>
       </c>
       <c r="E39" t="n">
-        <v>3810.3</v>
+        <v>692.8</v>
       </c>
       <c r="F39" t="n">
         <v>4.29</v>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>16390.78</v>
+        <v>2980.14</v>
       </c>
       <c r="E40" t="n">
-        <v>3820.7</v>
+        <v>694.7</v>
       </c>
       <c r="F40" t="n">
         <v>4.29</v>
@@ -1903,10 +1903,10 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>14925.9</v>
+        <v>2713.8</v>
       </c>
       <c r="E41" t="n">
-        <v>3649.4</v>
+        <v>663.5</v>
       </c>
       <c r="F41" t="n">
         <v>4.09</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>14940.33</v>
+        <v>2716.42</v>
       </c>
       <c r="E42" t="n">
-        <v>3652.9</v>
+        <v>664.2</v>
       </c>
       <c r="F42" t="n">
         <v>4.09</v>
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>14278.8</v>
+        <v>2596.15</v>
       </c>
       <c r="E43" t="n">
-        <v>3491.1</v>
+        <v>634.8</v>
       </c>
       <c r="F43" t="n">
         <v>4.09</v>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12709.63</v>
+        <v>2310.84</v>
       </c>
       <c r="E44" t="n">
-        <v>4555.4</v>
+        <v>828.3</v>
       </c>
       <c r="F44" t="n">
         <v>2.79</v>
@@ -2047,10 +2047,10 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11903.45</v>
+        <v>2164.26</v>
       </c>
       <c r="E45" t="n">
-        <v>4266.5</v>
+        <v>775.7</v>
       </c>
       <c r="F45" t="n">
         <v>2.79</v>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12665.02</v>
+        <v>2302.73</v>
       </c>
       <c r="E46" t="n">
-        <v>4539.4</v>
+        <v>825.4</v>
       </c>
       <c r="F46" t="n">
         <v>2.79</v>
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>17906.4</v>
+        <v>3255.71</v>
       </c>
       <c r="E47" t="n">
-        <v>2846.8</v>
+        <v>517.6</v>
       </c>
       <c r="F47" t="n">
         <v>6.29</v>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>17834.4</v>
+        <v>3242.62</v>
       </c>
       <c r="E48" t="n">
-        <v>2835.4</v>
+        <v>515.5</v>
       </c>
       <c r="F48" t="n">
         <v>6.29</v>
@@ -2191,10 +2191,10 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>17681.31</v>
+        <v>3214.78</v>
       </c>
       <c r="E49" t="n">
-        <v>2811</v>
+        <v>511.1</v>
       </c>
       <c r="F49" t="n">
         <v>6.29</v>
@@ -2227,10 +2227,10 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>16085.45</v>
+        <v>2924.63</v>
       </c>
       <c r="E50" t="n">
-        <v>2478.5</v>
+        <v>450.6</v>
       </c>
       <c r="F50" t="n">
         <v>6.49</v>
@@ -2263,10 +2263,10 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>16050.68</v>
+        <v>2918.31</v>
       </c>
       <c r="E51" t="n">
-        <v>2473.1</v>
+        <v>449.7</v>
       </c>
       <c r="F51" t="n">
         <v>6.49</v>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>16100.97</v>
+        <v>2927.45</v>
       </c>
       <c r="E52" t="n">
-        <v>2480.9</v>
+        <v>451.1</v>
       </c>
       <c r="F52" t="n">
         <v>6.49</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>16564.82</v>
+        <v>3011.79</v>
       </c>
       <c r="E53" t="n">
-        <v>3861.3</v>
+        <v>702</v>
       </c>
       <c r="F53" t="n">
         <v>4.29</v>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>16430.04</v>
+        <v>2987.28</v>
       </c>
       <c r="E54" t="n">
-        <v>3829.8</v>
+        <v>696.3</v>
       </c>
       <c r="F54" t="n">
         <v>4.29</v>
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>16029.93</v>
+        <v>2914.53</v>
       </c>
       <c r="E55" t="n">
-        <v>3736.6</v>
+        <v>679.4</v>
       </c>
       <c r="F55" t="n">
         <v>4.29</v>
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>14183.87</v>
+        <v>2578.89</v>
       </c>
       <c r="E56" t="n">
-        <v>3467.9</v>
+        <v>630.5</v>
       </c>
       <c r="F56" t="n">
         <v>4.09</v>
@@ -2479,10 +2479,10 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>15150.76</v>
+        <v>2754.68</v>
       </c>
       <c r="E57" t="n">
-        <v>3704.3</v>
+        <v>673.5</v>
       </c>
       <c r="F57" t="n">
         <v>4.09</v>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>14600.73</v>
+        <v>2654.68</v>
       </c>
       <c r="E58" t="n">
-        <v>3569.9</v>
+        <v>649.1</v>
       </c>
       <c r="F58" t="n">
         <v>4.09</v>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12721.08</v>
+        <v>2312.92</v>
       </c>
       <c r="E59" t="n">
-        <v>4559.5</v>
+        <v>829</v>
       </c>
       <c r="F59" t="n">
         <v>2.79</v>
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11945.61</v>
+        <v>2171.93</v>
       </c>
       <c r="E60" t="n">
-        <v>4281.6</v>
+        <v>778.5</v>
       </c>
       <c r="F60" t="n">
         <v>2.79</v>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12329.44</v>
+        <v>2241.72</v>
       </c>
       <c r="E61" t="n">
-        <v>4419.2</v>
+        <v>803.5</v>
       </c>
       <c r="F61" t="n">
         <v>2.79</v>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>29645.24</v>
+        <v>5390.04</v>
       </c>
       <c r="E62" t="n">
-        <v>5882</v>
+        <v>1069.5</v>
       </c>
       <c r="F62" t="n">
         <v>5.04</v>
@@ -2695,10 +2695,10 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>31518.16</v>
+        <v>5730.57</v>
       </c>
       <c r="E63" t="n">
-        <v>6253.6</v>
+        <v>1137</v>
       </c>
       <c r="F63" t="n">
         <v>5.04</v>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>30105.09</v>
+        <v>5473.65</v>
       </c>
       <c r="E64" t="n">
-        <v>5973.2</v>
+        <v>1086</v>
       </c>
       <c r="F64" t="n">
         <v>5.04</v>
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>14710.4</v>
+        <v>2674.62</v>
       </c>
       <c r="E65" t="n">
-        <v>2266.6</v>
+        <v>412.1</v>
       </c>
       <c r="F65" t="n">
         <v>6.49</v>
@@ -2803,10 +2803,10 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>15067.22</v>
+        <v>2739.5</v>
       </c>
       <c r="E66" t="n">
-        <v>2321.6</v>
+        <v>422.1</v>
       </c>
       <c r="F66" t="n">
         <v>6.49</v>
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>15619.08</v>
+        <v>2839.83</v>
       </c>
       <c r="E67" t="n">
-        <v>2406.6</v>
+        <v>437.6</v>
       </c>
       <c r="F67" t="n">
         <v>6.49</v>
@@ -2875,10 +2875,10 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>16345.06</v>
+        <v>2971.83</v>
       </c>
       <c r="E68" t="n">
-        <v>3810</v>
+        <v>692.7</v>
       </c>
       <c r="F68" t="n">
         <v>4.29</v>
@@ -2911,10 +2911,10 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>16510.98</v>
+        <v>3002</v>
       </c>
       <c r="E69" t="n">
-        <v>3848.7</v>
+        <v>699.8</v>
       </c>
       <c r="F69" t="n">
         <v>4.29</v>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>16566.4</v>
+        <v>3012.07</v>
       </c>
       <c r="E70" t="n">
-        <v>3861.6</v>
+        <v>702.1</v>
       </c>
       <c r="F70" t="n">
         <v>4.29</v>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13999.12</v>
+        <v>2545.29</v>
       </c>
       <c r="E71" t="n">
-        <v>3422.8</v>
+        <v>622.3</v>
       </c>
       <c r="F71" t="n">
         <v>4.09</v>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>14815.12</v>
+        <v>2693.66</v>
       </c>
       <c r="E72" t="n">
-        <v>3622.3</v>
+        <v>658.6</v>
       </c>
       <c r="F72" t="n">
         <v>4.09</v>
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>14258.23</v>
+        <v>2592.41</v>
       </c>
       <c r="E73" t="n">
-        <v>3486.1</v>
+        <v>633.8</v>
       </c>
       <c r="F73" t="n">
         <v>4.09</v>
@@ -3091,10 +3091,10 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>12412.52</v>
+        <v>2256.82</v>
       </c>
       <c r="E74" t="n">
-        <v>4448.9</v>
+        <v>808.9</v>
       </c>
       <c r="F74" t="n">
         <v>2.79</v>
@@ -3127,10 +3127,10 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11787.23</v>
+        <v>2143.13</v>
       </c>
       <c r="E75" t="n">
-        <v>4224.8</v>
+        <v>768.1</v>
       </c>
       <c r="F75" t="n">
         <v>2.79</v>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>12760.53</v>
+        <v>2320.1</v>
       </c>
       <c r="E76" t="n">
-        <v>4573.7</v>
+        <v>831.6</v>
       </c>
       <c r="F76" t="n">
         <v>2.79</v>
@@ -3199,10 +3199,10 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>30108.32</v>
+        <v>5474.24</v>
       </c>
       <c r="E77" t="n">
-        <v>5973.9</v>
+        <v>1086.2</v>
       </c>
       <c r="F77" t="n">
         <v>5.04</v>
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>29704.66</v>
+        <v>5400.85</v>
       </c>
       <c r="E78" t="n">
-        <v>5893.8</v>
+        <v>1071.6</v>
       </c>
       <c r="F78" t="n">
         <v>5.04</v>
@@ -3271,10 +3271,10 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>30926.44</v>
+        <v>5622.99</v>
       </c>
       <c r="E79" t="n">
-        <v>6136.2</v>
+        <v>1115.7</v>
       </c>
       <c r="F79" t="n">
         <v>5.04</v>
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>15682.01</v>
+        <v>2851.27</v>
       </c>
       <c r="E80" t="n">
-        <v>2416.3</v>
+        <v>439.3</v>
       </c>
       <c r="F80" t="n">
         <v>6.49</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>14698.37</v>
+        <v>2672.43</v>
       </c>
       <c r="E81" t="n">
-        <v>2264.8</v>
+        <v>411.8</v>
       </c>
       <c r="F81" t="n">
         <v>6.49</v>
@@ -3379,10 +3379,10 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>15198.13</v>
+        <v>2763.3</v>
       </c>
       <c r="E82" t="n">
-        <v>2341.8</v>
+        <v>425.8</v>
       </c>
       <c r="F82" t="n">
         <v>6.49</v>
@@ -3415,10 +3415,10 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>16694.4</v>
+        <v>3035.35</v>
       </c>
       <c r="E83" t="n">
-        <v>3891.5</v>
+        <v>707.5</v>
       </c>
       <c r="F83" t="n">
         <v>4.29</v>
@@ -3451,10 +3451,10 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>16509.4</v>
+        <v>3001.71</v>
       </c>
       <c r="E84" t="n">
-        <v>3848.3</v>
+        <v>699.7</v>
       </c>
       <c r="F84" t="n">
         <v>4.29</v>
@@ -3487,10 +3487,10 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>16823.01</v>
+        <v>3058.73</v>
       </c>
       <c r="E85" t="n">
-        <v>3921.4</v>
+        <v>713</v>
       </c>
       <c r="F85" t="n">
         <v>4.29</v>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>14365.33</v>
+        <v>2611.88</v>
       </c>
       <c r="E86" t="n">
-        <v>3512.3</v>
+        <v>638.6</v>
       </c>
       <c r="F86" t="n">
         <v>4.09</v>
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>14512.73</v>
+        <v>2638.68</v>
       </c>
       <c r="E87" t="n">
-        <v>3548.3</v>
+        <v>645.2</v>
       </c>
       <c r="F87" t="n">
         <v>4.09</v>
@@ -3595,10 +3595,10 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>14102.89</v>
+        <v>2564.16</v>
       </c>
       <c r="E88" t="n">
-        <v>3448.1</v>
+        <v>626.9</v>
       </c>
       <c r="F88" t="n">
         <v>4.09</v>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>12715.52</v>
+        <v>2311.91</v>
       </c>
       <c r="E89" t="n">
-        <v>4557.5</v>
+        <v>828.6</v>
       </c>
       <c r="F89" t="n">
         <v>2.79</v>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>12144.73</v>
+        <v>2208.13</v>
       </c>
       <c r="E90" t="n">
-        <v>4353</v>
+        <v>791.4</v>
       </c>
       <c r="F90" t="n">
         <v>2.79</v>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>12510.24</v>
+        <v>2274.59</v>
       </c>
       <c r="E91" t="n">
-        <v>4484</v>
+        <v>815.3</v>
       </c>
       <c r="F91" t="n">
         <v>2.79</v>
@@ -3739,10 +3739,10 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>29320.54</v>
+        <v>5331.01</v>
       </c>
       <c r="E92" t="n">
-        <v>5817.6</v>
+        <v>1057.7</v>
       </c>
       <c r="F92" t="n">
         <v>5.04</v>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>30068.89</v>
+        <v>5467.07</v>
       </c>
       <c r="E93" t="n">
-        <v>5966</v>
+        <v>1084.7</v>
       </c>
       <c r="F93" t="n">
         <v>5.04</v>
@@ -3811,10 +3811,10 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>29754.85</v>
+        <v>5409.97</v>
       </c>
       <c r="E94" t="n">
-        <v>5903.7</v>
+        <v>1073.4</v>
       </c>
       <c r="F94" t="n">
         <v>5.04</v>
@@ -3847,10 +3847,10 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>15599.17</v>
+        <v>2836.21</v>
       </c>
       <c r="E95" t="n">
-        <v>2403.6</v>
+        <v>437</v>
       </c>
       <c r="F95" t="n">
         <v>6.49</v>
@@ -3883,10 +3883,10 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>15699.86</v>
+        <v>2854.52</v>
       </c>
       <c r="E96" t="n">
-        <v>2419.1</v>
+        <v>439.8</v>
       </c>
       <c r="F96" t="n">
         <v>6.49</v>
@@ -3919,10 +3919,10 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>14950.37</v>
+        <v>2718.25</v>
       </c>
       <c r="E97" t="n">
-        <v>2303.6</v>
+        <v>418.8</v>
       </c>
       <c r="F97" t="n">
         <v>6.49</v>
@@ -3955,10 +3955,10 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>16403.52</v>
+        <v>2982.46</v>
       </c>
       <c r="E98" t="n">
-        <v>3823.7</v>
+        <v>695.2</v>
       </c>
       <c r="F98" t="n">
         <v>4.29</v>
@@ -3991,10 +3991,10 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>15706.23</v>
+        <v>2855.68</v>
       </c>
       <c r="E99" t="n">
-        <v>3661.1</v>
+        <v>665.7</v>
       </c>
       <c r="F99" t="n">
         <v>4.29</v>
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>15895.02</v>
+        <v>2890</v>
       </c>
       <c r="E100" t="n">
-        <v>3705.1</v>
+        <v>673.7</v>
       </c>
       <c r="F100" t="n">
         <v>4.29</v>
@@ -4063,10 +4063,10 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>13915.09</v>
+        <v>2530.02</v>
       </c>
       <c r="E101" t="n">
-        <v>3402.2</v>
+        <v>618.6</v>
       </c>
       <c r="F101" t="n">
         <v>4.09</v>
@@ -4099,10 +4099,10 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>14081.16</v>
+        <v>2560.21</v>
       </c>
       <c r="E102" t="n">
-        <v>3442.8</v>
+        <v>626</v>
       </c>
       <c r="F102" t="n">
         <v>4.09</v>
@@ -4135,10 +4135,10 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>14529.62</v>
+        <v>2641.75</v>
       </c>
       <c r="E103" t="n">
-        <v>3552.5</v>
+        <v>645.9</v>
       </c>
       <c r="F103" t="n">
         <v>4.09</v>
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>12678.97</v>
+        <v>2305.27</v>
       </c>
       <c r="E104" t="n">
-        <v>4544.4</v>
+        <v>826.3</v>
       </c>
       <c r="F104" t="n">
         <v>2.79</v>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11983.85</v>
+        <v>2178.88</v>
       </c>
       <c r="E105" t="n">
-        <v>4295.3</v>
+        <v>781</v>
       </c>
       <c r="F105" t="n">
         <v>2.79</v>
@@ -4243,10 +4243,10 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>12317.32</v>
+        <v>2239.51</v>
       </c>
       <c r="E106" t="n">
-        <v>4414.8</v>
+        <v>802.7</v>
       </c>
       <c r="F106" t="n">
         <v>2.79</v>
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>31355.5</v>
+        <v>5701</v>
       </c>
       <c r="E107" t="n">
-        <v>6221.3</v>
+        <v>1131.2</v>
       </c>
       <c r="F107" t="n">
         <v>5.04</v>
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>30058.32</v>
+        <v>5465.15</v>
       </c>
       <c r="E108" t="n">
-        <v>5964</v>
+        <v>1084.4</v>
       </c>
       <c r="F108" t="n">
         <v>5.04</v>
@@ -4351,10 +4351,10 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>30600.67</v>
+        <v>5563.76</v>
       </c>
       <c r="E109" t="n">
-        <v>6071.6</v>
+        <v>1103.9</v>
       </c>
       <c r="F109" t="n">
         <v>5.04</v>
@@ -4387,10 +4387,10 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>15247.19</v>
+        <v>2772.22</v>
       </c>
       <c r="E110" t="n">
-        <v>2349.3</v>
+        <v>427.2</v>
       </c>
       <c r="F110" t="n">
         <v>6.49</v>
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>15421</v>
+        <v>2803.82</v>
       </c>
       <c r="E111" t="n">
-        <v>2376.1</v>
+        <v>432</v>
       </c>
       <c r="F111" t="n">
         <v>6.49</v>
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>15057.1</v>
+        <v>2737.65</v>
       </c>
       <c r="E112" t="n">
-        <v>2320</v>
+        <v>421.8</v>
       </c>
       <c r="F112" t="n">
         <v>6.49</v>
@@ -4495,10 +4495,10 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>15854.94</v>
+        <v>2882.72</v>
       </c>
       <c r="E113" t="n">
-        <v>3695.8</v>
+        <v>672</v>
       </c>
       <c r="F113" t="n">
         <v>4.29</v>
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>16720.54</v>
+        <v>3040.1</v>
       </c>
       <c r="E114" t="n">
-        <v>3897.6</v>
+        <v>708.6</v>
       </c>
       <c r="F114" t="n">
         <v>4.29</v>
@@ -4567,10 +4567,10 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>16735.04</v>
+        <v>3042.73</v>
       </c>
       <c r="E115" t="n">
-        <v>3900.9</v>
+        <v>709.3</v>
       </c>
       <c r="F115" t="n">
         <v>4.29</v>
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>14722.88</v>
+        <v>2676.89</v>
       </c>
       <c r="E116" t="n">
-        <v>3599.7</v>
+        <v>654.5</v>
       </c>
       <c r="F116" t="n">
         <v>4.09</v>
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>14877.5</v>
+        <v>2705</v>
       </c>
       <c r="E117" t="n">
-        <v>3637.5</v>
+        <v>661.4</v>
       </c>
       <c r="F117" t="n">
         <v>4.09</v>
@@ -4675,10 +4675,10 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>14610.16</v>
+        <v>2656.39</v>
       </c>
       <c r="E118" t="n">
-        <v>3572.2</v>
+        <v>649.5</v>
       </c>
       <c r="F118" t="n">
         <v>4.09</v>
@@ -4711,10 +4711,10 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>12535.92</v>
+        <v>2279.26</v>
       </c>
       <c r="E119" t="n">
-        <v>4493.2</v>
+        <v>816.9</v>
       </c>
       <c r="F119" t="n">
         <v>2.79</v>
@@ -4747,10 +4747,10 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>12533.88</v>
+        <v>2278.89</v>
       </c>
       <c r="E120" t="n">
-        <v>4492.4</v>
+        <v>816.8</v>
       </c>
       <c r="F120" t="n">
         <v>2.79</v>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>12256.96</v>
+        <v>2228.54</v>
       </c>
       <c r="E121" t="n">
-        <v>4393.2</v>
+        <v>798.8</v>
       </c>
       <c r="F121" t="n">
         <v>2.79</v>
@@ -4819,10 +4819,10 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>12933.71</v>
+        <v>2351.58</v>
       </c>
       <c r="E122" t="n">
-        <v>2056.2</v>
+        <v>373.9</v>
       </c>
       <c r="F122" t="n">
         <v>6.29</v>
@@ -4855,10 +4855,10 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>13611.39</v>
+        <v>2474.8</v>
       </c>
       <c r="E123" t="n">
-        <v>2164</v>
+        <v>393.4</v>
       </c>
       <c r="F123" t="n">
         <v>6.29</v>
@@ -4891,10 +4891,10 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>12909.6</v>
+        <v>2347.2</v>
       </c>
       <c r="E124" t="n">
-        <v>2052.4</v>
+        <v>373.2</v>
       </c>
       <c r="F124" t="n">
         <v>6.29</v>
@@ -4927,10 +4927,10 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>15921.48</v>
+        <v>2894.81</v>
       </c>
       <c r="E125" t="n">
-        <v>2453.2</v>
+        <v>446</v>
       </c>
       <c r="F125" t="n">
         <v>6.49</v>
@@ -4963,10 +4963,10 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>16703.47</v>
+        <v>3037</v>
       </c>
       <c r="E126" t="n">
-        <v>2573.7</v>
+        <v>467.9</v>
       </c>
       <c r="F126" t="n">
         <v>6.49</v>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>15667.72</v>
+        <v>2848.68</v>
       </c>
       <c r="E127" t="n">
-        <v>2414.1</v>
+        <v>438.9</v>
       </c>
       <c r="F127" t="n">
         <v>6.49</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>16059.28</v>
+        <v>2919.87</v>
       </c>
       <c r="E128" t="n">
-        <v>3743.4</v>
+        <v>680.6</v>
       </c>
       <c r="F128" t="n">
         <v>4.29</v>
@@ -5071,10 +5071,10 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>16414.49</v>
+        <v>2984.45</v>
       </c>
       <c r="E129" t="n">
-        <v>3826.2</v>
+        <v>695.7</v>
       </c>
       <c r="F129" t="n">
         <v>4.29</v>
@@ -5107,10 +5107,10 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>16674.62</v>
+        <v>3031.75</v>
       </c>
       <c r="E130" t="n">
-        <v>3886.9</v>
+        <v>706.7</v>
       </c>
       <c r="F130" t="n">
         <v>4.29</v>
@@ -5143,10 +5143,10 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>15128.13</v>
+        <v>2750.57</v>
       </c>
       <c r="E131" t="n">
-        <v>3698.8</v>
+        <v>672.5</v>
       </c>
       <c r="F131" t="n">
         <v>4.09</v>
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>15184.19</v>
+        <v>2760.76</v>
       </c>
       <c r="E132" t="n">
-        <v>3712.5</v>
+        <v>675</v>
       </c>
       <c r="F132" t="n">
         <v>4.09</v>
@@ -5215,10 +5215,10 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>14118.34</v>
+        <v>2566.97</v>
       </c>
       <c r="E133" t="n">
-        <v>3451.9</v>
+        <v>627.6</v>
       </c>
       <c r="F133" t="n">
         <v>4.09</v>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>11920.48</v>
+        <v>2167.36</v>
       </c>
       <c r="E134" t="n">
-        <v>4272.6</v>
+        <v>776.8</v>
       </c>
       <c r="F134" t="n">
         <v>2.79</v>
@@ -5287,10 +5287,10 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>12561.53</v>
+        <v>2283.91</v>
       </c>
       <c r="E135" t="n">
-        <v>4502.3</v>
+        <v>818.6</v>
       </c>
       <c r="F135" t="n">
         <v>2.79</v>
@@ -5323,10 +5323,10 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>12050.74</v>
+        <v>2191.04</v>
       </c>
       <c r="E136" t="n">
-        <v>4319.3</v>
+        <v>785.3</v>
       </c>
       <c r="F136" t="n">
         <v>2.79</v>
@@ -5359,10 +5359,10 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>14365.69</v>
+        <v>2611.94</v>
       </c>
       <c r="E137" t="n">
-        <v>2283.9</v>
+        <v>415.3</v>
       </c>
       <c r="F137" t="n">
         <v>6.29</v>
@@ -5395,10 +5395,10 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>13636.88</v>
+        <v>2479.43</v>
       </c>
       <c r="E138" t="n">
-        <v>2168</v>
+        <v>394.2</v>
       </c>
       <c r="F138" t="n">
         <v>6.29</v>
@@ -5431,10 +5431,10 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>13795.06</v>
+        <v>2508.19</v>
       </c>
       <c r="E139" t="n">
-        <v>2193.2</v>
+        <v>398.8</v>
       </c>
       <c r="F139" t="n">
         <v>6.29</v>
@@ -5467,10 +5467,10 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>15966.09</v>
+        <v>2902.92</v>
       </c>
       <c r="E140" t="n">
-        <v>2460.1</v>
+        <v>447.3</v>
       </c>
       <c r="F140" t="n">
         <v>6.49</v>
@@ -5503,10 +5503,10 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>15486.31</v>
+        <v>2815.69</v>
       </c>
       <c r="E141" t="n">
-        <v>2386.2</v>
+        <v>433.9</v>
       </c>
       <c r="F141" t="n">
         <v>6.49</v>
@@ -5539,10 +5539,10 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>16284.11</v>
+        <v>2960.75</v>
       </c>
       <c r="E142" t="n">
-        <v>2509.1</v>
+        <v>456.2</v>
       </c>
       <c r="F142" t="n">
         <v>6.49</v>
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>16322.71</v>
+        <v>2967.77</v>
       </c>
       <c r="E143" t="n">
-        <v>3804.8</v>
+        <v>691.8</v>
       </c>
       <c r="F143" t="n">
         <v>4.29</v>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>16896.33</v>
+        <v>3072.06</v>
       </c>
       <c r="E144" t="n">
-        <v>3938.5</v>
+        <v>716.1</v>
       </c>
       <c r="F144" t="n">
         <v>4.29</v>
@@ -5647,10 +5647,10 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>16955.34</v>
+        <v>3082.79</v>
       </c>
       <c r="E145" t="n">
-        <v>3952.3</v>
+        <v>718.6</v>
       </c>
       <c r="F145" t="n">
         <v>4.29</v>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>14997.51</v>
+        <v>2726.82</v>
       </c>
       <c r="E146" t="n">
-        <v>3666.9</v>
+        <v>666.7</v>
       </c>
       <c r="F146" t="n">
         <v>4.09</v>
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>14524.27</v>
+        <v>2640.78</v>
       </c>
       <c r="E147" t="n">
-        <v>3551.2</v>
+        <v>645.7</v>
       </c>
       <c r="F147" t="n">
         <v>4.09</v>
@@ -5755,10 +5755,10 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>14413</v>
+        <v>2620.55</v>
       </c>
       <c r="E148" t="n">
-        <v>3524</v>
+        <v>640.7</v>
       </c>
       <c r="F148" t="n">
         <v>4.09</v>
@@ -5791,10 +5791,10 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>12520.36</v>
+        <v>2276.43</v>
       </c>
       <c r="E149" t="n">
-        <v>4487.6</v>
+        <v>815.9</v>
       </c>
       <c r="F149" t="n">
         <v>2.79</v>
@@ -5827,10 +5827,10 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>12571.99</v>
+        <v>2285.82</v>
       </c>
       <c r="E150" t="n">
-        <v>4506.1</v>
+        <v>819.3</v>
       </c>
       <c r="F150" t="n">
         <v>2.79</v>
@@ -5863,10 +5863,10 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>12267.41</v>
+        <v>2230.44</v>
       </c>
       <c r="E151" t="n">
-        <v>4396.9</v>
+        <v>799.4</v>
       </c>
       <c r="F151" t="n">
         <v>2.79</v>
@@ -5899,10 +5899,10 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>14119.42</v>
+        <v>2567.17</v>
       </c>
       <c r="E152" t="n">
-        <v>2244.7</v>
+        <v>408.1</v>
       </c>
       <c r="F152" t="n">
         <v>6.29</v>
@@ -5935,10 +5935,10 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>14949.29</v>
+        <v>2718.05</v>
       </c>
       <c r="E153" t="n">
-        <v>2376.7</v>
+        <v>432.1</v>
       </c>
       <c r="F153" t="n">
         <v>6.29</v>
@@ -5971,10 +5971,10 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>14905.5</v>
+        <v>2710.09</v>
       </c>
       <c r="E154" t="n">
-        <v>2369.7</v>
+        <v>430.9</v>
       </c>
       <c r="F154" t="n">
         <v>6.29</v>
@@ -6007,10 +6007,10 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>16112.79</v>
+        <v>2929.6</v>
       </c>
       <c r="E155" t="n">
-        <v>2482.7</v>
+        <v>451.4</v>
       </c>
       <c r="F155" t="n">
         <v>6.49</v>
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>16472.93</v>
+        <v>2995.08</v>
       </c>
       <c r="E156" t="n">
-        <v>2538.2</v>
+        <v>461.5</v>
       </c>
       <c r="F156" t="n">
         <v>6.49</v>
@@ -6079,10 +6079,10 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>15539.43</v>
+        <v>2825.35</v>
       </c>
       <c r="E157" t="n">
-        <v>2394.4</v>
+        <v>435.3</v>
       </c>
       <c r="F157" t="n">
         <v>6.49</v>
@@ -6115,10 +6115,10 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>16377.08</v>
+        <v>2977.65</v>
       </c>
       <c r="E158" t="n">
-        <v>3817.5</v>
+        <v>694.1</v>
       </c>
       <c r="F158" t="n">
         <v>4.29</v>
@@ -6151,10 +6151,10 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>16830.71</v>
+        <v>3060.13</v>
       </c>
       <c r="E159" t="n">
-        <v>3923.2</v>
+        <v>713.3</v>
       </c>
       <c r="F159" t="n">
         <v>4.29</v>
@@ -6187,10 +6187,10 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>16196.02</v>
+        <v>2944.73</v>
       </c>
       <c r="E160" t="n">
-        <v>3775.3</v>
+        <v>686.4</v>
       </c>
       <c r="F160" t="n">
         <v>4.29</v>
@@ -6223,10 +6223,10 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>14916.91</v>
+        <v>2712.17</v>
       </c>
       <c r="E161" t="n">
-        <v>3647.2</v>
+        <v>663.1</v>
       </c>
       <c r="F161" t="n">
         <v>4.09</v>
@@ -6259,10 +6259,10 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>14626.64</v>
+        <v>2659.39</v>
       </c>
       <c r="E162" t="n">
-        <v>3576.2</v>
+        <v>650.2</v>
       </c>
       <c r="F162" t="n">
         <v>4.09</v>
@@ -6295,10 +6295,10 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>14914.5</v>
+        <v>2711.73</v>
       </c>
       <c r="E163" t="n">
-        <v>3646.6</v>
+        <v>663</v>
       </c>
       <c r="F163" t="n">
         <v>4.09</v>
@@ -6331,10 +6331,10 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>12241.31</v>
+        <v>2225.69</v>
       </c>
       <c r="E164" t="n">
-        <v>4387.6</v>
+        <v>797.7</v>
       </c>
       <c r="F164" t="n">
         <v>2.79</v>
@@ -6367,10 +6367,10 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>12146.27</v>
+        <v>2208.41</v>
       </c>
       <c r="E165" t="n">
-        <v>4353.5</v>
+        <v>791.5</v>
       </c>
       <c r="F165" t="n">
         <v>2.79</v>
@@ -6403,10 +6403,10 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>12000.22</v>
+        <v>2181.86</v>
       </c>
       <c r="E166" t="n">
-        <v>4301.2</v>
+        <v>782</v>
       </c>
       <c r="F166" t="n">
         <v>2.79</v>
@@ -6439,10 +6439,10 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>15497.71</v>
+        <v>2817.77</v>
       </c>
       <c r="E167" t="n">
-        <v>2463.9</v>
+        <v>448</v>
       </c>
       <c r="F167" t="n">
         <v>6.29</v>
@@ -6475,10 +6475,10 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>14678.38</v>
+        <v>2668.8</v>
       </c>
       <c r="E168" t="n">
-        <v>2333.6</v>
+        <v>424.3</v>
       </c>
       <c r="F168" t="n">
         <v>6.29</v>
@@ -6511,10 +6511,10 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>14712.69</v>
+        <v>2675.03</v>
       </c>
       <c r="E169" t="n">
-        <v>2339.1</v>
+        <v>425.3</v>
       </c>
       <c r="F169" t="n">
         <v>6.29</v>
@@ -6547,10 +6547,10 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>16263.31</v>
+        <v>2956.97</v>
       </c>
       <c r="E170" t="n">
-        <v>2505.9</v>
+        <v>455.6</v>
       </c>
       <c r="F170" t="n">
         <v>6.49</v>
@@ -6583,10 +6583,10 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>15791.72</v>
+        <v>2871.22</v>
       </c>
       <c r="E171" t="n">
-        <v>2433.2</v>
+        <v>442.4</v>
       </c>
       <c r="F171" t="n">
         <v>6.49</v>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>16364.38</v>
+        <v>2975.34</v>
       </c>
       <c r="E172" t="n">
-        <v>2521.5</v>
+        <v>458.5</v>
       </c>
       <c r="F172" t="n">
         <v>6.49</v>
@@ -6655,10 +6655,10 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>16604.26</v>
+        <v>3018.96</v>
       </c>
       <c r="E173" t="n">
-        <v>3870.5</v>
+        <v>703.7</v>
       </c>
       <c r="F173" t="n">
         <v>4.29</v>
@@ -6691,10 +6691,10 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>16583.77</v>
+        <v>3015.23</v>
       </c>
       <c r="E174" t="n">
-        <v>3865.7</v>
+        <v>702.9</v>
       </c>
       <c r="F174" t="n">
         <v>4.29</v>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>16950.62</v>
+        <v>3081.93</v>
       </c>
       <c r="E175" t="n">
-        <v>3951.2</v>
+        <v>718.4</v>
       </c>
       <c r="F175" t="n">
         <v>4.29</v>
@@ -6763,10 +6763,10 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>14868.02</v>
+        <v>2703.28</v>
       </c>
       <c r="E176" t="n">
-        <v>3635.2</v>
+        <v>660.9</v>
       </c>
       <c r="F176" t="n">
         <v>4.09</v>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>14067.97</v>
+        <v>2557.81</v>
       </c>
       <c r="E177" t="n">
-        <v>3439.6</v>
+        <v>625.4</v>
       </c>
       <c r="F177" t="n">
         <v>4.09</v>
@@ -6835,10 +6835,10 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>14094.73</v>
+        <v>2562.68</v>
       </c>
       <c r="E178" t="n">
-        <v>3446.1</v>
+        <v>626.6</v>
       </c>
       <c r="F178" t="n">
         <v>4.09</v>
@@ -6871,10 +6871,10 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>12375.74</v>
+        <v>2250.13</v>
       </c>
       <c r="E179" t="n">
-        <v>4435.7</v>
+        <v>806.5</v>
       </c>
       <c r="F179" t="n">
         <v>2.79</v>
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>12262.44</v>
+        <v>2229.53</v>
       </c>
       <c r="E180" t="n">
-        <v>4395.1</v>
+        <v>799.1</v>
       </c>
       <c r="F180" t="n">
         <v>2.79</v>
@@ -6943,10 +6943,10 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>12040.48</v>
+        <v>2189.18</v>
       </c>
       <c r="E181" t="n">
-        <v>4315.6</v>
+        <v>784.7</v>
       </c>
       <c r="F181" t="n">
         <v>2.79</v>
@@ -6979,10 +6979,10 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>15159.2</v>
+        <v>2756.22</v>
       </c>
       <c r="E182" t="n">
-        <v>2410</v>
+        <v>438.2</v>
       </c>
       <c r="F182" t="n">
         <v>6.29</v>
@@ -7015,10 +7015,10 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>16053.79</v>
+        <v>2918.87</v>
       </c>
       <c r="E183" t="n">
-        <v>2552.3</v>
+        <v>464</v>
       </c>
       <c r="F183" t="n">
         <v>6.29</v>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>15530.33</v>
+        <v>2823.7</v>
       </c>
       <c r="E184" t="n">
-        <v>2469.1</v>
+        <v>448.9</v>
       </c>
       <c r="F184" t="n">
         <v>6.29</v>
@@ -7087,10 +7087,10 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>16032.03</v>
+        <v>2914.91</v>
       </c>
       <c r="E185" t="n">
-        <v>2470.3</v>
+        <v>449.1</v>
       </c>
       <c r="F185" t="n">
         <v>6.49</v>
@@ -7123,10 +7123,10 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>16622.43</v>
+        <v>3022.26</v>
       </c>
       <c r="E186" t="n">
-        <v>2561.2</v>
+        <v>465.7</v>
       </c>
       <c r="F186" t="n">
         <v>6.49</v>
@@ -7159,10 +7159,10 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>15496.68</v>
+        <v>2817.58</v>
       </c>
       <c r="E187" t="n">
-        <v>2387.8</v>
+        <v>434.1</v>
       </c>
       <c r="F187" t="n">
         <v>6.49</v>
@@ -7195,10 +7195,10 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>16140.16</v>
+        <v>2934.57</v>
       </c>
       <c r="E188" t="n">
-        <v>3762.3</v>
+        <v>684</v>
       </c>
       <c r="F188" t="n">
         <v>4.29</v>
@@ -7231,10 +7231,10 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>16629.83</v>
+        <v>3023.61</v>
       </c>
       <c r="E189" t="n">
-        <v>3876.4</v>
+        <v>704.8</v>
       </c>
       <c r="F189" t="n">
         <v>4.29</v>
@@ -7267,10 +7267,10 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>16114.14</v>
+        <v>2929.84</v>
       </c>
       <c r="E190" t="n">
-        <v>3756.2</v>
+        <v>682.9</v>
       </c>
       <c r="F190" t="n">
         <v>4.29</v>
@@ -7303,10 +7303,10 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>14831.75</v>
+        <v>2696.68</v>
       </c>
       <c r="E191" t="n">
-        <v>3626.3</v>
+        <v>659.3</v>
       </c>
       <c r="F191" t="n">
         <v>4.09</v>
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>14287.31</v>
+        <v>2597.69</v>
       </c>
       <c r="E192" t="n">
-        <v>3493.2</v>
+        <v>635.1</v>
       </c>
       <c r="F192" t="n">
         <v>4.09</v>
@@ -7375,10 +7375,10 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>14152.87</v>
+        <v>2573.25</v>
       </c>
       <c r="E193" t="n">
-        <v>3460.4</v>
+        <v>629.2</v>
       </c>
       <c r="F193" t="n">
         <v>4.09</v>
@@ -7411,10 +7411,10 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>11988.24</v>
+        <v>2179.68</v>
       </c>
       <c r="E194" t="n">
-        <v>4296.9</v>
+        <v>781.2</v>
       </c>
       <c r="F194" t="n">
         <v>2.79</v>
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>12200.12</v>
+        <v>2218.2</v>
       </c>
       <c r="E195" t="n">
-        <v>4372.8</v>
+        <v>795.1</v>
       </c>
       <c r="F195" t="n">
         <v>2.79</v>
@@ -7483,10 +7483,10 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>11957.94</v>
+        <v>2174.17</v>
       </c>
       <c r="E196" t="n">
-        <v>4286</v>
+        <v>779.3</v>
       </c>
       <c r="F196" t="n">
         <v>2.79</v>
@@ -7519,10 +7519,10 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>15600.17</v>
+        <v>2836.4</v>
       </c>
       <c r="E197" t="n">
-        <v>2480.2</v>
+        <v>450.9</v>
       </c>
       <c r="F197" t="n">
         <v>6.29</v>
@@ -7555,10 +7555,10 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>16540.17</v>
+        <v>3007.3</v>
       </c>
       <c r="E198" t="n">
-        <v>2629.6</v>
+        <v>478.1</v>
       </c>
       <c r="F198" t="n">
         <v>6.29</v>
@@ -7591,10 +7591,10 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>16413.91</v>
+        <v>2984.35</v>
       </c>
       <c r="E199" t="n">
-        <v>2609.5</v>
+        <v>474.5</v>
       </c>
       <c r="F199" t="n">
         <v>6.29</v>
@@ -7627,10 +7627,10 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>16473.71</v>
+        <v>2995.22</v>
       </c>
       <c r="E200" t="n">
-        <v>2538.3</v>
+        <v>461.5</v>
       </c>
       <c r="F200" t="n">
         <v>6.49</v>
@@ -7663,10 +7663,10 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>16096.24</v>
+        <v>2926.59</v>
       </c>
       <c r="E201" t="n">
-        <v>2480.2</v>
+        <v>450.9</v>
       </c>
       <c r="F201" t="n">
         <v>6.49</v>
@@ -7699,10 +7699,10 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>16700.99</v>
+        <v>3036.54</v>
       </c>
       <c r="E202" t="n">
-        <v>2573.3</v>
+        <v>467.9</v>
       </c>
       <c r="F202" t="n">
         <v>6.49</v>
@@ -7735,10 +7735,10 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>15914.21</v>
+        <v>2893.49</v>
       </c>
       <c r="E203" t="n">
-        <v>3709.6</v>
+        <v>674.5</v>
       </c>
       <c r="F203" t="n">
         <v>4.29</v>
@@ -7771,10 +7771,10 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>16386.04</v>
+        <v>2979.28</v>
       </c>
       <c r="E204" t="n">
-        <v>3819.6</v>
+        <v>694.5</v>
       </c>
       <c r="F204" t="n">
         <v>4.29</v>
@@ -7807,10 +7807,10 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>16283.86</v>
+        <v>2960.7</v>
       </c>
       <c r="E205" t="n">
-        <v>3795.8</v>
+        <v>690.1</v>
       </c>
       <c r="F205" t="n">
         <v>4.29</v>
@@ -7843,10 +7843,10 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>15146.55</v>
+        <v>2753.92</v>
       </c>
       <c r="E206" t="n">
-        <v>3703.3</v>
+        <v>673.3</v>
       </c>
       <c r="F206" t="n">
         <v>4.09</v>
@@ -7879,10 +7879,10 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>14711.66</v>
+        <v>2674.85</v>
       </c>
       <c r="E207" t="n">
-        <v>3597</v>
+        <v>654</v>
       </c>
       <c r="F207" t="n">
         <v>4.09</v>
@@ -7915,10 +7915,10 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>14979.91</v>
+        <v>2723.62</v>
       </c>
       <c r="E208" t="n">
-        <v>3662.6</v>
+        <v>665.9</v>
       </c>
       <c r="F208" t="n">
         <v>4.09</v>
@@ -7951,10 +7951,10 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>11952.25</v>
+        <v>2173.14</v>
       </c>
       <c r="E209" t="n">
-        <v>4284</v>
+        <v>778.9</v>
       </c>
       <c r="F209" t="n">
         <v>2.79</v>
@@ -7987,10 +7987,10 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>12746.06</v>
+        <v>2317.46</v>
       </c>
       <c r="E210" t="n">
-        <v>4568.5</v>
+        <v>830.6</v>
       </c>
       <c r="F210" t="n">
         <v>2.79</v>
@@ -8023,10 +8023,10 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>12274.66</v>
+        <v>2231.76</v>
       </c>
       <c r="E211" t="n">
-        <v>4399.5</v>
+        <v>799.9</v>
       </c>
       <c r="F211" t="n">
         <v>2.79</v>
@@ -8059,10 +8059,10 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>17172.54</v>
+        <v>3122.28</v>
       </c>
       <c r="E212" t="n">
-        <v>2730.1</v>
+        <v>496.4</v>
       </c>
       <c r="F212" t="n">
         <v>6.29</v>
@@ -8095,10 +8095,10 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>17180.53</v>
+        <v>3123.73</v>
       </c>
       <c r="E213" t="n">
-        <v>2731.4</v>
+        <v>496.6</v>
       </c>
       <c r="F213" t="n">
         <v>6.29</v>
@@ -8131,10 +8131,10 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>16461.45</v>
+        <v>2992.99</v>
       </c>
       <c r="E214" t="n">
-        <v>2617.1</v>
+        <v>475.8</v>
       </c>
       <c r="F214" t="n">
         <v>6.29</v>
@@ -8167,10 +8167,10 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>15843.35</v>
+        <v>2880.61</v>
       </c>
       <c r="E215" t="n">
-        <v>2441.2</v>
+        <v>443.9</v>
       </c>
       <c r="F215" t="n">
         <v>6.49</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>15999.84</v>
+        <v>2909.06</v>
       </c>
       <c r="E216" t="n">
-        <v>2465.3</v>
+        <v>448.2</v>
       </c>
       <c r="F216" t="n">
         <v>6.49</v>
@@ -8239,10 +8239,10 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>16150.05</v>
+        <v>2936.37</v>
       </c>
       <c r="E217" t="n">
-        <v>2488.5</v>
+        <v>452.4</v>
       </c>
       <c r="F217" t="n">
         <v>6.49</v>
@@ -8275,10 +8275,10 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>16466.05</v>
+        <v>2993.83</v>
       </c>
       <c r="E218" t="n">
-        <v>3838.2</v>
+        <v>697.9</v>
       </c>
       <c r="F218" t="n">
         <v>4.29</v>
@@ -8311,10 +8311,10 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>16726.26</v>
+        <v>3041.14</v>
       </c>
       <c r="E219" t="n">
-        <v>3898.9</v>
+        <v>708.9</v>
       </c>
       <c r="F219" t="n">
         <v>4.29</v>
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>16588.38</v>
+        <v>3016.07</v>
       </c>
       <c r="E220" t="n">
-        <v>3866.8</v>
+        <v>703</v>
       </c>
       <c r="F220" t="n">
         <v>4.29</v>
@@ -8383,10 +8383,10 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>14412.03</v>
+        <v>2620.37</v>
       </c>
       <c r="E221" t="n">
-        <v>3523.7</v>
+        <v>640.7</v>
       </c>
       <c r="F221" t="n">
         <v>4.09</v>
@@ -8419,10 +8419,10 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>14441.3</v>
+        <v>2625.69</v>
       </c>
       <c r="E222" t="n">
-        <v>3530.9</v>
+        <v>642</v>
       </c>
       <c r="F222" t="n">
         <v>4.09</v>
@@ -8455,10 +8455,10 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>14479.74</v>
+        <v>2632.68</v>
       </c>
       <c r="E223" t="n">
-        <v>3540.3</v>
+        <v>643.7</v>
       </c>
       <c r="F223" t="n">
         <v>4.09</v>
@@ -8491,10 +8491,10 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>11877.9</v>
+        <v>2159.62</v>
       </c>
       <c r="E224" t="n">
-        <v>4257.3</v>
+        <v>774.1</v>
       </c>
       <c r="F224" t="n">
         <v>2.79</v>
@@ -8527,10 +8527,10 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>11948.05</v>
+        <v>2172.37</v>
       </c>
       <c r="E225" t="n">
-        <v>4282.5</v>
+        <v>778.6</v>
       </c>
       <c r="F225" t="n">
         <v>2.79</v>
@@ -8563,10 +8563,10 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>12495.12</v>
+        <v>2271.84</v>
       </c>
       <c r="E226" t="n">
-        <v>4478.5</v>
+        <v>814.3</v>
       </c>
       <c r="F226" t="n">
         <v>2.79</v>
@@ -8599,10 +8599,10 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>16658.93</v>
+        <v>3028.9</v>
       </c>
       <c r="E227" t="n">
-        <v>2648.5</v>
+        <v>481.5</v>
       </c>
       <c r="F227" t="n">
         <v>6.29</v>
@@ -8635,10 +8635,10 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>17547.16</v>
+        <v>3190.39</v>
       </c>
       <c r="E228" t="n">
-        <v>2789.7</v>
+        <v>507.2</v>
       </c>
       <c r="F228" t="n">
         <v>6.29</v>
@@ -8671,10 +8671,10 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>17384.22</v>
+        <v>3160.77</v>
       </c>
       <c r="E229" t="n">
-        <v>2763.8</v>
+        <v>502.5</v>
       </c>
       <c r="F229" t="n">
         <v>6.29</v>
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>15454.33</v>
+        <v>2809.88</v>
       </c>
       <c r="E230" t="n">
-        <v>2381.3</v>
+        <v>433</v>
       </c>
       <c r="F230" t="n">
         <v>6.49</v>
@@ -8743,10 +8743,10 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>16375.6</v>
+        <v>2977.38</v>
       </c>
       <c r="E231" t="n">
-        <v>2523.2</v>
+        <v>458.8</v>
       </c>
       <c r="F231" t="n">
         <v>6.49</v>
@@ -8779,10 +8779,10 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>16515.26</v>
+        <v>3002.78</v>
       </c>
       <c r="E232" t="n">
-        <v>2544.7</v>
+        <v>462.7</v>
       </c>
       <c r="F232" t="n">
         <v>6.49</v>
@@ -8815,10 +8815,10 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>16511.77</v>
+        <v>3002.14</v>
       </c>
       <c r="E233" t="n">
-        <v>3848.9</v>
+        <v>699.8</v>
       </c>
       <c r="F233" t="n">
         <v>4.29</v>
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>16471.25</v>
+        <v>2994.77</v>
       </c>
       <c r="E234" t="n">
-        <v>3839.5</v>
+        <v>698.1</v>
       </c>
       <c r="F234" t="n">
         <v>4.29</v>
@@ -8887,10 +8887,10 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>15863.07</v>
+        <v>2884.19</v>
       </c>
       <c r="E235" t="n">
-        <v>3697.7</v>
+        <v>672.3</v>
       </c>
       <c r="F235" t="n">
         <v>4.29</v>
@@ -8923,10 +8923,10 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>14957.06</v>
+        <v>2719.46</v>
       </c>
       <c r="E236" t="n">
-        <v>3657</v>
+        <v>664.9</v>
       </c>
       <c r="F236" t="n">
         <v>4.09</v>
@@ -8959,10 +8959,10 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>14423.73</v>
+        <v>2622.5</v>
       </c>
       <c r="E237" t="n">
-        <v>3526.6</v>
+        <v>641.2</v>
       </c>
       <c r="F237" t="n">
         <v>4.09</v>
@@ -8995,10 +8995,10 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>15064.8</v>
+        <v>2739.06</v>
       </c>
       <c r="E238" t="n">
-        <v>3683.3</v>
+        <v>669.7</v>
       </c>
       <c r="F238" t="n">
         <v>4.09</v>
@@ -9031,10 +9031,10 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>12151.34</v>
+        <v>2209.33</v>
       </c>
       <c r="E239" t="n">
-        <v>4355.3</v>
+        <v>791.9</v>
       </c>
       <c r="F239" t="n">
         <v>2.79</v>
@@ -9067,10 +9067,10 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>12339.91</v>
+        <v>2243.62</v>
       </c>
       <c r="E240" t="n">
-        <v>4422.9</v>
+        <v>804.2</v>
       </c>
       <c r="F240" t="n">
         <v>2.79</v>
@@ -9103,10 +9103,10 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>12050.46</v>
+        <v>2190.99</v>
       </c>
       <c r="E241" t="n">
-        <v>4319.2</v>
+        <v>785.3</v>
       </c>
       <c r="F241" t="n">
         <v>2.79</v>

--- a/stella/test_fixtures/pantry_loaded/iri_data.xlsx
+++ b/stella/test_fixtures/pantry_loaded/iri_data.xlsx
@@ -508,10 +508,10 @@
         <v>6.29</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0725</v>
+        <v>0.0746</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0519</v>
+        <v>0.0534</v>
       </c>
       <c r="I2" t="n">
         <v>90</v>
@@ -544,10 +544,10 @@
         <v>6.29</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.0755</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0553</v>
+        <v>0.054</v>
       </c>
       <c r="I3" t="n">
         <v>90</v>
@@ -580,10 +580,10 @@
         <v>6.29</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0771</v>
+        <v>0.0755</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0552</v>
+        <v>0.054</v>
       </c>
       <c r="I4" t="n">
         <v>90</v>
@@ -616,10 +616,10 @@
         <v>6.49</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0712</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0494</v>
+        <v>0.0486</v>
       </c>
       <c r="I5" t="n">
         <v>92</v>
@@ -652,10 +652,10 @@
         <v>6.49</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0673</v>
+        <v>0.0693</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0467</v>
+        <v>0.0481</v>
       </c>
       <c r="I6" t="n">
         <v>90</v>
@@ -688,10 +688,10 @@
         <v>6.49</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0679</v>
+        <v>0.0694</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0471</v>
+        <v>0.0482</v>
       </c>
       <c r="I7" t="n">
         <v>89</v>
@@ -724,10 +724,10 @@
         <v>4.29</v>
       </c>
       <c r="G8" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0765</v>
+        <v>0.0755</v>
       </c>
       <c r="I8" t="n">
         <v>89</v>
@@ -760,10 +760,10 @@
         <v>4.29</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0688</v>
+        <v>0.0712</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0722</v>
+        <v>0.0747</v>
       </c>
       <c r="I9" t="n">
         <v>89</v>
@@ -796,10 +796,10 @@
         <v>4.29</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0742</v>
+        <v>0.0722</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0779</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="I10" t="n">
         <v>88</v>
@@ -832,10 +832,10 @@
         <v>4.09</v>
       </c>
       <c r="G11" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.0633</v>
       </c>
       <c r="H11" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0697</v>
       </c>
       <c r="I11" t="n">
         <v>88</v>
@@ -868,10 +868,10 @@
         <v>4.09</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0644</v>
+        <v>0.0636</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0709</v>
+        <v>0.0701</v>
       </c>
       <c r="I12" t="n">
         <v>91</v>
@@ -904,10 +904,10 @@
         <v>4.09</v>
       </c>
       <c r="G13" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.0638</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0718</v>
+        <v>0.0702</v>
       </c>
       <c r="I13" t="n">
         <v>89</v>
@@ -940,10 +940,10 @@
         <v>2.79</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0527</v>
+        <v>0.0532</v>
       </c>
       <c r="H14" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.0858</v>
       </c>
       <c r="I14" t="n">
         <v>92</v>
@@ -976,10 +976,10 @@
         <v>2.79</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0524</v>
+        <v>0.0531</v>
       </c>
       <c r="H15" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.0857</v>
       </c>
       <c r="I15" t="n">
         <v>89</v>
@@ -1012,10 +1012,10 @@
         <v>2.79</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0536</v>
+        <v>0.0534</v>
       </c>
       <c r="H16" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.0861</v>
       </c>
       <c r="I16" t="n">
         <v>88</v>
@@ -1048,10 +1048,10 @@
         <v>6.29</v>
       </c>
       <c r="G17" t="n">
-        <v>0.077</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0552</v>
+        <v>0.054</v>
       </c>
       <c r="I17" t="n">
         <v>89</v>
@@ -1084,10 +1084,10 @@
         <v>6.29</v>
       </c>
       <c r="G18" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0756</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0557</v>
+        <v>0.0541</v>
       </c>
       <c r="I18" t="n">
         <v>91</v>
@@ -1120,10 +1120,10 @@
         <v>6.29</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0741</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0531</v>
+        <v>0.0536</v>
       </c>
       <c r="I19" t="n">
         <v>92</v>
@@ -1156,10 +1156,10 @@
         <v>6.49</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0684</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0475</v>
+        <v>0.0482</v>
       </c>
       <c r="I20" t="n">
         <v>92</v>
@@ -1192,10 +1192,10 @@
         <v>6.49</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0683</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0475</v>
+        <v>0.0482</v>
       </c>
       <c r="I21" t="n">
         <v>92</v>
@@ -1228,10 +1228,10 @@
         <v>6.49</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0702</v>
+        <v>0.0698</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0488</v>
+        <v>0.0485</v>
       </c>
       <c r="I22" t="n">
         <v>92</v>
@@ -1264,10 +1264,10 @@
         <v>4.29</v>
       </c>
       <c r="G23" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0717</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0755</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="I23" t="n">
         <v>92</v>
@@ -1300,10 +1300,10 @@
         <v>4.29</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0707</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0743</v>
+        <v>0.0751</v>
       </c>
       <c r="I24" t="n">
         <v>88</v>
@@ -1336,10 +1336,10 @@
         <v>4.29</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0694</v>
+        <v>0.0713</v>
       </c>
       <c r="H25" t="n">
-        <v>0.073</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="I25" t="n">
         <v>88</v>
@@ -1372,10 +1372,10 @@
         <v>4.09</v>
       </c>
       <c r="G26" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.0635</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0702</v>
+        <v>0.0699</v>
       </c>
       <c r="I26" t="n">
         <v>89</v>
@@ -1408,10 +1408,10 @@
         <v>4.09</v>
       </c>
       <c r="G27" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.064</v>
       </c>
       <c r="H27" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.0704</v>
       </c>
       <c r="I27" t="n">
         <v>90</v>
@@ -1444,10 +1444,10 @@
         <v>4.09</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0646</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0712</v>
+        <v>0.0701</v>
       </c>
       <c r="I28" t="n">
         <v>88</v>
@@ -1480,10 +1480,10 @@
         <v>2.79</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0535</v>
+        <v>0.0533</v>
       </c>
       <c r="H29" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.0861</v>
       </c>
       <c r="I29" t="n">
         <v>92</v>
@@ -1516,10 +1516,10 @@
         <v>2.79</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0519</v>
+        <v>0.053</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0838</v>
+        <v>0.0856</v>
       </c>
       <c r="I30" t="n">
         <v>91</v>
@@ -1552,10 +1552,10 @@
         <v>2.79</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0525</v>
+        <v>0.0532</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0848</v>
+        <v>0.0858</v>
       </c>
       <c r="I31" t="n">
         <v>90</v>
@@ -1588,10 +1588,10 @@
         <v>6.29</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0732</v>
+        <v>0.0747</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0523</v>
+        <v>0.0535</v>
       </c>
       <c r="I32" t="n">
         <v>88</v>
@@ -1624,10 +1624,10 @@
         <v>6.29</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0737</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0527</v>
+        <v>0.0536</v>
       </c>
       <c r="I33" t="n">
         <v>89</v>
@@ -1660,10 +1660,10 @@
         <v>6.29</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0731</v>
+        <v>0.0747</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0523</v>
+        <v>0.0535</v>
       </c>
       <c r="I34" t="n">
         <v>92</v>
@@ -1696,10 +1696,10 @@
         <v>6.49</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0718</v>
+        <v>0.0701</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0497</v>
+        <v>0.0486</v>
       </c>
       <c r="I35" t="n">
         <v>88</v>
@@ -1732,10 +1732,10 @@
         <v>6.49</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0703</v>
+        <v>0.0698</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0487</v>
+        <v>0.0484</v>
       </c>
       <c r="I36" t="n">
         <v>90</v>
@@ -1768,10 +1768,10 @@
         <v>6.49</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0711</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0493</v>
+        <v>0.0485</v>
       </c>
       <c r="I37" t="n">
         <v>90</v>
@@ -1804,10 +1804,10 @@
         <v>4.29</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0706</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="H38" t="n">
-        <v>0.074</v>
+        <v>0.075</v>
       </c>
       <c r="I38" t="n">
         <v>89</v>
@@ -1840,10 +1840,10 @@
         <v>4.29</v>
       </c>
       <c r="G39" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.0716</v>
       </c>
       <c r="H39" t="n">
-        <v>0.0745</v>
+        <v>0.0751</v>
       </c>
       <c r="I39" t="n">
         <v>91</v>
@@ -1876,10 +1876,10 @@
         <v>4.29</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0712</v>
+        <v>0.0716</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0747</v>
+        <v>0.0752</v>
       </c>
       <c r="I40" t="n">
         <v>92</v>
@@ -1912,10 +1912,10 @@
         <v>4.09</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0649</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="H41" t="n">
-        <v>0.0713</v>
+        <v>0.0701</v>
       </c>
       <c r="I41" t="n">
         <v>92</v>
@@ -1948,10 +1948,10 @@
         <v>4.09</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0649</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="I42" t="n">
         <v>89</v>
@@ -1984,10 +1984,10 @@
         <v>4.09</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0621</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0682</v>
+        <v>0.0696</v>
       </c>
       <c r="I43" t="n">
         <v>90</v>
@@ -2020,10 +2020,10 @@
         <v>2.79</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0552</v>
+        <v>0.0537</v>
       </c>
       <c r="H44" t="n">
-        <v>0.089</v>
+        <v>0.0866</v>
       </c>
       <c r="I44" t="n">
         <v>89</v>
@@ -2056,10 +2056,10 @@
         <v>2.79</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0517</v>
+        <v>0.053</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0834</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="I45" t="n">
         <v>89</v>
@@ -2092,10 +2092,10 @@
         <v>2.79</v>
       </c>
       <c r="G46" t="n">
-        <v>0.055</v>
+        <v>0.0536</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0887</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="I46" t="n">
         <v>88</v>
@@ -2128,10 +2128,10 @@
         <v>6.29</v>
       </c>
       <c r="G47" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.0755</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0554</v>
+        <v>0.0541</v>
       </c>
       <c r="I47" t="n">
         <v>89</v>
@@ -2164,10 +2164,10 @@
         <v>6.29</v>
       </c>
       <c r="G48" t="n">
-        <v>0.077</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="H48" t="n">
-        <v>0.0552</v>
+        <v>0.054</v>
       </c>
       <c r="I48" t="n">
         <v>89</v>
@@ -2200,10 +2200,10 @@
         <v>6.29</v>
       </c>
       <c r="G49" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0547</v>
+        <v>0.0539</v>
       </c>
       <c r="I49" t="n">
         <v>88</v>
@@ -2236,10 +2236,10 @@
         <v>6.49</v>
       </c>
       <c r="G50" t="n">
-        <v>0.0694</v>
+        <v>0.0697</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0483</v>
+        <v>0.0484</v>
       </c>
       <c r="I50" t="n">
         <v>88</v>
@@ -2272,10 +2272,10 @@
         <v>6.49</v>
       </c>
       <c r="G51" t="n">
-        <v>0.0693</v>
+        <v>0.0697</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0482</v>
+        <v>0.0483</v>
       </c>
       <c r="I51" t="n">
         <v>92</v>
@@ -2308,10 +2308,10 @@
         <v>6.49</v>
       </c>
       <c r="G52" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.0697</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0483</v>
+        <v>0.0484</v>
       </c>
       <c r="I52" t="n">
         <v>89</v>
@@ -2344,10 +2344,10 @@
         <v>4.29</v>
       </c>
       <c r="G53" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.0717</v>
       </c>
       <c r="H53" t="n">
-        <v>0.0752</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="I53" t="n">
         <v>91</v>
@@ -2380,10 +2380,10 @@
         <v>4.29</v>
       </c>
       <c r="G54" t="n">
-        <v>0.0709</v>
+        <v>0.0716</v>
       </c>
       <c r="H54" t="n">
-        <v>0.0746</v>
+        <v>0.0751</v>
       </c>
       <c r="I54" t="n">
         <v>90</v>
@@ -2416,10 +2416,10 @@
         <v>4.29</v>
       </c>
       <c r="G55" t="n">
-        <v>0.0692</v>
+        <v>0.0713</v>
       </c>
       <c r="H55" t="n">
-        <v>0.0728</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="I55" t="n">
         <v>90</v>
@@ -2452,10 +2452,10 @@
         <v>4.09</v>
       </c>
       <c r="G56" t="n">
-        <v>0.0612</v>
+        <v>0.0631</v>
       </c>
       <c r="H56" t="n">
-        <v>0.0675</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="I56" t="n">
         <v>90</v>
@@ -2488,10 +2488,10 @@
         <v>4.09</v>
       </c>
       <c r="G57" t="n">
-        <v>0.0654</v>
+        <v>0.0638</v>
       </c>
       <c r="H57" t="n">
-        <v>0.0721</v>
+        <v>0.0703</v>
       </c>
       <c r="I57" t="n">
         <v>88</v>
@@ -2524,10 +2524,10 @@
         <v>4.09</v>
       </c>
       <c r="G58" t="n">
-        <v>0.063</v>
+        <v>0.0634</v>
       </c>
       <c r="H58" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.0698</v>
       </c>
       <c r="I58" t="n">
         <v>92</v>
@@ -2560,10 +2560,10 @@
         <v>2.79</v>
       </c>
       <c r="G59" t="n">
-        <v>0.0549</v>
+        <v>0.0536</v>
       </c>
       <c r="H59" t="n">
-        <v>0.0888</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="I59" t="n">
         <v>92</v>
@@ -2596,10 +2596,10 @@
         <v>2.79</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0516</v>
+        <v>0.053</v>
       </c>
       <c r="H60" t="n">
-        <v>0.0834</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="I60" t="n">
         <v>91</v>
@@ -2632,7 +2632,7 @@
         <v>2.79</v>
       </c>
       <c r="G61" t="n">
-        <v>0.0532</v>
+        <v>0.0533</v>
       </c>
       <c r="H61" t="n">
         <v>0.08599999999999999</v>
@@ -2668,10 +2668,10 @@
         <v>5.04</v>
       </c>
       <c r="G62" t="n">
-        <v>0.1114</v>
+        <v>0.0825</v>
       </c>
       <c r="H62" t="n">
-        <v>0.0974</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="I62" t="n">
         <v>89</v>
@@ -2704,10 +2704,10 @@
         <v>5.04</v>
       </c>
       <c r="G63" t="n">
-        <v>0.1184</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1035</v>
+        <v>0.0641</v>
       </c>
       <c r="I63" t="n">
         <v>87</v>
@@ -2740,10 +2740,10 @@
         <v>5.04</v>
       </c>
       <c r="G64" t="n">
-        <v>0.1131</v>
+        <v>0.0829</v>
       </c>
       <c r="H64" t="n">
-        <v>0.0989</v>
+        <v>0.0631</v>
       </c>
       <c r="I64" t="n">
         <v>90</v>
@@ -2776,10 +2776,10 @@
         <v>6.49</v>
       </c>
       <c r="G65" t="n">
-        <v>0.0553</v>
+        <v>0.0668</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0375</v>
+        <v>0.0461</v>
       </c>
       <c r="I65" t="n">
         <v>88</v>
@@ -2812,10 +2812,10 @@
         <v>6.49</v>
       </c>
       <c r="G66" t="n">
-        <v>0.0566</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="H66" t="n">
-        <v>0.0384</v>
+        <v>0.0463</v>
       </c>
       <c r="I66" t="n">
         <v>88</v>
@@ -2848,10 +2848,10 @@
         <v>6.49</v>
       </c>
       <c r="G67" t="n">
-        <v>0.0587</v>
+        <v>0.0675</v>
       </c>
       <c r="H67" t="n">
-        <v>0.0398</v>
+        <v>0.0466</v>
       </c>
       <c r="I67" t="n">
         <v>91</v>
@@ -2884,10 +2884,10 @@
         <v>4.29</v>
       </c>
       <c r="G68" t="n">
-        <v>0.0614</v>
+        <v>0.0696</v>
       </c>
       <c r="H68" t="n">
-        <v>0.0631</v>
+        <v>0.0727</v>
       </c>
       <c r="I68" t="n">
         <v>89</v>
@@ -2920,10 +2920,10 @@
         <v>4.29</v>
       </c>
       <c r="G69" t="n">
-        <v>0.062</v>
+        <v>0.0697</v>
       </c>
       <c r="H69" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="I69" t="n">
         <v>92</v>
@@ -2956,10 +2956,10 @@
         <v>4.29</v>
       </c>
       <c r="G70" t="n">
-        <v>0.0623</v>
+        <v>0.0698</v>
       </c>
       <c r="H70" t="n">
-        <v>0.0639</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="I70" t="n">
         <v>89</v>
@@ -2992,10 +2992,10 @@
         <v>4.09</v>
       </c>
       <c r="G71" t="n">
-        <v>0.0526</v>
+        <v>0.0613</v>
       </c>
       <c r="H71" t="n">
-        <v>0.0567</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="I71" t="n">
         <v>91</v>
@@ -3028,10 +3028,10 @@
         <v>4.09</v>
       </c>
       <c r="G72" t="n">
-        <v>0.0557</v>
+        <v>0.0619</v>
       </c>
       <c r="H72" t="n">
-        <v>0.06</v>
+        <v>0.0678</v>
       </c>
       <c r="I72" t="n">
         <v>90</v>
@@ -3064,10 +3064,10 @@
         <v>4.09</v>
       </c>
       <c r="G73" t="n">
-        <v>0.0536</v>
+        <v>0.0615</v>
       </c>
       <c r="H73" t="n">
-        <v>0.0577</v>
+        <v>0.0674</v>
       </c>
       <c r="I73" t="n">
         <v>91</v>
@@ -3100,10 +3100,10 @@
         <v>2.79</v>
       </c>
       <c r="G74" t="n">
-        <v>0.0466</v>
+        <v>0.0519</v>
       </c>
       <c r="H74" t="n">
-        <v>0.0737</v>
+        <v>0.0835</v>
       </c>
       <c r="I74" t="n">
         <v>90</v>
@@ -3136,10 +3136,10 @@
         <v>2.79</v>
       </c>
       <c r="G75" t="n">
-        <v>0.0443</v>
+        <v>0.0515</v>
       </c>
       <c r="H75" t="n">
-        <v>0.0699</v>
+        <v>0.0827</v>
       </c>
       <c r="I75" t="n">
         <v>90</v>
@@ -3172,10 +3172,10 @@
         <v>2.79</v>
       </c>
       <c r="G76" t="n">
-        <v>0.048</v>
+        <v>0.0522</v>
       </c>
       <c r="H76" t="n">
-        <v>0.0757</v>
+        <v>0.0839</v>
       </c>
       <c r="I76" t="n">
         <v>92</v>
@@ -3208,10 +3208,10 @@
         <v>5.04</v>
       </c>
       <c r="G77" t="n">
-        <v>0.1129</v>
+        <v>0.0828</v>
       </c>
       <c r="H77" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.0631</v>
       </c>
       <c r="I77" t="n">
         <v>89</v>
@@ -3244,10 +3244,10 @@
         <v>5.04</v>
       </c>
       <c r="G78" t="n">
-        <v>0.1114</v>
+        <v>0.0825</v>
       </c>
       <c r="H78" t="n">
-        <v>0.0973</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="I78" t="n">
         <v>90</v>
@@ -3280,10 +3280,10 @@
         <v>5.04</v>
       </c>
       <c r="G79" t="n">
-        <v>0.116</v>
+        <v>0.0835</v>
       </c>
       <c r="H79" t="n">
-        <v>0.1013</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="I79" t="n">
         <v>91</v>
@@ -3316,10 +3316,10 @@
         <v>6.49</v>
       </c>
       <c r="G80" t="n">
-        <v>0.0588</v>
+        <v>0.0675</v>
       </c>
       <c r="H80" t="n">
-        <v>0.0399</v>
+        <v>0.0466</v>
       </c>
       <c r="I80" t="n">
         <v>90</v>
@@ -3352,10 +3352,10 @@
         <v>6.49</v>
       </c>
       <c r="G81" t="n">
-        <v>0.0551</v>
+        <v>0.0667</v>
       </c>
       <c r="H81" t="n">
-        <v>0.0374</v>
+        <v>0.0461</v>
       </c>
       <c r="I81" t="n">
         <v>92</v>
@@ -3388,10 +3388,10 @@
         <v>6.49</v>
       </c>
       <c r="G82" t="n">
-        <v>0.057</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="H82" t="n">
-        <v>0.0386</v>
+        <v>0.0464</v>
       </c>
       <c r="I82" t="n">
         <v>90</v>
@@ -3424,10 +3424,10 @@
         <v>4.29</v>
       </c>
       <c r="G83" t="n">
-        <v>0.0626</v>
+        <v>0.0698</v>
       </c>
       <c r="H83" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.073</v>
       </c>
       <c r="I83" t="n">
         <v>91</v>
@@ -3460,10 +3460,10 @@
         <v>4.29</v>
       </c>
       <c r="G84" t="n">
-        <v>0.0619</v>
+        <v>0.0697</v>
       </c>
       <c r="H84" t="n">
-        <v>0.0635</v>
+        <v>0.0728</v>
       </c>
       <c r="I84" t="n">
         <v>89</v>
@@ -3496,10 +3496,10 @@
         <v>4.29</v>
       </c>
       <c r="G85" t="n">
-        <v>0.0631</v>
+        <v>0.0699</v>
       </c>
       <c r="H85" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.0731</v>
       </c>
       <c r="I85" t="n">
         <v>90</v>
@@ -3532,10 +3532,10 @@
         <v>4.09</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0539</v>
+        <v>0.0615</v>
       </c>
       <c r="H86" t="n">
-        <v>0.058</v>
+        <v>0.0674</v>
       </c>
       <c r="I86" t="n">
         <v>90</v>
@@ -3568,10 +3568,10 @@
         <v>4.09</v>
       </c>
       <c r="G87" t="n">
-        <v>0.0544</v>
+        <v>0.0616</v>
       </c>
       <c r="H87" t="n">
-        <v>0.0586</v>
+        <v>0.0675</v>
       </c>
       <c r="I87" t="n">
         <v>88</v>
@@ -3604,10 +3604,10 @@
         <v>4.09</v>
       </c>
       <c r="G88" t="n">
-        <v>0.0529</v>
+        <v>0.0613</v>
       </c>
       <c r="H88" t="n">
-        <v>0.0569</v>
+        <v>0.0672</v>
       </c>
       <c r="I88" t="n">
         <v>88</v>
@@ -3640,10 +3640,10 @@
         <v>2.79</v>
       </c>
       <c r="G89" t="n">
-        <v>0.0477</v>
+        <v>0.0521</v>
       </c>
       <c r="H89" t="n">
-        <v>0.0752</v>
+        <v>0.0838</v>
       </c>
       <c r="I89" t="n">
         <v>91</v>
@@ -3676,10 +3676,10 @@
         <v>2.79</v>
       </c>
       <c r="G90" t="n">
-        <v>0.0455</v>
+        <v>0.0517</v>
       </c>
       <c r="H90" t="n">
-        <v>0.0718</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="I90" t="n">
         <v>91</v>
@@ -3712,10 +3712,10 @@
         <v>2.79</v>
       </c>
       <c r="G91" t="n">
-        <v>0.0469</v>
+        <v>0.052</v>
       </c>
       <c r="H91" t="n">
-        <v>0.074</v>
+        <v>0.0835</v>
       </c>
       <c r="I91" t="n">
         <v>91</v>
@@ -3748,10 +3748,10 @@
         <v>5.04</v>
       </c>
       <c r="G92" t="n">
-        <v>0.1115</v>
+        <v>0.0825</v>
       </c>
       <c r="H92" t="n">
-        <v>0.0975</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="I92" t="n">
         <v>91</v>
@@ -3784,10 +3784,10 @@
         <v>5.04</v>
       </c>
       <c r="G93" t="n">
-        <v>0.1144</v>
+        <v>0.083</v>
       </c>
       <c r="H93" t="n">
-        <v>0.1</v>
+        <v>0.0633</v>
       </c>
       <c r="I93" t="n">
         <v>93</v>
@@ -3820,10 +3820,10 @@
         <v>5.04</v>
       </c>
       <c r="G94" t="n">
-        <v>0.1132</v>
+        <v>0.0828</v>
       </c>
       <c r="H94" t="n">
-        <v>0.099</v>
+        <v>0.0631</v>
       </c>
       <c r="I94" t="n">
         <v>91</v>
@@ -3856,10 +3856,10 @@
         <v>6.49</v>
       </c>
       <c r="G95" t="n">
-        <v>0.0593</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="H95" t="n">
-        <v>0.0403</v>
+        <v>0.0467</v>
       </c>
       <c r="I95" t="n">
         <v>89</v>
@@ -3892,10 +3892,10 @@
         <v>6.49</v>
       </c>
       <c r="G96" t="n">
-        <v>0.0597</v>
+        <v>0.0677</v>
       </c>
       <c r="H96" t="n">
-        <v>0.0406</v>
+        <v>0.0468</v>
       </c>
       <c r="I96" t="n">
         <v>91</v>
@@ -3928,10 +3928,10 @@
         <v>6.49</v>
       </c>
       <c r="G97" t="n">
-        <v>0.0569</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="H97" t="n">
-        <v>0.0386</v>
+        <v>0.0464</v>
       </c>
       <c r="I97" t="n">
         <v>89</v>
@@ -3964,10 +3964,10 @@
         <v>4.29</v>
       </c>
       <c r="G98" t="n">
-        <v>0.0624</v>
+        <v>0.0698</v>
       </c>
       <c r="H98" t="n">
-        <v>0.0641</v>
+        <v>0.073</v>
       </c>
       <c r="I98" t="n">
         <v>92</v>
@@ -4000,10 +4000,10 @@
         <v>4.29</v>
       </c>
       <c r="G99" t="n">
-        <v>0.0597</v>
+        <v>0.0693</v>
       </c>
       <c r="H99" t="n">
-        <v>0.0614</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="I99" t="n">
         <v>90</v>
@@ -4036,10 +4036,10 @@
         <v>4.29</v>
       </c>
       <c r="G100" t="n">
-        <v>0.0605</v>
+        <v>0.0694</v>
       </c>
       <c r="H100" t="n">
-        <v>0.0621</v>
+        <v>0.0726</v>
       </c>
       <c r="I100" t="n">
         <v>91</v>
@@ -4072,10 +4072,10 @@
         <v>4.09</v>
       </c>
       <c r="G101" t="n">
-        <v>0.0529</v>
+        <v>0.0613</v>
       </c>
       <c r="H101" t="n">
-        <v>0.057</v>
+        <v>0.0672</v>
       </c>
       <c r="I101" t="n">
         <v>88</v>
@@ -4108,10 +4108,10 @@
         <v>4.09</v>
       </c>
       <c r="G102" t="n">
-        <v>0.0536</v>
+        <v>0.0615</v>
       </c>
       <c r="H102" t="n">
-        <v>0.0577</v>
+        <v>0.0674</v>
       </c>
       <c r="I102" t="n">
         <v>90</v>
@@ -4144,10 +4144,10 @@
         <v>4.09</v>
       </c>
       <c r="G103" t="n">
-        <v>0.0553</v>
+        <v>0.0618</v>
       </c>
       <c r="H103" t="n">
-        <v>0.0595</v>
+        <v>0.0678</v>
       </c>
       <c r="I103" t="n">
         <v>92</v>
@@ -4180,10 +4180,10 @@
         <v>2.79</v>
       </c>
       <c r="G104" t="n">
-        <v>0.0482</v>
+        <v>0.0523</v>
       </c>
       <c r="H104" t="n">
-        <v>0.0762</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="I104" t="n">
         <v>91</v>
@@ -4216,10 +4216,10 @@
         <v>2.79</v>
       </c>
       <c r="G105" t="n">
-        <v>0.0456</v>
+        <v>0.0517</v>
       </c>
       <c r="H105" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="I105" t="n">
         <v>90</v>
@@ -4252,10 +4252,10 @@
         <v>2.79</v>
       </c>
       <c r="G106" t="n">
-        <v>0.0469</v>
+        <v>0.052</v>
       </c>
       <c r="H106" t="n">
-        <v>0.074</v>
+        <v>0.0835</v>
       </c>
       <c r="I106" t="n">
         <v>92</v>
@@ -4288,10 +4288,10 @@
         <v>5.04</v>
       </c>
       <c r="G107" t="n">
-        <v>0.1167</v>
+        <v>0.0837</v>
       </c>
       <c r="H107" t="n">
-        <v>0.102</v>
+        <v>0.0639</v>
       </c>
       <c r="I107" t="n">
         <v>90</v>
@@ -4324,10 +4324,10 @@
         <v>5.04</v>
       </c>
       <c r="G108" t="n">
-        <v>0.1119</v>
+        <v>0.0827</v>
       </c>
       <c r="H108" t="n">
-        <v>0.0978</v>
+        <v>0.063</v>
       </c>
       <c r="I108" t="n">
         <v>88</v>
@@ -4360,10 +4360,10 @@
         <v>5.04</v>
       </c>
       <c r="G109" t="n">
-        <v>0.1139</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="H109" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.0634</v>
       </c>
       <c r="I109" t="n">
         <v>91</v>
@@ -4396,10 +4396,10 @@
         <v>6.49</v>
       </c>
       <c r="G110" t="n">
-        <v>0.0568</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="H110" t="n">
-        <v>0.0385</v>
+        <v>0.0463</v>
       </c>
       <c r="I110" t="n">
         <v>89</v>
@@ -4432,10 +4432,10 @@
         <v>6.49</v>
       </c>
       <c r="G111" t="n">
-        <v>0.0574</v>
+        <v>0.0672</v>
       </c>
       <c r="H111" t="n">
-        <v>0.039</v>
+        <v>0.0464</v>
       </c>
       <c r="I111" t="n">
         <v>89</v>
@@ -4468,10 +4468,10 @@
         <v>6.49</v>
       </c>
       <c r="G112" t="n">
-        <v>0.0561</v>
+        <v>0.0669</v>
       </c>
       <c r="H112" t="n">
-        <v>0.038</v>
+        <v>0.0462</v>
       </c>
       <c r="I112" t="n">
         <v>90</v>
@@ -4504,10 +4504,10 @@
         <v>4.29</v>
       </c>
       <c r="G113" t="n">
-        <v>0.059</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="H113" t="n">
-        <v>0.0606</v>
+        <v>0.0722</v>
       </c>
       <c r="I113" t="n">
         <v>90</v>
@@ -4540,10 +4540,10 @@
         <v>4.29</v>
       </c>
       <c r="G114" t="n">
-        <v>0.0623</v>
+        <v>0.0698</v>
       </c>
       <c r="H114" t="n">
-        <v>0.0639</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="I114" t="n">
         <v>89</v>
@@ -4576,10 +4576,10 @@
         <v>4.29</v>
       </c>
       <c r="G115" t="n">
-        <v>0.0623</v>
+        <v>0.0698</v>
       </c>
       <c r="H115" t="n">
-        <v>0.064</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="I115" t="n">
         <v>92</v>
@@ -4612,10 +4612,10 @@
         <v>4.09</v>
       </c>
       <c r="G116" t="n">
-        <v>0.0548</v>
+        <v>0.0617</v>
       </c>
       <c r="H116" t="n">
-        <v>0.059</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="I116" t="n">
         <v>92</v>
@@ -4648,10 +4648,10 @@
         <v>4.09</v>
       </c>
       <c r="G117" t="n">
-        <v>0.0554</v>
+        <v>0.0618</v>
       </c>
       <c r="H117" t="n">
-        <v>0.0596</v>
+        <v>0.0677</v>
       </c>
       <c r="I117" t="n">
         <v>88</v>
@@ -4684,10 +4684,10 @@
         <v>4.09</v>
       </c>
       <c r="G118" t="n">
-        <v>0.0544</v>
+        <v>0.0616</v>
       </c>
       <c r="H118" t="n">
-        <v>0.0586</v>
+        <v>0.0675</v>
       </c>
       <c r="I118" t="n">
         <v>88</v>
@@ -4720,10 +4720,10 @@
         <v>2.79</v>
       </c>
       <c r="G119" t="n">
-        <v>0.0467</v>
+        <v>0.0519</v>
       </c>
       <c r="H119" t="n">
-        <v>0.0737</v>
+        <v>0.0834</v>
       </c>
       <c r="I119" t="n">
         <v>89</v>
@@ -4756,10 +4756,10 @@
         <v>2.79</v>
       </c>
       <c r="G120" t="n">
-        <v>0.0467</v>
+        <v>0.0519</v>
       </c>
       <c r="H120" t="n">
-        <v>0.0737</v>
+        <v>0.0834</v>
       </c>
       <c r="I120" t="n">
         <v>91</v>
@@ -4792,10 +4792,10 @@
         <v>2.79</v>
       </c>
       <c r="G121" t="n">
-        <v>0.0456</v>
+        <v>0.0517</v>
       </c>
       <c r="H121" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="I121" t="n">
         <v>92</v>
@@ -4828,10 +4828,10 @@
         <v>6.29</v>
       </c>
       <c r="G122" t="n">
-        <v>0.0594</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="H122" t="n">
-        <v>0.0419</v>
+        <v>0.0517</v>
       </c>
       <c r="I122" t="n">
         <v>92</v>
@@ -4864,10 +4864,10 @@
         <v>6.29</v>
       </c>
       <c r="G123" t="n">
-        <v>0.0625</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="H123" t="n">
-        <v>0.044</v>
+        <v>0.0521</v>
       </c>
       <c r="I123" t="n">
         <v>91</v>
@@ -4900,10 +4900,10 @@
         <v>6.29</v>
       </c>
       <c r="G124" t="n">
-        <v>0.0593</v>
+        <v>0.0723</v>
       </c>
       <c r="H124" t="n">
-        <v>0.0418</v>
+        <v>0.0517</v>
       </c>
       <c r="I124" t="n">
         <v>88</v>
@@ -4936,10 +4936,10 @@
         <v>6.49</v>
       </c>
       <c r="G125" t="n">
-        <v>0.0731</v>
+        <v>0.0703</v>
       </c>
       <c r="H125" t="n">
-        <v>0.0499</v>
+        <v>0.0487</v>
       </c>
       <c r="I125" t="n">
         <v>92</v>
@@ -4972,10 +4972,10 @@
         <v>6.49</v>
       </c>
       <c r="G126" t="n">
-        <v>0.0767</v>
+        <v>0.0709</v>
       </c>
       <c r="H126" t="n">
-        <v>0.0524</v>
+        <v>0.0491</v>
       </c>
       <c r="I126" t="n">
         <v>88</v>
@@ -5008,10 +5008,10 @@
         <v>6.49</v>
       </c>
       <c r="G127" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0701</v>
       </c>
       <c r="H127" t="n">
-        <v>0.0491</v>
+        <v>0.0485</v>
       </c>
       <c r="I127" t="n">
         <v>90</v>
@@ -5044,10 +5044,10 @@
         <v>4.29</v>
       </c>
       <c r="G128" t="n">
-        <v>0.0737</v>
+        <v>0.0721</v>
       </c>
       <c r="H128" t="n">
-        <v>0.0762</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="I128" t="n">
         <v>90</v>
@@ -5080,10 +5080,10 @@
         <v>4.29</v>
       </c>
       <c r="G129" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.0723</v>
       </c>
       <c r="H129" t="n">
-        <v>0.0779</v>
+        <v>0.0757</v>
       </c>
       <c r="I129" t="n">
         <v>90</v>
@@ -5116,10 +5116,10 @@
         <v>4.29</v>
       </c>
       <c r="G130" t="n">
-        <v>0.0765</v>
+        <v>0.0725</v>
       </c>
       <c r="H130" t="n">
-        <v>0.0791</v>
+        <v>0.0759</v>
       </c>
       <c r="I130" t="n">
         <v>91</v>
@@ -5152,10 +5152,10 @@
         <v>4.09</v>
       </c>
       <c r="G131" t="n">
-        <v>0.0694</v>
+        <v>0.0645</v>
       </c>
       <c r="H131" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.0708</v>
       </c>
       <c r="I131" t="n">
         <v>91</v>
@@ -5188,10 +5188,10 @@
         <v>4.09</v>
       </c>
       <c r="G132" t="n">
-        <v>0.0697</v>
+        <v>0.0646</v>
       </c>
       <c r="H132" t="n">
-        <v>0.0756</v>
+        <v>0.0709</v>
       </c>
       <c r="I132" t="n">
         <v>92</v>
@@ -5224,10 +5224,10 @@
         <v>4.09</v>
       </c>
       <c r="G133" t="n">
-        <v>0.0648</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="H133" t="n">
-        <v>0.0703</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I133" t="n">
         <v>92</v>
@@ -5260,10 +5260,10 @@
         <v>2.79</v>
       </c>
       <c r="G134" t="n">
-        <v>0.0547</v>
+        <v>0.0535</v>
       </c>
       <c r="H134" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0862</v>
       </c>
       <c r="I134" t="n">
         <v>90</v>
@@ -5296,10 +5296,10 @@
         <v>2.79</v>
       </c>
       <c r="G135" t="n">
-        <v>0.0577</v>
+        <v>0.0541</v>
       </c>
       <c r="H135" t="n">
-        <v>0.0916</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="I135" t="n">
         <v>88</v>
@@ -5332,10 +5332,10 @@
         <v>2.79</v>
       </c>
       <c r="G136" t="n">
-        <v>0.0553</v>
+        <v>0.0536</v>
       </c>
       <c r="H136" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.0864</v>
       </c>
       <c r="I136" t="n">
         <v>91</v>
@@ -5368,10 +5368,10 @@
         <v>6.29</v>
       </c>
       <c r="G137" t="n">
-        <v>0.065</v>
+        <v>0.0733</v>
       </c>
       <c r="H137" t="n">
-        <v>0.0458</v>
+        <v>0.0524</v>
       </c>
       <c r="I137" t="n">
         <v>92</v>
@@ -5404,10 +5404,10 @@
         <v>6.29</v>
       </c>
       <c r="G138" t="n">
-        <v>0.0617</v>
+        <v>0.0727</v>
       </c>
       <c r="H138" t="n">
-        <v>0.0435</v>
+        <v>0.0519</v>
       </c>
       <c r="I138" t="n">
         <v>88</v>
@@ -5440,10 +5440,10 @@
         <v>6.29</v>
       </c>
       <c r="G139" t="n">
-        <v>0.0624</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="H139" t="n">
-        <v>0.044</v>
+        <v>0.052</v>
       </c>
       <c r="I139" t="n">
         <v>92</v>
@@ -5476,10 +5476,10 @@
         <v>6.49</v>
       </c>
       <c r="G140" t="n">
-        <v>0.0722</v>
+        <v>0.0702</v>
       </c>
       <c r="H140" t="n">
-        <v>0.0494</v>
+        <v>0.0486</v>
       </c>
       <c r="I140" t="n">
         <v>88</v>
@@ -5512,10 +5512,10 @@
         <v>6.49</v>
       </c>
       <c r="G141" t="n">
-        <v>0.0701</v>
+        <v>0.0698</v>
       </c>
       <c r="H141" t="n">
-        <v>0.0479</v>
+        <v>0.0483</v>
       </c>
       <c r="I141" t="n">
         <v>88</v>
@@ -5548,10 +5548,10 @@
         <v>6.49</v>
       </c>
       <c r="G142" t="n">
-        <v>0.0737</v>
+        <v>0.0704</v>
       </c>
       <c r="H142" t="n">
-        <v>0.0504</v>
+        <v>0.0487</v>
       </c>
       <c r="I142" t="n">
         <v>90</v>
@@ -5584,10 +5584,10 @@
         <v>4.29</v>
       </c>
       <c r="G143" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.0721</v>
       </c>
       <c r="H143" t="n">
-        <v>0.0764</v>
+        <v>0.0755</v>
       </c>
       <c r="I143" t="n">
         <v>88</v>
@@ -5620,10 +5620,10 @@
         <v>4.29</v>
       </c>
       <c r="G144" t="n">
-        <v>0.0765</v>
+        <v>0.0725</v>
       </c>
       <c r="H144" t="n">
-        <v>0.079</v>
+        <v>0.0759</v>
       </c>
       <c r="I144" t="n">
         <v>88</v>
@@ -5656,10 +5656,10 @@
         <v>4.29</v>
       </c>
       <c r="G145" t="n">
-        <v>0.0767</v>
+        <v>0.0726</v>
       </c>
       <c r="H145" t="n">
-        <v>0.0793</v>
+        <v>0.076</v>
       </c>
       <c r="I145" t="n">
         <v>88</v>
@@ -5692,10 +5692,10 @@
         <v>4.09</v>
       </c>
       <c r="G146" t="n">
-        <v>0.0679</v>
+        <v>0.0643</v>
       </c>
       <c r="H146" t="n">
-        <v>0.0736</v>
+        <v>0.0706</v>
       </c>
       <c r="I146" t="n">
         <v>90</v>
@@ -5728,10 +5728,10 @@
         <v>4.09</v>
       </c>
       <c r="G147" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.0639</v>
       </c>
       <c r="H147" t="n">
-        <v>0.0713</v>
+        <v>0.0701</v>
       </c>
       <c r="I147" t="n">
         <v>91</v>
@@ -5764,10 +5764,10 @@
         <v>4.09</v>
       </c>
       <c r="G148" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.0638</v>
       </c>
       <c r="H148" t="n">
-        <v>0.0707</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I148" t="n">
         <v>88</v>
@@ -5800,10 +5800,10 @@
         <v>2.79</v>
       </c>
       <c r="G149" t="n">
-        <v>0.0567</v>
+        <v>0.0539</v>
       </c>
       <c r="H149" t="n">
-        <v>0.0901</v>
+        <v>0.0867</v>
       </c>
       <c r="I149" t="n">
         <v>91</v>
@@ -5836,10 +5836,10 @@
         <v>2.79</v>
       </c>
       <c r="G150" t="n">
-        <v>0.0569</v>
+        <v>0.0539</v>
       </c>
       <c r="H150" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.0868</v>
       </c>
       <c r="I150" t="n">
         <v>92</v>
@@ -5872,10 +5872,10 @@
         <v>2.79</v>
       </c>
       <c r="G151" t="n">
-        <v>0.0555</v>
+        <v>0.0537</v>
       </c>
       <c r="H151" t="n">
-        <v>0.0882</v>
+        <v>0.0864</v>
       </c>
       <c r="I151" t="n">
         <v>88</v>
@@ -5908,10 +5908,10 @@
         <v>6.29</v>
       </c>
       <c r="G152" t="n">
-        <v>0.0635</v>
+        <v>0.0731</v>
       </c>
       <c r="H152" t="n">
-        <v>0.045</v>
+        <v>0.0522</v>
       </c>
       <c r="I152" t="n">
         <v>89</v>
@@ -5944,10 +5944,10 @@
         <v>6.29</v>
       </c>
       <c r="G153" t="n">
-        <v>0.0672</v>
+        <v>0.0737</v>
       </c>
       <c r="H153" t="n">
-        <v>0.0477</v>
+        <v>0.0527</v>
       </c>
       <c r="I153" t="n">
         <v>91</v>
@@ -5980,10 +5980,10 @@
         <v>6.29</v>
       </c>
       <c r="G154" t="n">
-        <v>0.067</v>
+        <v>0.0737</v>
       </c>
       <c r="H154" t="n">
-        <v>0.0476</v>
+        <v>0.0527</v>
       </c>
       <c r="I154" t="n">
         <v>88</v>
@@ -6016,10 +6016,10 @@
         <v>6.49</v>
       </c>
       <c r="G155" t="n">
-        <v>0.0725</v>
+        <v>0.0702</v>
       </c>
       <c r="H155" t="n">
-        <v>0.0498</v>
+        <v>0.0486</v>
       </c>
       <c r="I155" t="n">
         <v>88</v>
@@ -6052,10 +6052,10 @@
         <v>6.49</v>
       </c>
       <c r="G156" t="n">
-        <v>0.0741</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="H156" t="n">
-        <v>0.0509</v>
+        <v>0.0488</v>
       </c>
       <c r="I156" t="n">
         <v>88</v>
@@ -6088,10 +6088,10 @@
         <v>6.49</v>
       </c>
       <c r="G157" t="n">
-        <v>0.0699</v>
+        <v>0.0698</v>
       </c>
       <c r="H157" t="n">
-        <v>0.048</v>
+        <v>0.0483</v>
       </c>
       <c r="I157" t="n">
         <v>88</v>
@@ -6124,10 +6124,10 @@
         <v>4.29</v>
       </c>
       <c r="G158" t="n">
-        <v>0.0737</v>
+        <v>0.0721</v>
       </c>
       <c r="H158" t="n">
-        <v>0.0766</v>
+        <v>0.0755</v>
       </c>
       <c r="I158" t="n">
         <v>92</v>
@@ -6160,10 +6160,10 @@
         <v>4.29</v>
       </c>
       <c r="G159" t="n">
-        <v>0.0757</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="H159" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.0759</v>
       </c>
       <c r="I159" t="n">
         <v>90</v>
@@ -6196,10 +6196,10 @@
         <v>4.29</v>
       </c>
       <c r="G160" t="n">
-        <v>0.0728</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="H160" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="I160" t="n">
         <v>92</v>
@@ -6232,10 +6232,10 @@
         <v>4.09</v>
       </c>
       <c r="G161" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.0641</v>
       </c>
       <c r="H161" t="n">
-        <v>0.0732</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="I161" t="n">
         <v>88</v>
@@ -6268,10 +6268,10 @@
         <v>4.09</v>
       </c>
       <c r="G162" t="n">
-        <v>0.0658</v>
+        <v>0.0639</v>
       </c>
       <c r="H162" t="n">
-        <v>0.0718</v>
+        <v>0.0702</v>
       </c>
       <c r="I162" t="n">
         <v>91</v>
@@ -6304,10 +6304,10 @@
         <v>4.09</v>
       </c>
       <c r="G163" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.0641</v>
       </c>
       <c r="H163" t="n">
-        <v>0.0732</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="I163" t="n">
         <v>90</v>
@@ -6340,10 +6340,10 @@
         <v>2.79</v>
       </c>
       <c r="G164" t="n">
-        <v>0.0551</v>
+        <v>0.0536</v>
       </c>
       <c r="H164" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.0864</v>
       </c>
       <c r="I164" t="n">
         <v>89</v>
@@ -6376,10 +6376,10 @@
         <v>2.79</v>
       </c>
       <c r="G165" t="n">
-        <v>0.0546</v>
+        <v>0.0535</v>
       </c>
       <c r="H165" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.0863</v>
       </c>
       <c r="I165" t="n">
         <v>92</v>
@@ -6412,10 +6412,10 @@
         <v>2.79</v>
       </c>
       <c r="G166" t="n">
-        <v>0.054</v>
+        <v>0.0534</v>
       </c>
       <c r="H166" t="n">
-        <v>0.0863</v>
+        <v>0.0861</v>
       </c>
       <c r="I166" t="n">
         <v>92</v>
@@ -6448,10 +6448,10 @@
         <v>6.29</v>
       </c>
       <c r="G167" t="n">
-        <v>0.0694</v>
+        <v>0.0741</v>
       </c>
       <c r="H167" t="n">
-        <v>0.0493</v>
+        <v>0.053</v>
       </c>
       <c r="I167" t="n">
         <v>90</v>
@@ -6484,10 +6484,10 @@
         <v>6.29</v>
       </c>
       <c r="G168" t="n">
-        <v>0.0658</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="H168" t="n">
-        <v>0.0467</v>
+        <v>0.0525</v>
       </c>
       <c r="I168" t="n">
         <v>91</v>
@@ -6520,10 +6520,10 @@
         <v>6.29</v>
       </c>
       <c r="G169" t="n">
-        <v>0.0659</v>
+        <v>0.0735</v>
       </c>
       <c r="H169" t="n">
-        <v>0.0468</v>
+        <v>0.0525</v>
       </c>
       <c r="I169" t="n">
         <v>92</v>
@@ -6556,10 +6556,10 @@
         <v>6.49</v>
       </c>
       <c r="G170" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.0703</v>
       </c>
       <c r="H170" t="n">
-        <v>0.0502</v>
+        <v>0.0487</v>
       </c>
       <c r="I170" t="n">
         <v>90</v>
@@ -6592,10 +6592,10 @@
         <v>6.49</v>
       </c>
       <c r="G171" t="n">
-        <v>0.0708</v>
+        <v>0.0699</v>
       </c>
       <c r="H171" t="n">
-        <v>0.0487</v>
+        <v>0.0484</v>
       </c>
       <c r="I171" t="n">
         <v>89</v>
@@ -6628,10 +6628,10 @@
         <v>6.49</v>
       </c>
       <c r="G172" t="n">
-        <v>0.0733</v>
+        <v>0.0704</v>
       </c>
       <c r="H172" t="n">
-        <v>0.0505</v>
+        <v>0.0488</v>
       </c>
       <c r="I172" t="n">
         <v>89</v>
@@ -6664,10 +6664,10 @@
         <v>4.29</v>
       </c>
       <c r="G173" t="n">
-        <v>0.07439999999999999</v>
+        <v>0.0722</v>
       </c>
       <c r="H173" t="n">
-        <v>0.0775</v>
+        <v>0.0757</v>
       </c>
       <c r="I173" t="n">
         <v>90</v>
@@ -6700,10 +6700,10 @@
         <v>4.29</v>
       </c>
       <c r="G174" t="n">
-        <v>0.0743</v>
+        <v>0.0722</v>
       </c>
       <c r="H174" t="n">
-        <v>0.0774</v>
+        <v>0.0756</v>
       </c>
       <c r="I174" t="n">
         <v>89</v>
@@ -6736,10 +6736,10 @@
         <v>4.29</v>
       </c>
       <c r="G175" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="H175" t="n">
         <v>0.076</v>
-      </c>
-      <c r="H175" t="n">
-        <v>0.0791</v>
       </c>
       <c r="I175" t="n">
         <v>90</v>
@@ -6772,10 +6772,10 @@
         <v>4.09</v>
       </c>
       <c r="G176" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.064</v>
       </c>
       <c r="H176" t="n">
-        <v>0.0728</v>
+        <v>0.0704</v>
       </c>
       <c r="I176" t="n">
         <v>91</v>
@@ -6808,10 +6808,10 @@
         <v>4.09</v>
       </c>
       <c r="G177" t="n">
-        <v>0.063</v>
+        <v>0.0634</v>
       </c>
       <c r="H177" t="n">
-        <v>0.0689</v>
+        <v>0.0697</v>
       </c>
       <c r="I177" t="n">
         <v>88</v>
@@ -6844,10 +6844,10 @@
         <v>4.09</v>
       </c>
       <c r="G178" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.0634</v>
       </c>
       <c r="H178" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0697</v>
       </c>
       <c r="I178" t="n">
         <v>88</v>
@@ -6880,10 +6880,10 @@
         <v>2.79</v>
       </c>
       <c r="G179" t="n">
-        <v>0.0555</v>
+        <v>0.0537</v>
       </c>
       <c r="H179" t="n">
-        <v>0.0888</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="I179" t="n">
         <v>89</v>
@@ -6916,10 +6916,10 @@
         <v>2.79</v>
       </c>
       <c r="G180" t="n">
-        <v>0.055</v>
+        <v>0.0536</v>
       </c>
       <c r="H180" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.0864</v>
       </c>
       <c r="I180" t="n">
         <v>92</v>
@@ -6952,10 +6952,10 @@
         <v>2.79</v>
       </c>
       <c r="G181" t="n">
-        <v>0.054</v>
+        <v>0.0534</v>
       </c>
       <c r="H181" t="n">
-        <v>0.0864</v>
+        <v>0.0861</v>
       </c>
       <c r="I181" t="n">
         <v>91</v>
@@ -6988,10 +6988,10 @@
         <v>6.29</v>
       </c>
       <c r="G182" t="n">
-        <v>0.0679</v>
+        <v>0.0743</v>
       </c>
       <c r="H182" t="n">
-        <v>0.0484</v>
+        <v>0.0532</v>
       </c>
       <c r="I182" t="n">
         <v>88</v>
@@ -7024,10 +7024,10 @@
         <v>6.29</v>
       </c>
       <c r="G183" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.075</v>
       </c>
       <c r="H183" t="n">
-        <v>0.0513</v>
+        <v>0.0537</v>
       </c>
       <c r="I183" t="n">
         <v>92</v>
@@ -7060,10 +7060,10 @@
         <v>6.29</v>
       </c>
       <c r="G184" t="n">
-        <v>0.0696</v>
+        <v>0.0746</v>
       </c>
       <c r="H184" t="n">
-        <v>0.0496</v>
+        <v>0.0534</v>
       </c>
       <c r="I184" t="n">
         <v>89</v>
@@ -7096,10 +7096,10 @@
         <v>6.49</v>
       </c>
       <c r="G185" t="n">
-        <v>0.0718</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H185" t="n">
-        <v>0.0496</v>
+        <v>0.0485</v>
       </c>
       <c r="I185" t="n">
         <v>89</v>
@@ -7132,10 +7132,10 @@
         <v>6.49</v>
       </c>
       <c r="G186" t="n">
-        <v>0.0745</v>
+        <v>0.0704</v>
       </c>
       <c r="H186" t="n">
-        <v>0.0514</v>
+        <v>0.0489</v>
       </c>
       <c r="I186" t="n">
         <v>88</v>
@@ -7168,10 +7168,10 @@
         <v>6.49</v>
       </c>
       <c r="G187" t="n">
-        <v>0.0694</v>
+        <v>0.0696</v>
       </c>
       <c r="H187" t="n">
-        <v>0.048</v>
+        <v>0.0482</v>
       </c>
       <c r="I187" t="n">
         <v>89</v>
@@ -7204,10 +7204,10 @@
         <v>4.29</v>
       </c>
       <c r="G188" t="n">
-        <v>0.0723</v>
+        <v>0.0717</v>
       </c>
       <c r="H188" t="n">
-        <v>0.0756</v>
+        <v>0.0752</v>
       </c>
       <c r="I188" t="n">
         <v>89</v>
@@ -7240,10 +7240,10 @@
         <v>4.29</v>
       </c>
       <c r="G189" t="n">
-        <v>0.0745</v>
+        <v>0.0721</v>
       </c>
       <c r="H189" t="n">
-        <v>0.0779</v>
+        <v>0.0756</v>
       </c>
       <c r="I189" t="n">
         <v>91</v>
@@ -7276,10 +7276,10 @@
         <v>4.29</v>
       </c>
       <c r="G190" t="n">
-        <v>0.0722</v>
+        <v>0.0717</v>
       </c>
       <c r="H190" t="n">
-        <v>0.0755</v>
+        <v>0.0752</v>
       </c>
       <c r="I190" t="n">
         <v>89</v>
@@ -7312,10 +7312,10 @@
         <v>4.09</v>
       </c>
       <c r="G191" t="n">
-        <v>0.0665</v>
+        <v>0.0639</v>
       </c>
       <c r="H191" t="n">
-        <v>0.0728</v>
+        <v>0.0703</v>
       </c>
       <c r="I191" t="n">
         <v>92</v>
@@ -7348,10 +7348,10 @@
         <v>4.09</v>
       </c>
       <c r="G192" t="n">
-        <v>0.064</v>
+        <v>0.0635</v>
       </c>
       <c r="H192" t="n">
-        <v>0.0702</v>
+        <v>0.0698</v>
       </c>
       <c r="I192" t="n">
         <v>92</v>
@@ -7387,7 +7387,7 @@
         <v>0.0634</v>
       </c>
       <c r="H193" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.0697</v>
       </c>
       <c r="I193" t="n">
         <v>88</v>
@@ -7420,10 +7420,10 @@
         <v>2.79</v>
       </c>
       <c r="G194" t="n">
-        <v>0.0537</v>
+        <v>0.0533</v>
       </c>
       <c r="H194" t="n">
-        <v>0.0863</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="I194" t="n">
         <v>88</v>
@@ -7456,10 +7456,10 @@
         <v>2.79</v>
       </c>
       <c r="G195" t="n">
-        <v>0.0547</v>
+        <v>0.0534</v>
       </c>
       <c r="H195" t="n">
-        <v>0.0878</v>
+        <v>0.0862</v>
       </c>
       <c r="I195" t="n">
         <v>88</v>
@@ -7492,10 +7492,10 @@
         <v>2.79</v>
       </c>
       <c r="G196" t="n">
-        <v>0.0536</v>
+        <v>0.0532</v>
       </c>
       <c r="H196" t="n">
-        <v>0.0861</v>
+        <v>0.0859</v>
       </c>
       <c r="I196" t="n">
         <v>91</v>
@@ -7528,10 +7528,10 @@
         <v>6.29</v>
       </c>
       <c r="G197" t="n">
-        <v>0.0684</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="H197" t="n">
-        <v>0.0488</v>
+        <v>0.0532</v>
       </c>
       <c r="I197" t="n">
         <v>90</v>
@@ -7564,10 +7564,10 @@
         <v>6.29</v>
       </c>
       <c r="G198" t="n">
-        <v>0.0725</v>
+        <v>0.0751</v>
       </c>
       <c r="H198" t="n">
-        <v>0.0517</v>
+        <v>0.0538</v>
       </c>
       <c r="I198" t="n">
         <v>92</v>
@@ -7600,10 +7600,10 @@
         <v>6.29</v>
       </c>
       <c r="G199" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.075</v>
       </c>
       <c r="H199" t="n">
-        <v>0.0513</v>
+        <v>0.0537</v>
       </c>
       <c r="I199" t="n">
         <v>89</v>
@@ -7636,10 +7636,10 @@
         <v>6.49</v>
       </c>
       <c r="G200" t="n">
-        <v>0.0722</v>
+        <v>0.0701</v>
       </c>
       <c r="H200" t="n">
-        <v>0.0499</v>
+        <v>0.0486</v>
       </c>
       <c r="I200" t="n">
         <v>90</v>
@@ -7672,10 +7672,10 @@
         <v>6.49</v>
       </c>
       <c r="G201" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.0698</v>
       </c>
       <c r="H201" t="n">
-        <v>0.0488</v>
+        <v>0.0484</v>
       </c>
       <c r="I201" t="n">
         <v>90</v>
@@ -7708,10 +7708,10 @@
         <v>6.49</v>
       </c>
       <c r="G202" t="n">
-        <v>0.0732</v>
+        <v>0.0702</v>
       </c>
       <c r="H202" t="n">
-        <v>0.0506</v>
+        <v>0.0487</v>
       </c>
       <c r="I202" t="n">
         <v>88</v>
@@ -7744,10 +7744,10 @@
         <v>4.29</v>
       </c>
       <c r="G203" t="n">
-        <v>0.0697</v>
+        <v>0.0712</v>
       </c>
       <c r="H203" t="n">
-        <v>0.073</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="I203" t="n">
         <v>89</v>
@@ -7780,7 +7780,7 @@
         <v>4.29</v>
       </c>
       <c r="G204" t="n">
-        <v>0.0718</v>
+        <v>0.0716</v>
       </c>
       <c r="H204" t="n">
         <v>0.0751</v>
@@ -7816,10 +7816,10 @@
         <v>4.29</v>
       </c>
       <c r="G205" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="H205" t="n">
-        <v>0.0746</v>
+        <v>0.0751</v>
       </c>
       <c r="I205" t="n">
         <v>88</v>
@@ -7852,10 +7852,10 @@
         <v>4.09</v>
       </c>
       <c r="G206" t="n">
-        <v>0.0664</v>
+        <v>0.0639</v>
       </c>
       <c r="H206" t="n">
-        <v>0.0728</v>
+        <v>0.0703</v>
       </c>
       <c r="I206" t="n">
         <v>92</v>
@@ -7888,10 +7888,10 @@
         <v>4.09</v>
       </c>
       <c r="G207" t="n">
-        <v>0.0645</v>
+        <v>0.0635</v>
       </c>
       <c r="H207" t="n">
-        <v>0.0707</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I207" t="n">
         <v>90</v>
@@ -7924,10 +7924,10 @@
         <v>4.09</v>
       </c>
       <c r="G208" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.0638</v>
       </c>
       <c r="H208" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.0702</v>
       </c>
       <c r="I208" t="n">
         <v>89</v>
@@ -7960,10 +7960,10 @@
         <v>2.79</v>
       </c>
       <c r="G209" t="n">
-        <v>0.0524</v>
+        <v>0.053</v>
       </c>
       <c r="H209" t="n">
-        <v>0.0842</v>
+        <v>0.0856</v>
       </c>
       <c r="I209" t="n">
         <v>90</v>
@@ -7996,10 +7996,10 @@
         <v>2.79</v>
       </c>
       <c r="G210" t="n">
-        <v>0.0558</v>
+        <v>0.0537</v>
       </c>
       <c r="H210" t="n">
-        <v>0.0898</v>
+        <v>0.0866</v>
       </c>
       <c r="I210" t="n">
         <v>90</v>
@@ -8032,10 +8032,10 @@
         <v>2.79</v>
       </c>
       <c r="G211" t="n">
-        <v>0.0538</v>
+        <v>0.0533</v>
       </c>
       <c r="H211" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="I211" t="n">
         <v>91</v>
@@ -8068,10 +8068,10 @@
         <v>6.29</v>
       </c>
       <c r="G212" t="n">
-        <v>0.0752</v>
+        <v>0.0756</v>
       </c>
       <c r="H212" t="n">
-        <v>0.0539</v>
+        <v>0.0541</v>
       </c>
       <c r="I212" t="n">
         <v>89</v>
@@ -8104,10 +8104,10 @@
         <v>6.29</v>
       </c>
       <c r="G213" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.0756</v>
       </c>
       <c r="H213" t="n">
-        <v>0.0539</v>
+        <v>0.0542</v>
       </c>
       <c r="I213" t="n">
         <v>89</v>
@@ -8140,10 +8140,10 @@
         <v>6.29</v>
       </c>
       <c r="G214" t="n">
-        <v>0.0721</v>
+        <v>0.075</v>
       </c>
       <c r="H214" t="n">
-        <v>0.0516</v>
+        <v>0.0537</v>
       </c>
       <c r="I214" t="n">
         <v>90</v>
@@ -8176,10 +8176,10 @@
         <v>6.49</v>
       </c>
       <c r="G215" t="n">
-        <v>0.0694</v>
+        <v>0.0696</v>
       </c>
       <c r="H215" t="n">
-        <v>0.0482</v>
+        <v>0.0483</v>
       </c>
       <c r="I215" t="n">
         <v>91</v>
@@ -8212,10 +8212,10 @@
         <v>6.49</v>
       </c>
       <c r="G216" t="n">
-        <v>0.0701</v>
+        <v>0.0697</v>
       </c>
       <c r="H216" t="n">
-        <v>0.0486</v>
+        <v>0.0484</v>
       </c>
       <c r="I216" t="n">
         <v>89</v>
@@ -8248,10 +8248,10 @@
         <v>6.49</v>
       </c>
       <c r="G217" t="n">
-        <v>0.0708</v>
+        <v>0.0698</v>
       </c>
       <c r="H217" t="n">
-        <v>0.0491</v>
+        <v>0.0485</v>
       </c>
       <c r="I217" t="n">
         <v>92</v>
@@ -8284,10 +8284,10 @@
         <v>4.29</v>
       </c>
       <c r="G218" t="n">
-        <v>0.0721</v>
+        <v>0.0717</v>
       </c>
       <c r="H218" t="n">
-        <v>0.0757</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="I218" t="n">
         <v>92</v>
@@ -8320,10 +8320,10 @@
         <v>4.29</v>
       </c>
       <c r="G219" t="n">
-        <v>0.0733</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="H219" t="n">
-        <v>0.0769</v>
+        <v>0.0755</v>
       </c>
       <c r="I219" t="n">
         <v>90</v>
@@ -8356,10 +8356,10 @@
         <v>4.29</v>
       </c>
       <c r="G220" t="n">
-        <v>0.0727</v>
+        <v>0.0718</v>
       </c>
       <c r="H220" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="I220" t="n">
         <v>91</v>
@@ -8392,10 +8392,10 @@
         <v>4.09</v>
       </c>
       <c r="G221" t="n">
-        <v>0.0631</v>
+        <v>0.0633</v>
       </c>
       <c r="H221" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.0697</v>
       </c>
       <c r="I221" t="n">
         <v>88</v>
@@ -8431,7 +8431,7 @@
         <v>0.0633</v>
       </c>
       <c r="H222" t="n">
-        <v>0.0697</v>
+        <v>0.0698</v>
       </c>
       <c r="I222" t="n">
         <v>92</v>
@@ -8500,10 +8500,10 @@
         <v>2.79</v>
       </c>
       <c r="G224" t="n">
-        <v>0.052</v>
+        <v>0.053</v>
       </c>
       <c r="H224" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="I224" t="n">
         <v>92</v>
@@ -8536,10 +8536,10 @@
         <v>2.79</v>
       </c>
       <c r="G225" t="n">
-        <v>0.0523</v>
+        <v>0.053</v>
       </c>
       <c r="H225" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.0856</v>
       </c>
       <c r="I225" t="n">
         <v>90</v>
@@ -8572,10 +8572,10 @@
         <v>2.79</v>
       </c>
       <c r="G226" t="n">
-        <v>0.0547</v>
+        <v>0.0535</v>
       </c>
       <c r="H226" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.0863</v>
       </c>
       <c r="I226" t="n">
         <v>88</v>
@@ -8608,10 +8608,10 @@
         <v>6.29</v>
       </c>
       <c r="G227" t="n">
-        <v>0.0725</v>
+        <v>0.0751</v>
       </c>
       <c r="H227" t="n">
-        <v>0.0519</v>
+        <v>0.0538</v>
       </c>
       <c r="I227" t="n">
         <v>88</v>
@@ -8644,10 +8644,10 @@
         <v>6.29</v>
       </c>
       <c r="G228" t="n">
-        <v>0.0764</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="H228" t="n">
-        <v>0.0547</v>
+        <v>0.0543</v>
       </c>
       <c r="I228" t="n">
         <v>91</v>
@@ -8716,10 +8716,10 @@
         <v>6.49</v>
       </c>
       <c r="G230" t="n">
-        <v>0.0673</v>
+        <v>0.0692</v>
       </c>
       <c r="H230" t="n">
-        <v>0.0467</v>
+        <v>0.048</v>
       </c>
       <c r="I230" t="n">
         <v>90</v>
@@ -8752,10 +8752,10 @@
         <v>6.49</v>
       </c>
       <c r="G231" t="n">
-        <v>0.0713</v>
+        <v>0.0699</v>
       </c>
       <c r="H231" t="n">
-        <v>0.0495</v>
+        <v>0.0485</v>
       </c>
       <c r="I231" t="n">
         <v>92</v>
@@ -8788,10 +8788,10 @@
         <v>6.49</v>
       </c>
       <c r="G232" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H232" t="n">
-        <v>0.0499</v>
+        <v>0.0486</v>
       </c>
       <c r="I232" t="n">
         <v>92</v>
@@ -8824,10 +8824,10 @@
         <v>4.29</v>
       </c>
       <c r="G233" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0716</v>
       </c>
       <c r="H233" t="n">
-        <v>0.0755</v>
+        <v>0.0752</v>
       </c>
       <c r="I233" t="n">
         <v>92</v>
@@ -8860,10 +8860,10 @@
         <v>4.29</v>
       </c>
       <c r="G234" t="n">
-        <v>0.0717</v>
+        <v>0.0716</v>
       </c>
       <c r="H234" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.0752</v>
       </c>
       <c r="I234" t="n">
         <v>89</v>
@@ -8896,10 +8896,10 @@
         <v>4.29</v>
       </c>
       <c r="G235" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0711</v>
       </c>
       <c r="H235" t="n">
-        <v>0.0725</v>
+        <v>0.0747</v>
       </c>
       <c r="I235" t="n">
         <v>90</v>
@@ -8932,10 +8932,10 @@
         <v>4.09</v>
       </c>
       <c r="G236" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="H236" t="n">
-        <v>0.0717</v>
+        <v>0.0701</v>
       </c>
       <c r="I236" t="n">
         <v>92</v>
@@ -8968,10 +8968,10 @@
         <v>4.09</v>
       </c>
       <c r="G237" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="H237" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.0697</v>
       </c>
       <c r="I237" t="n">
         <v>89</v>
@@ -9004,10 +9004,10 @@
         <v>4.09</v>
       </c>
       <c r="G238" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="H238" t="n">
-        <v>0.0722</v>
+        <v>0.0702</v>
       </c>
       <c r="I238" t="n">
         <v>88</v>
@@ -9040,10 +9040,10 @@
         <v>2.79</v>
       </c>
       <c r="G239" t="n">
-        <v>0.0529</v>
+        <v>0.0531</v>
       </c>
       <c r="H239" t="n">
-        <v>0.0854</v>
+        <v>0.0858</v>
       </c>
       <c r="I239" t="n">
         <v>91</v>
@@ -9076,10 +9076,10 @@
         <v>2.79</v>
       </c>
       <c r="G240" t="n">
-        <v>0.0537</v>
+        <v>0.0533</v>
       </c>
       <c r="H240" t="n">
-        <v>0.0867</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="I240" t="n">
         <v>90</v>
@@ -9112,10 +9112,10 @@
         <v>2.79</v>
       </c>
       <c r="G241" t="n">
-        <v>0.0524</v>
+        <v>0.053</v>
       </c>
       <c r="H241" t="n">
-        <v>0.0847</v>
+        <v>0.0857</v>
       </c>
       <c r="I241" t="n">
         <v>90</v>
